--- a/Dados.xlsx
+++ b/Dados.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/paulo_martins_tja_pt/Documents/Dep. Formação/Ambiente Formadores/Mercadona HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="8_{106A7645-39E5-4B5B-88D6-4249688DBD04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D8699E8-C8BA-4550-900B-AB8B6D6C57DA}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="8_{106A7645-39E5-4B5B-88D6-4249688DBD04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0638F2D-0AAF-4366-A74A-1E7DCF130800}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CAF6C6F6-601C-4433-BACD-193488ADEEEE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CAF6C6F6-601C-4433-BACD-193488ADEEEE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Almerim" sheetId="1" r:id="rId1"/>
-    <sheet name="Póvoa do Varzim" sheetId="2" r:id="rId2"/>
+    <sheet name="Almeirim" sheetId="1" r:id="rId1"/>
+    <sheet name="Póvoa de Varzim" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/Dados.xlsx
+++ b/Dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/paulo_martins_tja_pt/Documents/Dep. Formação/Ambiente Formadores/Mercadona HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="8_{106A7645-39E5-4B5B-88D6-4249688DBD04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0638F2D-0AAF-4366-A74A-1E7DCF130800}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="8_{106A7645-39E5-4B5B-88D6-4249688DBD04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BB8651F-F95B-43F7-AEAF-4462FBF0A0E4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CAF6C6F6-601C-4433-BACD-193488ADEEEE}"/>
   </bookViews>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="22">
   <si>
     <t>Nome</t>
   </si>
@@ -151,6 +151,9 @@
   </si>
   <si>
     <t>Redobrar a atenção durante a manobra, uma vez que esta é efetuada entre a estrutura dos equipamentos do “VOLTA” e os estacionamentos cobertos.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1orsus1RBOw-k7LYJupf8lMFA6jYKuHXP/view?usp=drive_link</t>
   </si>
 </sst>
 </file>
@@ -686,14 +689,18 @@
       <c r="K2" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
+      <c r="L2" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" xr:uid="{CFCC2D3F-C4BE-4D01-AC59-103D75593C2D}"/>
     <hyperlink ref="G2" r:id="rId2" xr:uid="{76B3AB30-19CC-4C56-A9E9-10B2A75CAE08}"/>
+    <hyperlink ref="L2" r:id="rId3" xr:uid="{89AC559E-0F98-4B66-8F52-6F1DF2724021}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 

--- a/Dados.xlsx
+++ b/Dados.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/paulo_martins_tja_pt/Documents/Dep. Formação/Ambiente Formadores/Mercadona HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="8_{106A7645-39E5-4B5B-88D6-4249688DBD04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BB8651F-F95B-43F7-AEAF-4462FBF0A0E4}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="8_{106A7645-39E5-4B5B-88D6-4249688DBD04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D8699E8-C8BA-4550-900B-AB8B6D6C57DA}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CAF6C6F6-601C-4433-BACD-193488ADEEEE}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CAF6C6F6-601C-4433-BACD-193488ADEEEE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Almeirim" sheetId="1" r:id="rId1"/>
-    <sheet name="Póvoa de Varzim" sheetId="2" r:id="rId2"/>
+    <sheet name="Almerim" sheetId="1" r:id="rId1"/>
+    <sheet name="Póvoa do Varzim" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="21">
   <si>
     <t>Nome</t>
   </si>
@@ -151,9 +151,6 @@
   </si>
   <si>
     <t>Redobrar a atenção durante a manobra, uma vez que esta é efetuada entre a estrutura dos equipamentos do “VOLTA” e os estacionamentos cobertos.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1orsus1RBOw-k7LYJupf8lMFA6jYKuHXP/view?usp=drive_link</t>
   </si>
 </sst>
 </file>
@@ -689,18 +686,14 @@
       <c r="K2" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>21</v>
-      </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" xr:uid="{CFCC2D3F-C4BE-4D01-AC59-103D75593C2D}"/>
     <hyperlink ref="G2" r:id="rId2" xr:uid="{76B3AB30-19CC-4C56-A9E9-10B2A75CAE08}"/>
-    <hyperlink ref="L2" r:id="rId3" xr:uid="{89AC559E-0F98-4B66-8F52-6F1DF2724021}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 

--- a/Dados.xlsx
+++ b/Dados.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/paulo_martins_tja_pt/Documents/Dep. Formação/Ambiente Formadores/Mercadona HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="8_{106A7645-39E5-4B5B-88D6-4249688DBD04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D8699E8-C8BA-4550-900B-AB8B6D6C57DA}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="8_{106A7645-39E5-4B5B-88D6-4249688DBD04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DAB5595-A9B5-4BFF-B6A9-00D758889947}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CAF6C6F6-601C-4433-BACD-193488ADEEEE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Almerim" sheetId="1" r:id="rId1"/>
-    <sheet name="Póvoa do Varzim" sheetId="2" r:id="rId2"/>
+    <sheet name="Almeirim" sheetId="1" r:id="rId1"/>
+    <sheet name="Póvoa de Varzim" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="4">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -55,40 +55,20 @@
         </ext>
       </extLst>
     </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
   </futureMetadata>
-  <valueMetadata count="4">
+  <valueMetadata count="2">
     <bk>
       <rc t="1" v="0"/>
     </bk>
     <bk>
       <rc t="1" v="1"/>
     </bk>
-    <bk>
-      <rc t="1" v="2"/>
-    </bk>
-    <bk>
-      <rc t="1" v="3"/>
-    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="56">
   <si>
     <t>Nome</t>
   </si>
@@ -151,6 +131,111 @@
   </si>
   <si>
     <t>Redobrar a atenção durante a manobra, uma vez que esta é efetuada entre a estrutura dos equipamentos do “VOLTA” e os estacionamentos cobertos.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1orsus1RBOw-k7LYJupf8lMFA6jYKuHXP/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Lima de Freitas</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Montijo</t>
+  </si>
+  <si>
+    <t>TagusPark</t>
+  </si>
+  <si>
+    <t>Mercês</t>
+  </si>
+  <si>
+    <t>Santarém Retail Park</t>
+  </si>
+  <si>
+    <t>Massama</t>
+  </si>
+  <si>
+    <t>Caldas da Rainha</t>
+  </si>
+  <si>
+    <t>Rio de Mouro</t>
+  </si>
+  <si>
+    <t>Torres Vedras</t>
+  </si>
+  <si>
+    <t>Alta de Lisboa</t>
+  </si>
+  <si>
+    <t>Alverca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Évora </t>
+  </si>
+  <si>
+    <t>Corroios</t>
+  </si>
+  <si>
+    <t>Fernão Ferro</t>
+  </si>
+  <si>
+    <t>Parque Verde</t>
+  </si>
+  <si>
+    <t>Santa Iria da Azóia</t>
+  </si>
+  <si>
+    <t>Q. do Lambert</t>
+  </si>
+  <si>
+    <t>Lavradio</t>
+  </si>
+  <si>
+    <t>Vale Sepal</t>
+  </si>
+  <si>
+    <t>Frielas</t>
+  </si>
+  <si>
+    <t>S. Julião</t>
+  </si>
+  <si>
+    <t>Setúbal</t>
+  </si>
+  <si>
+    <t>Montijo</t>
+  </si>
+  <si>
+    <t>Oeiras</t>
+  </si>
+  <si>
+    <t>Sintra</t>
+  </si>
+  <si>
+    <t>Santarém</t>
+  </si>
+  <si>
+    <t>Lisboa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vila Franca de Xira </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corroios </t>
+  </si>
+  <si>
+    <t>Almada</t>
+  </si>
+  <si>
+    <t>Leiria</t>
+  </si>
+  <si>
+    <t>Barreiro</t>
+  </si>
+  <si>
+    <t>Loures</t>
+  </si>
+  <si>
+    <t>Palmela</t>
   </si>
 </sst>
 </file>
@@ -197,17 +282,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hiperligação" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="2" xr:uid="{AD4F0AE1-EA25-462F-8B68-10DF9FD5D10E}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -264,15 +359,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>1</v>
-    <v>5</v>
-  </rv>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
   <rv s="0">
     <v>2</v>
     <v>5</v>
@@ -599,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDC4123D-EE0E-454D-BCF3-7B0A093E9B80}">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="18.5546875" customWidth="1"/>
@@ -608,10 +695,10 @@
     <col min="6" max="6" width="40.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="39.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="39.6640625" customWidth="1"/>
-    <col min="9" max="13" width="18.5546875" customWidth="1"/>
+    <col min="9" max="11" width="18.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -640,60 +727,340 @@
         <v>5</v>
       </c>
       <c r="J1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" t="s">
-        <v>6</v>
-      </c>
-      <c r="M1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2">
+    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
         <v>7009</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>221205057</v>
       </c>
-      <c r="J2" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K2" t="e" vm="2">
-        <v>#VALUE!</v>
+      <c r="J2" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>7033</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3">
+        <v>265121501</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>7036</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4">
+        <v>211202941</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>7041</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5">
+        <v>211202943</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>7044</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6">
+        <v>211202942</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>7046</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7">
+        <v>243120160</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7048</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8">
+        <v>211202946</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>7049</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9">
+        <v>262130010</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>7054</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10">
+        <v>211202945</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>7055</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11">
+        <v>261133001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>7057</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I12">
+        <v>211202951</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>7058</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13">
+        <v>263137011</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>7060</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14">
+        <v>266127951</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>7061</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
+      </c>
+      <c r="I15">
+        <v>265121502</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>7068</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>51</v>
+      </c>
+      <c r="I16">
+        <v>211202947</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>7069</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>52</v>
+      </c>
+      <c r="I17">
+        <v>244122590</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>7073</v>
+      </c>
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18">
+        <v>910759388</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>7076</v>
+      </c>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>7079</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" t="s">
+        <v>53</v>
+      </c>
+      <c r="I20">
+        <v>211202948</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>7082</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" t="s">
+        <v>52</v>
+      </c>
+      <c r="I21">
+        <v>244122591</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>7084</v>
+      </c>
+      <c r="B22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" t="s">
+        <v>54</v>
+      </c>
+      <c r="I22">
+        <v>211202950</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>7088</v>
+      </c>
+      <c r="B23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" xr:uid="{CFCC2D3F-C4BE-4D01-AC59-103D75593C2D}"/>
     <hyperlink ref="G2" r:id="rId2" xr:uid="{76B3AB30-19CC-4C56-A9E9-10B2A75CAE08}"/>
+    <hyperlink ref="J2" r:id="rId3" xr:uid="{89AC559E-0F98-4B66-8F52-6F1DF2724021}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -769,10 +1136,10 @@
       <c r="H2">
         <v>221205057</v>
       </c>
-      <c r="I2" t="e" vm="3">
+      <c r="I2" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="J2" t="e" vm="4">
+      <c r="J2" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
     </row>

--- a/Dados.xlsx
+++ b/Dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/paulo_martins_tja_pt/Documents/Dep. Formação/Ambiente Formadores/Mercadona HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3ECB6CA0-9746-43FE-8E62-14652AAF4818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{3ECB6CA0-9746-43FE-8E62-14652AAF4818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88B61498-643D-48E3-B711-6F0BEC6573A9}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{462C5653-B832-456D-BA7D-C78D43202BCF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{462C5653-B832-456D-BA7D-C78D43202BCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Almeirim" sheetId="3" r:id="rId1"/>
@@ -191,13 +191,15 @@
     <t>https://drive.google.com/file/d/1orsus1RBOw-k7LYJupf8lMFA6jYKuHXP/view?usp=drive_link</t>
   </si>
   <si>
-    <t>Redobrar a atenção durante a manobra, uma vez que esta é efetuada entre a estrutura dos equipamentos do “VOLTA” e os estacionamentos cobertos.</t>
-  </si>
-  <si>
     <t>Ovar</t>
   </si>
   <si>
     <t>Notas</t>
+  </si>
+  <si>
+    <t>•  Redobrar a atenção durante a manobra, uma vez que esta é efetuada entre a estrutura dos equipamentos do “VOLTA” e os estacionamentos cobertos.
+•  A loja tem cão
+•  A gerente e boa</t>
   </si>
 </sst>
 </file>
@@ -258,7 +260,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -578,7 +580,8 @@
   <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="18.5546875" customWidth="1"/>
+    <col min="1" max="1" width="18.5546875" style="2" customWidth="1"/>
+    <col min="2" max="3" width="18.5546875" customWidth="1"/>
     <col min="4" max="4" width="33.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="36.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="40.6640625" bestFit="1" customWidth="1"/>
@@ -588,7 +591,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -610,7 +613,7 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I1" t="s">
         <v>7</v>
@@ -622,15 +625,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>7009</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>12</v>
@@ -645,7 +648,7 @@
         <v>15</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I2" s="2">
         <v>221205057</v>
@@ -655,7 +658,7 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="A3" s="2">
         <v>7033</v>
       </c>
       <c r="B3" t="s">
@@ -669,7 +672,7 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="A4" s="2">
         <v>7036</v>
       </c>
       <c r="B4" t="s">
@@ -683,7 +686,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="A5" s="2">
         <v>7041</v>
       </c>
       <c r="B5" t="s">
@@ -697,7 +700,7 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="A6" s="2">
         <v>7044</v>
       </c>
       <c r="B6" t="s">
@@ -711,7 +714,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="A7" s="2">
         <v>7046</v>
       </c>
       <c r="B7" t="s">
@@ -725,7 +728,7 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="A8" s="2">
         <v>7048</v>
       </c>
       <c r="B8" t="s">
@@ -739,7 +742,7 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="A9" s="2">
         <v>7049</v>
       </c>
       <c r="B9" t="s">
@@ -753,7 +756,7 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="A10" s="2">
         <v>7054</v>
       </c>
       <c r="B10" t="s">
@@ -767,7 +770,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11">
+      <c r="A11" s="2">
         <v>7055</v>
       </c>
       <c r="B11" t="s">
@@ -781,7 +784,7 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12">
+      <c r="A12" s="2">
         <v>7057</v>
       </c>
       <c r="B12" t="s">
@@ -795,7 +798,7 @@
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13">
+      <c r="A13" s="2">
         <v>7058</v>
       </c>
       <c r="B13" t="s">
@@ -809,7 +812,7 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14">
+      <c r="A14" s="2">
         <v>7060</v>
       </c>
       <c r="B14" t="s">
@@ -823,7 +826,7 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15">
+      <c r="A15" s="2">
         <v>7061</v>
       </c>
       <c r="B15" t="s">
@@ -837,7 +840,7 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16">
+      <c r="A16" s="2">
         <v>7068</v>
       </c>
       <c r="B16" t="s">
@@ -851,7 +854,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17">
+      <c r="A17" s="2">
         <v>7069</v>
       </c>
       <c r="B17" t="s">
@@ -865,7 +868,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18">
+      <c r="A18" s="2">
         <v>7073</v>
       </c>
       <c r="B18" t="s">
@@ -879,7 +882,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19">
+      <c r="A19" s="2">
         <v>7076</v>
       </c>
       <c r="B19" t="s">
@@ -890,7 +893,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20">
+      <c r="A20" s="2">
         <v>7079</v>
       </c>
       <c r="B20" t="s">
@@ -904,7 +907,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21">
+      <c r="A21" s="2">
         <v>7082</v>
       </c>
       <c r="B21" t="s">
@@ -918,7 +921,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22">
+      <c r="A22" s="2">
         <v>7084</v>
       </c>
       <c r="B22" t="s">
@@ -932,7 +935,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23">
+      <c r="A23" s="2">
         <v>7088</v>
       </c>
       <c r="B23" t="s">

--- a/Dados.xlsx
+++ b/Dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/paulo_martins_tja_pt/Documents/Dep. Formação/Ambiente Formadores/Mercadona HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{3ECB6CA0-9746-43FE-8E62-14652AAF4818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88B61498-643D-48E3-B711-6F0BEC6573A9}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{3ECB6CA0-9746-43FE-8E62-14652AAF4818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11F9896B-FB28-486D-9049-A020BE38341A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{462C5653-B832-456D-BA7D-C78D43202BCF}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{462C5653-B832-456D-BA7D-C78D43202BCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Almeirim" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="131">
   <si>
     <t>Número</t>
   </si>
@@ -66,12 +66,6 @@
   </si>
   <si>
     <t>Video2</t>
-  </si>
-  <si>
-    <t>Moldova</t>
-  </si>
-  <si>
-    <t>Estarreja</t>
   </si>
   <si>
     <t>R. Machado Santos 304, 3880-783 Ovar</t>
@@ -200,6 +194,244 @@
     <t>•  Redobrar a atenção durante a manobra, uma vez que esta é efetuada entre a estrutura dos equipamentos do “VOLTA” e os estacionamentos cobertos.
 •  A loja tem cão
 •  A gerente e boa</t>
+  </si>
+  <si>
+    <t>Canidelo</t>
+  </si>
+  <si>
+    <t>Gaia</t>
+  </si>
+  <si>
+    <t>Fânzeres</t>
+  </si>
+  <si>
+    <t>Gondomar</t>
+  </si>
+  <si>
+    <t>GAIA - AV DOM JOAO II (Mafamude)</t>
+  </si>
+  <si>
+    <t>BOAVISTA - DOMNGOS SEQUEIRA</t>
+  </si>
+  <si>
+    <t>Porto</t>
+  </si>
+  <si>
+    <t>OVAR</t>
+  </si>
+  <si>
+    <t>AVEIRO - AV EUROPA</t>
+  </si>
+  <si>
+    <t>Aveiro</t>
+  </si>
+  <si>
+    <t>SÃO SOÃO DA MADEIRA</t>
+  </si>
+  <si>
+    <t>São João da Madeira</t>
+  </si>
+  <si>
+    <t>AVEIRO - SILVA ROCHA</t>
+  </si>
+  <si>
+    <t>CAMPANHÃ</t>
+  </si>
+  <si>
+    <t>ESPINHO</t>
+  </si>
+  <si>
+    <t>Espinho</t>
+  </si>
+  <si>
+    <t>ÁGUEDA - AV 25 DE ABRIL</t>
+  </si>
+  <si>
+    <t>Águeda</t>
+  </si>
+  <si>
+    <t>DIOGO BOTELHO- PORTO</t>
+  </si>
+  <si>
+    <t>STª MARIA FEIRA - SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>Santa Maria da Feira</t>
+  </si>
+  <si>
+    <t>GONDOMAR- HOSPITAL</t>
+  </si>
+  <si>
+    <t>OLIVEIRA DE AZEMÉIS</t>
+  </si>
+  <si>
+    <t>Oliveira de Azeméis</t>
+  </si>
+  <si>
+    <t>FIGUEIRA DA FOZ</t>
+  </si>
+  <si>
+    <t>Figuera da Foz</t>
+  </si>
+  <si>
+    <t>VISEU - AV.ALEXANDRE ALVES</t>
+  </si>
+  <si>
+    <t>Viseu</t>
+  </si>
+  <si>
+    <t>LOUROSA</t>
+  </si>
+  <si>
+    <t>Lourosa</t>
+  </si>
+  <si>
+    <t>CANELAS</t>
+  </si>
+  <si>
+    <t>Coimbra Eiras</t>
+  </si>
+  <si>
+    <t>Coimbra</t>
+  </si>
+  <si>
+    <t>COIMBRA I - SOLUM</t>
+  </si>
+  <si>
+    <t>Guarda</t>
+  </si>
+  <si>
+    <t>R. Nova do Tronco</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/41%C2%B007'32.7%22N+8%C2%B038'15.3%22W/@41.1257397,-8.641813,17z/data=!3m1!4b1!4m13!1m8!3m7!1s0xd2465605bb840af:0x500ebbde4904a60!2sCanidelo,+Vila+Nova+de+Gaia,+Portugal!3b1!8m2!3d41.1233052!4d-8.6461724!16s%2Fm%2F03cmkjx!3m3!8m2!3d41.125736!4d-8.637575</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Galp/@41.2000023,-8.5840168,15z/data=!4m10!1m2!2m1!1sarea+de+servi%C3%A7o+A4!3m6!1s0xd2463fdd2d14787:0xe54397b5855d8659!8m2!3d41.2000023!4d-8.5665073!15sChNhcmVhIGRlIHNlcnZpw6dvIEE0WhUiE2FyZWEgZGUgc2VydmnDp28gYTSSAQtnYXNfc3RhdGlvbpoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VRdGJWbHFRbkJCUlJBQuABAA!16s%2Fg%2F11b6glyzq3</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/41%C2%B007'21.7%22N+8%C2%B035'48.0%22W/@41.122703,-8.601163,17z/data=!3m1!4b1!4m12!1m7!3m6!1s0xd24656afafc6ff3:0xc11a2dcebbc003c2!2sMercadona!8m2!3d41.1246388!4d-8.5969201!16s%2Fg%2F11j_yzbs4v!3m3!8m2!3d41.122699!4d-8.596673</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/5pjXgwsCNErwvRGi9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/AoR47GXGq7EgKqAp8</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/40%C2%B052'32.8%22N+8%C2%B029'17.1%22W/@40.875772,-8.490264,17z/data=!3m2!4b1!5s0xd23820180da1f8d:0x8b0405e1c751cf3!4m12!1m7!3m6!1s0xd2383bba89e7ae9:0x176ab06729d5877!2sMercadona+-+S%C3%A3o+Jo%C3%A3o+da+Madeira!8m2!3d40.8856236!4d-8.489615!16s%2Fg%2F11h0bckmzj!3m3!8m2!3d40.875768!4d-8.48807</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/7XocvdHkTp8gdLfJA</t>
+  </si>
+  <si>
+    <t>https://www.google.pt/maps/@41.1736582,-8.568042,3a,75y,319.56h,81.17t/data=!3m6!1e1!3m4!1slPuAmAUFdAtUSiUCsmvOig!2e0!7i16384!8i8192?hl=pt-PT&amp;entry=ttu</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/41%C2%B001'32.5%22N+8%C2%B037'15.2%22W/@41.025699,-8.625366,17z/data=!3m1!4b1!4m13!1m8!3m7!1s0xd2479c7cd31a89b:0x73c82fb2f5e003f8!2sEspinho,+Portugal!3b1!8m2!3d41.0071914!4d-8.6410332!16zL20vMDNqMGs4!3m3!8m2!3d41.025695!4d-8.620876</t>
+  </si>
+  <si>
+    <t>https://www.google.pt/maps/@40.5709569,-8.4432262,3a,75y,72.33h,83.69t/data=!3m6!1e1!3m4!1sEzcyJ60lrOIqs4lH-KyyhQ!2e0!7i16384!8i8192?hl=pt-PT&amp;entry=ttu</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/40%C2%B055'20.7%22N+8%C2%B033'55.2%22W/@
+.922412,-8.567518,17z/data=!3m1!4b1!4m12!1m7!3m6!1s0xd2381dc14c68389:0x34102e58cb5f3f!2sMercadona+-+Santa+Maria+da+Feira!8m2!3d40.9312727!4d-8.5513214!16s%2Fg%2F11rjtt6bhx!3m3!8m2!3d40.922408!4d-8.565324</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/41%C2%B008'14.9%22N+8%C2%B032'11.9%22W/@41.137482,-8.537744,18z/data=!3m1!4b1!4m4!3m3!8m2!3d41.13748!4d-8.536647</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/h6x3SRaex5Rg8x8UA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/osrpRegG83ZdFVnt9</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Repsol+A25+Viseu+(sul)/@40.623534,-7.930495,17z/data=!4m14!1m7!3m6!1s0xd233706899600ed:0xb5ac567012a36aae!2sMercadona+Viseu!8m2!3d40.6326254!4d-7.9091179!16s%2Fg%2F11s2j25vhc!3m5!1s0xd23373e65fbfa6b:0x2354da54d5b13e37!8m2!3d40.623897!4d-7.933134!16s%2Fg%2F11bvcvn15h</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/40%C2%B059'53.6%22N+8%C2%B032'26.8%22W/@40.9982159,-8.5423314,17z/data=!3m1!4b1!4m12!1m7!3m6!1s0xd247f63178127ef:0x2a3060364fbec877!2sMercadona+-+Lourosa!8m2!3d40.9811537!4d-8.5357284!16s%2Fg%2F11pzhg7wh9!3m3!8m2!3d40.998213!4d-8.54078</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/@41.0845386,-8.6187478,3a,75y,110.4h,90t/data=!3m7!1e1!3m5!1sLIYhBDg9FYzt7FcbWR5jZw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D0%26panoid%3DLIYhBDg9FYzt7FcbWR5jZw%26yaw%3D110.4041920217924!7i16384!8i8192?coh=205410&amp;entry=ttu&amp;g_ep=EgoyMDI0MDkyOS4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/b3nXvnqrmNT2yM7W9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/r2K7Js5SqPFHPpUC8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/vDg9ntxLwPoKw4a7A</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Y64MqQxhyDfpVJbA8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/o49GFrTafmeBaYH98</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/EMPGhZ1nYY2xkFTKA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/CtdqHNaaXXQXcJN67</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/48Cd6njNfqcgTh2S8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/oUzU7dmTKNUkrVfGA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/f2D9yQJgXuQnAf2Y8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Xs4qJG9DwYnFsatz6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/QKnn5dczMTqytPYw6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/GsANA9C7Eik4vddC8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/NXzj8bT3eP82V2WT9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/sPuiAzwhrKtGQZd1A</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/mx3s9SgDTKD8aHYn7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/CWZWeriJ7UNqjFzn8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/zKeoLh7nz3B4JZtq9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/7gHZi1oWWoVD5TqP8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/eUpsDVmkzNxc1wxY7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/V6c8XaXVvLoZr4ac8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/WwHDp5hqWkC1fHez7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/nvJhynfQvNEEyUgP8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/saeN8WiGCWiDkHrW7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/w4iHoxS4Zm9hARVG8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/i2wQfR1zm89Gayky9</t>
   </si>
 </sst>
 </file>
@@ -229,15 +461,33 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -245,14 +495,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -260,11 +540,37 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hiperligação" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="2" xr:uid="{66064622-232A-4B66-8D8E-344707DA0960}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -580,7 +886,7 @@
   <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="18.5546875" style="1" customWidth="1"/>
     <col min="2" max="3" width="18.5546875" customWidth="1"/>
     <col min="4" max="4" width="33.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="36.33203125" bestFit="1" customWidth="1"/>
@@ -591,7 +897,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -613,7 +919,7 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I1" t="s">
         <v>7</v>
@@ -625,324 +931,324 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
         <v>7009</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="I2" s="2">
+      <c r="I2" s="1">
         <v>221205057</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>50</v>
+      <c r="J2" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>7033</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I3">
         <v>265121501</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>7036</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I4">
         <v>211202941</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>7041</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I5">
         <v>211202943</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>7044</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I6">
         <v>211202942</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>7046</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I7">
         <v>243120160</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>7048</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I8">
         <v>211202946</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>7049</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I9">
         <v>262130010</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>7054</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I10">
         <v>211202945</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>7055</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I11">
         <v>261133001</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>7057</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I12">
         <v>211202951</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>7058</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I13">
         <v>263137011</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
+      <c r="A14" s="1">
         <v>7060</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I14">
         <v>266127951</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
+      <c r="A15" s="1">
         <v>7061</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I15">
         <v>265121502</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
+      <c r="A16" s="1">
         <v>7068</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I16">
         <v>211202947</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
+      <c r="A17" s="1">
         <v>7069</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I17">
         <v>244122590</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
+      <c r="A18" s="1">
         <v>7073</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I18">
         <v>910759388</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
+      <c r="A19" s="1">
         <v>7076</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
+      <c r="A20" s="1">
         <v>7079</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I20">
         <v>211202948</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
+      <c r="A21" s="1">
         <v>7082</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I21">
         <v>244122591</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
+      <c r="A22" s="1">
         <v>7084</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I22">
         <v>211202950</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
+      <c r="A23" s="1">
         <v>7088</v>
       </c>
       <c r="B23" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -958,75 +1264,1073 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF5F13FE-4E63-48A0-84FC-D9B1FB307CA9}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="8" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2">
+        <v>7000</v>
+      </c>
+      <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H2">
+        <v>221201095</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>7002</v>
+      </c>
+      <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H3">
+        <v>221201094</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>7003</v>
+      </c>
+      <c r="B4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="H4">
+        <v>221205059</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>7008</v>
+      </c>
+      <c r="B5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="H5">
+        <v>221205056</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>7009</v>
+      </c>
+      <c r="B6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6">
+        <v>221205057</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>7013</v>
       </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2">
-        <v>221205057</v>
+      <c r="B7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H7">
+        <v>256120000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7015</v>
+      </c>
+      <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H8">
+        <v>221205058</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>7017</v>
+      </c>
+      <c r="B9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="H9">
+        <v>256120002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>7020</v>
+      </c>
+      <c r="B10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H10">
+        <v>221202915</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>7022</v>
+      </c>
+      <c r="B11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="H11">
+        <v>256120004</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>7023</v>
+      </c>
+      <c r="B12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="H12">
+        <v>256120003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>7029</v>
+      </c>
+      <c r="B13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="H13">
+        <v>221202919</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>7031</v>
+      </c>
+      <c r="B14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H14">
+        <v>256120250</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>7034</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="H15">
+        <v>221202922</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>7037</v>
+      </c>
+      <c r="B16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H16">
+        <v>256120252</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>7038</v>
+      </c>
+      <c r="B17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="H17">
+        <v>233120010</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>7040</v>
+      </c>
+      <c r="B18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H18">
+        <v>232120210</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>7045</v>
+      </c>
+      <c r="B19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="H19">
+        <v>256120251</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>7056</v>
+      </c>
+      <c r="B20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" t="s">
+        <v>53</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="H20">
+        <v>221202923</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>7066</v>
+      </c>
+      <c r="B21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="H21">
+        <v>239127942</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>7064</v>
+      </c>
+      <c r="B22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" t="s">
+        <v>84</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H22">
+        <v>239127941</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>7067</v>
+      </c>
+      <c r="B23" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="H23">
+        <v>271127941</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>7078</v>
+      </c>
+      <c r="B24" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="H24">
+        <v>221201005</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="F3">
+    <cfRule type="dataBar" priority="20">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{4EB981CD-BB3E-4E18-80E2-1E124DD4C1BD}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="dataBar" priority="19">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{F6A40BF1-B9F4-45C6-8D53-103870EB4B39}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6:F10">
+    <cfRule type="dataBar" priority="18">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{F2D78B82-B72A-4421-874B-4CD843CDF88E}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F11">
+    <cfRule type="dataBar" priority="15">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{86C0E903-4BA0-47B4-B905-76C3F67C57CE}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="dataBar" priority="16">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{0818DE56-5C48-406A-9BA9-84F492B36229}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F13">
+    <cfRule type="dataBar" priority="14">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{A4D5ADE0-6176-459A-85F6-CA1B33C513EB}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14">
+    <cfRule type="dataBar" priority="13">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{F54F33F8-6906-4139-9934-65E447715085}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
+    <cfRule type="dataBar" priority="17">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{B47EB2CE-358C-486D-A189-F0DB279E373E}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F16">
+    <cfRule type="dataBar" priority="10">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{043C1E1A-E301-4083-A263-12038E96B7B7}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17">
+    <cfRule type="dataBar" priority="8">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{5AB8BCA4-C044-47C5-AF38-746497910378}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F18">
+    <cfRule type="dataBar" priority="11">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{9F36BD4E-26D9-4004-B4E3-EF6523A1D063}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="dataBar" priority="12">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{E7A31A38-B52D-477B-98E9-2A0CBD7F2119}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F23">
+    <cfRule type="dataBar" priority="9">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{79500CEB-4C30-43A5-96A9-4489878BC6BF}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24 F5">
+    <cfRule type="dataBar" priority="22">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{0E5B2793-E734-42AC-9ABC-298292A3FE2F}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2">
+    <cfRule type="dataBar" priority="7">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{D8AD0291-2D57-4E56-B3D2-4CE3552BC305}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2">
+    <cfRule type="dataBar" priority="5">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{41C1945A-74C1-4CAA-B2D4-E31D3AD9AE40}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{CDF136A3-4357-467B-B289-155FA14F29A8}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{62ED83B1-7CDB-43D8-9643-E976CF99F150}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6:G8 G10:G23">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{8ADD97A5-EC2B-4596-924A-65E0AE378C8D}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G9">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{E7893CEF-82CD-4050-8BD2-796D578215EF}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5 G24">
+    <cfRule type="dataBar" priority="6">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{E79D7C0A-53D6-421E-89FD-B49CC226495F}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{48C9EFB6-EE40-41BB-BFD7-11D577D8922B}"/>
-    <hyperlink ref="G2" r:id="rId2" xr:uid="{8FC89D01-C6DD-4823-BA1A-210EEBEB9980}"/>
+    <hyperlink ref="F2" r:id="rId1" display="https://www.google.com/maps/place/41%C2%B007'32.7%22N+8%C2%B038'15.3%22W/@41.1257397,-8.641813,17z/data=!3m1!4b1!4m13!1m8!3m7!1s0xd2465605bb840af:0x500ebbde4904a60!2sCanidelo,+Vila+Nova+de+Gaia,+Portugal!3b1!8m2!3d41.1233052!4d-8.6461724!16s%2Fm%2F03cmkjx!3m3!8m2!3d41.125736!4d-8.637575" xr:uid="{19AA09C0-BB00-42C9-AE9F-80BEF3B7895A}"/>
+    <hyperlink ref="F3" r:id="rId2" display="https://www.google.com/maps/place/Galp/@41.2000023,-8.5840168,15z/data=!4m10!1m2!2m1!1sarea+de+servi%C3%A7o+A4!3m6!1s0xd2463fdd2d14787:0xe54397b5855d8659!8m2!3d41.2000023!4d-8.5665073!15sChNhcmVhIGRlIHNlcnZpw6dvIEE0WhUiE2FyZWEgZGUgc2VydmnDp28gYTSSAQtnYXNfc3RhdGlvbpoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VRdGJWbHFRbkJCUlJBQuABAA!16s%2Fg%2F11b6glyzq3" xr:uid="{F86785E8-34B2-4417-84E1-61BFB52D3D78}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{838A2B0E-F885-4894-B5F3-4562C7D493FD}"/>
+    <hyperlink ref="F5" r:id="rId4" xr:uid="{5A2D1402-EC3A-4047-929C-77A025AFD230}"/>
+    <hyperlink ref="F10" r:id="rId5" xr:uid="{B3433C29-4165-41B9-A0CA-911FAB0647B9}"/>
+    <hyperlink ref="F14" r:id="rId6" xr:uid="{61644480-88F4-4245-9FD6-FB736A24EEDA}"/>
+    <hyperlink ref="F19" r:id="rId7" xr:uid="{75B85A1E-4AC0-458F-A4A2-73E1AD786CBC}"/>
+    <hyperlink ref="F11" r:id="rId8" display="https://www.google.com/maps/place/41%C2%B001'32.5%22N+8%C2%B037'15.2%22W/@41.025699,-8.625366,17z/data=!3m1!4b1!4m13!1m8!3m7!1s0xd2479c7cd31a89b:0x73c82fb2f5e003f8!2sEspinho,+Portugal!3b1!8m2!3d41.0071914!4d-8.6410332!16zL20vMDNqMGs4!3m3!8m2!3d41.025695!4d-8.620876" xr:uid="{86B1731B-A1BC-44D9-AF65-177B78EE1519}"/>
+    <hyperlink ref="F15" r:id="rId9" xr:uid="{CD632606-9DD9-499B-8810-62FF547D7F43}"/>
+    <hyperlink ref="F12" r:id="rId10" xr:uid="{3F6652BF-D6A6-4834-A146-7A5E512DF694}"/>
+    <hyperlink ref="F20" r:id="rId11" display="https://www.google.com/maps/@41.0845386,-8.6187478,3a,75y,110.4h,90t/data=!3m7!1e1!3m5!1sLIYhBDg9FYzt7FcbWR5jZw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D0%26panoid%3DLIYhBDg9FYzt7FcbWR5jZw%26yaw%3D110.4041920217924!7i16384!8i8192?coh=205410&amp;entry=ttu&amp;g_ep=EgoyMDI0MDkyOS4wIKXMDSoASAFQAw%3D%3D" xr:uid="{78DCE02D-F81E-4277-8541-DF7E4C63A6AB}"/>
+    <hyperlink ref="F18" r:id="rId12" display="https://www.google.com/maps/place/Repsol+A25+Viseu+(sul)/@40.623534,-7.930495,17z/data=!4m14!1m7!3m6!1s0xd233706899600ed:0xb5ac567012a36aae!2sMercadona+Viseu!8m2!3d40.6326254!4d-7.9091179!16s%2Fg%2F11s2j25vhc!3m5!1s0xd23373e65fbfa6b:0x2354da54d5b13e37!8m2!3d40.623897!4d-7.933134!16s%2Fg%2F11bvcvn15h" xr:uid="{28578BE6-12BA-471E-82A5-111560DDD170}"/>
+    <hyperlink ref="F16" r:id="rId13" xr:uid="{F3F1B3D6-9528-400B-A5EF-C13DAA7D9EC5}"/>
+    <hyperlink ref="F6" r:id="rId14" xr:uid="{3388296C-9D48-4FF4-B58A-DE5A140E079B}"/>
+    <hyperlink ref="F7" r:id="rId15" xr:uid="{8FC35D1F-A3C7-4358-8AAD-5860E6019C11}"/>
+    <hyperlink ref="F9" r:id="rId16" xr:uid="{E7BD4AE1-B61A-46F1-AFDB-0BF749B2ED5A}"/>
+    <hyperlink ref="F17" r:id="rId17" xr:uid="{C36926B3-A65D-4FBC-8CD1-3ABCB11B2249}"/>
+    <hyperlink ref="F22" r:id="rId18" xr:uid="{2B4606B0-9891-4753-B802-CC966A8967EF}"/>
+    <hyperlink ref="F21" r:id="rId19" xr:uid="{B0FAADD4-EB10-4006-B700-2D489F41EA04}"/>
+    <hyperlink ref="F23" r:id="rId20" xr:uid="{25D72EC1-2EA4-460E-9D82-5274BBF4749A}"/>
+    <hyperlink ref="G5" r:id="rId21" xr:uid="{5ACD7D42-12EC-4DCA-84F2-4946F1A38CA5}"/>
+    <hyperlink ref="G21" r:id="rId22" xr:uid="{8B6F81C5-3270-45FF-BFF0-A7842E5DBDE2}"/>
+    <hyperlink ref="G7" r:id="rId23" xr:uid="{E184D786-EE4A-4781-9824-6F7D8B49FBDE}"/>
+    <hyperlink ref="G8" r:id="rId24" xr:uid="{B5C9E3E7-1402-4252-AE1E-7F4334F8AFA5}"/>
+    <hyperlink ref="G17" r:id="rId25" xr:uid="{25551BDD-0E8C-4577-BD45-AFEE5369E426}"/>
+    <hyperlink ref="G23" r:id="rId26" xr:uid="{4E92188D-DED9-4E9C-B6CA-68CDDDB2368E}"/>
+    <hyperlink ref="G6" r:id="rId27" xr:uid="{0790B85E-9275-47F2-9806-967353FEA854}"/>
+    <hyperlink ref="G9" r:id="rId28" xr:uid="{9A4168A3-3351-452B-96D0-F46764C7EF20}"/>
+    <hyperlink ref="G10" r:id="rId29" xr:uid="{D0C2FCE6-F417-4C60-83C9-2DC27CAAEF88}"/>
+    <hyperlink ref="G11" r:id="rId30" xr:uid="{A10111A9-5855-4053-B198-5913BF6CDA09}"/>
+    <hyperlink ref="G12" r:id="rId31" xr:uid="{75F09E22-DD66-46FD-97C9-B8F6D22B9A35}"/>
+    <hyperlink ref="G13" r:id="rId32" xr:uid="{B7B8D6E5-7B8D-4C93-8C75-1F6B6DA2DD22}"/>
+    <hyperlink ref="G15" r:id="rId33" xr:uid="{EDD28860-C80B-4522-8E09-285835234F9A}"/>
+    <hyperlink ref="G18" r:id="rId34" xr:uid="{C0C61306-92A5-40FD-96B0-E931783E712C}"/>
+    <hyperlink ref="G19" r:id="rId35" xr:uid="{FC56AA1F-BABF-4ECC-9E9C-3C6DED65D859}"/>
+    <hyperlink ref="G20" r:id="rId36" xr:uid="{8121E1B0-CFF7-488B-85A1-D2969EA79341}"/>
+    <hyperlink ref="G22" r:id="rId37" xr:uid="{6381B25B-8A67-4D0E-9DDE-4264F67AC8C3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{4EB981CD-BB3E-4E18-80E2-1E124DD4C1BD}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F3</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{F6A40BF1-B9F4-45C6-8D53-103870EB4B39}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F4</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{F2D78B82-B72A-4421-874B-4CD843CDF88E}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F6:F10</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{86C0E903-4BA0-47B4-B905-76C3F67C57CE}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F11</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{0818DE56-5C48-406A-9BA9-84F492B36229}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F12</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{A4D5ADE0-6176-459A-85F6-CA1B33C513EB}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F13</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{F54F33F8-6906-4139-9934-65E447715085}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F14</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{B47EB2CE-358C-486D-A189-F0DB279E373E}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F15</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{043C1E1A-E301-4083-A263-12038E96B7B7}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F16</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{5AB8BCA4-C044-47C5-AF38-746497910378}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F17</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{9F36BD4E-26D9-4004-B4E3-EF6523A1D063}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F18</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{E7A31A38-B52D-477B-98E9-2A0CBD7F2119}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{79500CEB-4C30-43A5-96A9-4489878BC6BF}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F22:F23</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{0E5B2793-E734-42AC-9ABC-298292A3FE2F}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F24 F5</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{D8AD0291-2D57-4E56-B3D2-4CE3552BC305}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F2</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{41C1945A-74C1-4CAA-B2D4-E31D3AD9AE40}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G2</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{CDF136A3-4357-467B-B289-155FA14F29A8}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G3</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{62ED83B1-7CDB-43D8-9643-E976CF99F150}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G4</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{8ADD97A5-EC2B-4596-924A-65E0AE378C8D}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G6:G8 G10:G23</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{E7893CEF-82CD-4050-8BD2-796D578215EF}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{E79D7C0A-53D6-421E-89FD-B49CC226495F}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G5 G24</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/Dados.xlsx
+++ b/Dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/paulo_martins_tja_pt/Documents/Dep. Formação/Ambiente Formadores/Mercadona HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="8_{3ECB6CA0-9746-43FE-8E62-14652AAF4818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11F9896B-FB28-486D-9049-A020BE38341A}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="8_{3ECB6CA0-9746-43FE-8E62-14652AAF4818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8A512F7-EE28-44F7-9710-658DA35217B5}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{462C5653-B832-456D-BA7D-C78D43202BCF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{462C5653-B832-456D-BA7D-C78D43202BCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Almeirim" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="141">
   <si>
     <t>Número</t>
   </si>
@@ -432,6 +432,36 @@
   </si>
   <si>
     <t>https://maps.app.goo.gl/i2wQfR1zm89Gayky9</t>
+  </si>
+  <si>
+    <t>40.623684369720124, -8.649769935290053</t>
+  </si>
+  <si>
+    <t>Av. Europa 705, 3810-140 Aveiro</t>
+  </si>
+  <si>
+    <t>Alameda Silva Rocha 29, 3800-385 Aveiro</t>
+  </si>
+  <si>
+    <t>40.64051565879391, -8.634234342349984</t>
+  </si>
+  <si>
+    <t>Av. 25 de Abril 470, 3750-137 Águeda</t>
+  </si>
+  <si>
+    <t>40.572822537360025, -8.440088551740251</t>
+  </si>
+  <si>
+    <t>R. Emissor 447, 4400-008 Vila Nova de Gaia</t>
+  </si>
+  <si>
+    <t>41.13169573596933, -8.644948247566026</t>
+  </si>
+  <si>
+    <t>40.20630829103632, -8.401459628846217</t>
+  </si>
+  <si>
+    <t>Av. Elísio de Moura 85, Fonte da Cheira, 3030-183 Coimbra</t>
   </si>
 </sst>
 </file>
@@ -1267,7 +1297,12 @@
   <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="8" width="18.109375" customWidth="1"/>
+    <col min="1" max="1" width="18.109375" customWidth="1"/>
+    <col min="2" max="2" width="31.77734375" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" customWidth="1"/>
+    <col min="4" max="4" width="20.21875" customWidth="1"/>
+    <col min="5" max="5" width="19.77734375" customWidth="1"/>
+    <col min="6" max="8" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -1312,6 +1347,12 @@
       <c r="C2" t="s">
         <v>53</v>
       </c>
+      <c r="D2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2" t="s">
+        <v>138</v>
+      </c>
       <c r="F2" s="5" t="s">
         <v>88</v>
       </c>
@@ -1392,6 +1433,12 @@
       <c r="C6" t="s">
         <v>49</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="F6" s="6" t="s">
         <v>12</v>
       </c>
@@ -1412,6 +1459,12 @@
       <c r="C7" t="s">
         <v>61</v>
       </c>
+      <c r="D7" t="s">
+        <v>132</v>
+      </c>
+      <c r="E7" t="s">
+        <v>131</v>
+      </c>
       <c r="F7" s="5" t="s">
         <v>92</v>
       </c>
@@ -1452,6 +1505,12 @@
       <c r="C9" t="s">
         <v>61</v>
       </c>
+      <c r="D9" t="s">
+        <v>133</v>
+      </c>
+      <c r="E9" t="s">
+        <v>134</v>
+      </c>
       <c r="F9" s="5" t="s">
         <v>94</v>
       </c>
@@ -1512,6 +1571,12 @@
       <c r="C12" t="s">
         <v>69</v>
       </c>
+      <c r="D12" t="s">
+        <v>135</v>
+      </c>
+      <c r="E12" t="s">
+        <v>136</v>
+      </c>
       <c r="F12" s="6" t="s">
         <v>97</v>
       </c>
@@ -1709,6 +1774,12 @@
       </c>
       <c r="C22" t="s">
         <v>84</v>
+      </c>
+      <c r="D22" t="s">
+        <v>140</v>
+      </c>
+      <c r="E22" t="s">
+        <v>139</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>106</v>
@@ -1943,7 +2014,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F24 F5">
+  <conditionalFormatting sqref="F5 F24">
     <cfRule type="dataBar" priority="22">
       <dataBar>
         <cfvo type="min"/>
@@ -2250,7 +2321,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>F24 F5</xm:sqref>
+          <xm:sqref>F5 F24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{D8AD0291-2D57-4E56-B3D2-4CE3552BC305}">

--- a/Dados.xlsx
+++ b/Dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/paulo_martins_tja_pt/Documents/Dep. Formação/Ambiente Formadores/Mercadona HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{3ECB6CA0-9746-43FE-8E62-14652AAF4818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8A512F7-EE28-44F7-9710-658DA35217B5}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="8_{3ECB6CA0-9746-43FE-8E62-14652AAF4818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6514B761-4580-446A-AA78-2F12B78F0BF0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{462C5653-B832-456D-BA7D-C78D43202BCF}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{462C5653-B832-456D-BA7D-C78D43202BCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Almeirim" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="319">
   <si>
     <t>Número</t>
   </si>
@@ -182,18 +182,10 @@
     <t>Lima de Freitas</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1orsus1RBOw-k7LYJupf8lMFA6jYKuHXP/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>Ovar</t>
   </si>
   <si>
     <t>Notas</t>
-  </si>
-  <si>
-    <t>•  Redobrar a atenção durante a manobra, uma vez que esta é efetuada entre a estrutura dos equipamentos do “VOLTA” e os estacionamentos cobertos.
-•  A loja tem cão
-•  A gerente e boa</t>
   </si>
   <si>
     <t>Canidelo</t>
@@ -462,13 +454,553 @@
   </si>
   <si>
     <t>Av. Elísio de Moura 85, Fonte da Cheira, 3030-183 Coimbra</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/6W67XuPyYerNiP4FA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Po8HtBQSmxAau1mZA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/ww7qmiV2AUiYhGdQ6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/3dVwA3iNtDxjcf1H8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Hc5dgV5CmC2xTQtC8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/3tfrptSSLjSA1VfN7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/9FADrmNf3jjGmUNy5</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/UG1d4ZobZaecFHrQ9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Wndzab6aukW8nkfV6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/VqfDF7hiv3QsWVb49</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/nUHYCrqcTLzqE6Df9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/5WnpVkpFdriaRUYs9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/kCRr5B8WnvGTAiVj8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/hyBgp5b2cAg8TfmP9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Em231dfQAi2qbzfo7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/HGQVNp7U1gFjTqHW8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Mtkq3NFMVyEH4wWH6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/PbvZv16QoGcJR6BB8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/f3VDWjWwd4U8UHmo6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/A1e8MreGpfmMMwd8A</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/JaBT9UqK2D68DM5v7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/dc9Fx1QDbHuNokVNA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/3w51VKTEot8guvD47</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/JopC2GaPoZ9yPZXr5</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/LZmvyoVUENCLWWc58</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/R5NUuES3VKNhcJwWA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/RV29onyJYwox5gbm9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/ukfb5awbkSnGanwx5</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/4LFkhjuANYxEbpNq6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/LVxL6pAoDNNosL927</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/67a2Rba3fbS9NJs66</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/kEZu4s2ZgJR4LzLV9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/vi6teqNJpnjgeEPS8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/V5MvtQCsjT8S54hk6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/txhaaNiZeoUYj7w4A</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/BXFdBmmeAYJ2jZXT6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/6QYPGV7Gjas7rf4a7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/mVarCwbbsTe6MXJ68</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/GziCMFcH6KrsweQg6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/QFthhVzyrDpbxcoU9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/LAFLf1X5cYTQurxL8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/hYpXMBgx28ZFnhaj9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/13txGFnB76nKBpgdA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/PyCfrhEb9TabQ7Xb6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/kBCDYfSJHNC8LEfL6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/4C2JjGDaAZqbbWYt6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/7FUYWek4mYVjHCjZ9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/r6PdNrN48C6frbtk6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/dYPbrSccZy4ysBUZA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/8jQThgbcGB5QVxeT9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/FcSMwHQk582TiZtq7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/CKJMRojJxR8VMSR67</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/3dtpMfdWyfc2KpPP8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/dVqLATccwzkQsUqh9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/tyzFRJM5UvMqqUtw6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/5rcuY2Lso4LJEG8U7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/6dKqr2dhrnbRx8Hf7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/86V86ybKjuFkvEyG7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/ShxUt89nsG4mSeK26</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/RHWtD45Mz4KDhakXA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/J7LuKtXyTTqu2V6E7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/aFeeF29sZeGBfWtF7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/mbhzF2c6dZgs9PHXA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/ShTyqfgazatM8Rm17</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/v13A7srdRQbLLFkC6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/rAqJMdDfXgirQTKH8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/CHUyN8H4MjvxdgjS6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/jNGxwst4zYnWZfQ19</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/reBMJKb8LmVrJF5V7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/wXBRsEdJS3Biqj9V9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/aFPAxFsob2Ler5KS8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/RhDnJNWf38dT2T359</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/9dAP2pVCEssXNLNu6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/xFmXcTx5wnzcKRjo6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Rg8BYySj4jz4zZXQ8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/XSH3kP7KpQZVeJwM7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/wPcq1iAAKgLYbmCV7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Gh4AjP4RY3mPizQXA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/AEg6WubCofb35Er19</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/ZMbe8qhb1NCyWow58</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/uZtvm1gvpwQBEDcPA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Zz6zTNCA6HQJRaQy6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/8yftzzRJwkr5VaHj8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/qroz9FAaJdDsReAt6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/T5QzMGQhbS8bhxGh8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/YGeV1Qs8cXPeA7Q46</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/zqacxvxttfUkwQ5j9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/5U6tTtfAfbrgyaDE7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/TgH4d4bYtBowveY98</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/cUTgiadgXmvWwhnp9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/1mGQBsEAhPyncthd8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/YvnHZnBwfpfJxDnu7</t>
+  </si>
+  <si>
+    <t>MATOSINHOS - SOUSA AROSO</t>
+  </si>
+  <si>
+    <t>Barcelos</t>
+  </si>
+  <si>
+    <t>Maia</t>
+  </si>
+  <si>
+    <t>BRAGA - LAMAÇAES</t>
+  </si>
+  <si>
+    <t>PENAFIEL</t>
+  </si>
+  <si>
+    <t>SILVARES - GUIMARAES</t>
+  </si>
+  <si>
+    <t>URGEZES (GUIMARÃES)</t>
+  </si>
+  <si>
+    <t>Santo Tirso Arco Texteis</t>
+  </si>
+  <si>
+    <t>VILA DO CONDE</t>
+  </si>
+  <si>
+    <t>ERMESINDE</t>
+  </si>
+  <si>
+    <t>VIANA DO CASTELO - ABELHEIRA</t>
+  </si>
+  <si>
+    <t>TROFA</t>
+  </si>
+  <si>
+    <t>VALONGO-OLIVEIRA ZINA</t>
+  </si>
+  <si>
+    <t>FAMALICÃO - ESTÁDIO</t>
+  </si>
+  <si>
+    <t>BRAGA II - Independencia</t>
+  </si>
+  <si>
+    <t>RUA DAS ICAS - (EXPONOR)</t>
+  </si>
+  <si>
+    <t>PAÇOS FERREIRA</t>
+  </si>
+  <si>
+    <t>PÓVOA DE VARZIM</t>
+  </si>
+  <si>
+    <t>FELGUEIRAS</t>
+  </si>
+  <si>
+    <t>Vila Real</t>
+  </si>
+  <si>
+    <t>BRAGA II - Quinta Stª Barbara</t>
+  </si>
+  <si>
+    <t>MARCO DE CANAVESES</t>
+  </si>
+  <si>
+    <t>LOUSADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rua de São Gens </t>
+  </si>
+  <si>
+    <t>CANELAS VNG</t>
+  </si>
+  <si>
+    <t>FAFE</t>
+  </si>
+  <si>
+    <t>Moreira da Maia</t>
+  </si>
+  <si>
+    <t>PENAFIEL - MILHUNDOS</t>
+  </si>
+  <si>
+    <t>Matosinhos</t>
+  </si>
+  <si>
+    <t>Braga</t>
+  </si>
+  <si>
+    <t>Penafiel</t>
+  </si>
+  <si>
+    <t>Guimaraes</t>
+  </si>
+  <si>
+    <t>Guimarães</t>
+  </si>
+  <si>
+    <t>Santo Tirso</t>
+  </si>
+  <si>
+    <t>Vila do Conde</t>
+  </si>
+  <si>
+    <t>Ermesinde</t>
+  </si>
+  <si>
+    <t>Viana do Castelo</t>
+  </si>
+  <si>
+    <t>Trofa</t>
+  </si>
+  <si>
+    <t>Valongo</t>
+  </si>
+  <si>
+    <t>Famalicão</t>
+  </si>
+  <si>
+    <t>Leça da Palmeira</t>
+  </si>
+  <si>
+    <t>Paços Ferreira</t>
+  </si>
+  <si>
+    <t>Póvoa de Varzim</t>
+  </si>
+  <si>
+    <t>Felgueiras</t>
+  </si>
+  <si>
+    <t>Marco de Canavezes</t>
+  </si>
+  <si>
+    <t>Lousada</t>
+  </si>
+  <si>
+    <t>Fafe</t>
+  </si>
+  <si>
+    <t>https://goo.gl/maps/nuhAmPRXu1NL34ZQA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/oQAYVhmtxNVKUWjp7</t>
+  </si>
+  <si>
+    <t>https://goo.gl/maps/8qJtKJJztSScvav66</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/oJB2URdShKFkyXii7</t>
+  </si>
+  <si>
+    <t>Directo à loja - desliga motor de Frío na loja</t>
+  </si>
+  <si>
+    <t>https://goo.gl/maps/3cY6CdSLivSwLvJ97</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/CEP2M49LfLfAedC29</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/AUUxsix1vrZJq6wT8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/XrhXZxEWZtcJwZFp6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/8h1uhqizAUBbAkAQ8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/gqiJEfvKdyS8S8VZ7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/r4JcHroaHCfHeCzR8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/AX5eLKqutQu8PbfV7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/xpYsTYaHqQZPoxrH8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/DamK2p292amLCpfP8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/nf7bp3BfKsW2znqF6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/TMZy3wjumLx1PJmX6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Er16VT28pTz4YDAr6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/CLzwJ1DvDPUDsYzY8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/bn4ie9ATR3FRbApCA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/QsxxjtDJEXppeSKm8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/KU5QDw1CmtXkERmr8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/PPF19bgxXazyHsbFA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/RSyRt3o22J3tUkdTA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/oiHbmuKyGYdczRGWA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Toyb9rDQ31AZ1yJo9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/a71TQ666A8tgwWT89</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/mhYU2i64hSk3JKpG6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/cp1rJrnXFRRGMUgq9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/ZUGtwrMvX2cgPnvX7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/V1JjjfA6E5uGDnUs9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/KZNDXeQF5tmkTDL28</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/w1f9kfrpsgT3Ln7WA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/szVhmi5DYyvmmLKBA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/MV8cDeAGLZrkmYKb9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/kj7zKURqcsDCNaN19</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Gr6zupSN5gjzC9pC9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/MXeoEP5L5PrxVaN58</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/kcymxiQy1n8K22rP6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/S6FBbvg4ApXgs9Mp6</t>
+  </si>
+  <si>
+    <t>211 202 950</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -489,6 +1021,32 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -517,7 +1075,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -555,13 +1113,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -579,22 +1150,73 @@
     <xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -913,17 +1535,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FD30D99-73F2-4328-8D2B-7F8242E8530C}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" style="1" customWidth="1"/>
-    <col min="2" max="3" width="18.5546875" customWidth="1"/>
+    <col min="2" max="2" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" customWidth="1"/>
     <col min="4" max="4" width="33.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="36.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="40.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="39.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="39.6640625" customWidth="1"/>
-    <col min="9" max="11" width="18.5546875" customWidth="1"/>
+    <col min="9" max="9" width="18.5546875" style="23" customWidth="1"/>
+    <col min="10" max="11" width="18.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -949,9 +1573,9 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" s="23" t="s">
         <v>7</v>
       </c>
       <c r="J1" t="s">
@@ -961,878 +1585,1018 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
+        <v>7000</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="23">
+        <v>221201095</v>
+      </c>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>7002</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I3" s="23">
+        <v>221201094</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>7003</v>
+      </c>
+      <c r="B4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="I4" s="23">
+        <v>221205059</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>7008</v>
+      </c>
+      <c r="B5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I5" s="23">
+        <v>221205056</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
         <v>7009</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I2" s="1">
-        <v>221205057</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="B6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>7033</v>
-      </c>
-      <c r="B3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I3">
-        <v>265121501</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>7036</v>
-      </c>
-      <c r="B4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" t="s">
-        <v>44</v>
-      </c>
-      <c r="I4">
-        <v>211202941</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>7041</v>
-      </c>
-      <c r="B5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5">
-        <v>211202943</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>7044</v>
-      </c>
-      <c r="B6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I6">
-        <v>211202942</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>7046</v>
-      </c>
-      <c r="B7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7">
-        <v>243120160</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>7048</v>
-      </c>
-      <c r="B8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I8">
-        <v>211202946</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <v>7049</v>
-      </c>
-      <c r="B9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I9">
-        <v>262130010</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <v>7054</v>
-      </c>
-      <c r="B10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I10">
-        <v>211202945</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
-        <v>7055</v>
-      </c>
-      <c r="B11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" t="s">
-        <v>34</v>
-      </c>
-      <c r="I11">
-        <v>261133001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
-        <v>7057</v>
-      </c>
-      <c r="B12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12">
-        <v>211202951</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
-        <v>7058</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13">
-        <v>263137011</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
-        <v>7060</v>
-      </c>
-      <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14">
-        <v>266127951</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
-        <v>7061</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" t="s">
-        <v>28</v>
-      </c>
-      <c r="I15">
-        <v>265121502</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
-        <v>7068</v>
-      </c>
-      <c r="B16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" t="s">
-        <v>26</v>
-      </c>
-      <c r="I16">
-        <v>211202947</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
-        <v>7069</v>
-      </c>
-      <c r="B17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" t="s">
-        <v>18</v>
-      </c>
-      <c r="I17">
-        <v>244122590</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
-        <v>7073</v>
-      </c>
-      <c r="B18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" t="s">
-        <v>24</v>
-      </c>
-      <c r="I18">
-        <v>910759388</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
-        <v>7076</v>
-      </c>
-      <c r="B19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
-        <v>7079</v>
-      </c>
-      <c r="B20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" t="s">
-        <v>20</v>
-      </c>
-      <c r="I20">
-        <v>211202948</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
-        <v>7082</v>
-      </c>
-      <c r="B21" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" t="s">
-        <v>18</v>
-      </c>
-      <c r="I21">
-        <v>244122591</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
-        <v>7084</v>
-      </c>
-      <c r="B22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22">
-        <v>211202950</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
-        <v>7088</v>
-      </c>
-      <c r="B23" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{8CA04C4B-F07B-4B05-AB3C-9B23CB7EE39B}"/>
-    <hyperlink ref="G2" r:id="rId2" xr:uid="{2833A35E-D69B-4DC0-805F-E2CFC8F15A64}"/>
-    <hyperlink ref="J2" r:id="rId3" xr:uid="{00851908-A944-44AE-8A1A-8F624846C0C0}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF5F13FE-4E63-48A0-84FC-D9B1FB307CA9}">
-  <dimension ref="A1:J24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18.109375" customWidth="1"/>
-    <col min="2" max="2" width="31.77734375" customWidth="1"/>
-    <col min="3" max="3" width="18.109375" customWidth="1"/>
-    <col min="4" max="4" width="20.21875" customWidth="1"/>
-    <col min="5" max="5" width="19.77734375" customWidth="1"/>
-    <col min="6" max="8" width="18.109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>7000</v>
-      </c>
-      <c r="B2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="H2">
-        <v>221201095</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>7002</v>
-      </c>
-      <c r="B3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="H3">
-        <v>221201094</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>7003</v>
-      </c>
-      <c r="B4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="H4">
-        <v>221205059</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>7008</v>
-      </c>
-      <c r="B5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="H5">
-        <v>221205056</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>7009</v>
-      </c>
-      <c r="B6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="16" t="s">
         <v>12</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="23">
         <v>221205057</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7">
+    <row r="7" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
         <v>7013</v>
       </c>
       <c r="B7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I7" s="23">
+        <v>256120000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>7015</v>
+      </c>
+      <c r="B8" t="s">
         <v>60</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>61</v>
       </c>
-      <c r="D7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E7" t="s">
-        <v>131</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="F8" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="I8" s="23">
+        <v>221205058</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>7017</v>
+      </c>
+      <c r="B9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="H7">
-        <v>256120000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7015</v>
-      </c>
-      <c r="B8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="I9" s="23">
+        <v>256120002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>7020</v>
+      </c>
+      <c r="B10" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G10" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="H8">
-        <v>221205058</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>7017</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="I10" s="23">
+        <v>221202915</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>7022</v>
+      </c>
+      <c r="B11" t="s">
         <v>64</v>
       </c>
-      <c r="C9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" t="s">
-        <v>133</v>
-      </c>
-      <c r="E9" t="s">
-        <v>134</v>
-      </c>
-      <c r="F9" s="5" t="s">
+      <c r="C11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G11" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="H9">
-        <v>256120002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>7020</v>
-      </c>
-      <c r="B10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" t="s">
-        <v>58</v>
-      </c>
-      <c r="F10" s="6" t="s">
+      <c r="I11" s="23">
+        <v>256120004</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>7023</v>
+      </c>
+      <c r="B12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G12" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="H10">
-        <v>221202915</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>7022</v>
-      </c>
-      <c r="B11" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" t="s">
-        <v>67</v>
-      </c>
-      <c r="F11" s="5" t="s">
+      <c r="I12" s="23">
+        <v>256120003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>7029</v>
+      </c>
+      <c r="B13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" s="15"/>
+      <c r="G13" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I13" s="23">
+        <v>221202919</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>7031</v>
+      </c>
+      <c r="B14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="H11">
-        <v>256120004</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>7023</v>
-      </c>
-      <c r="B12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D12" t="s">
-        <v>135</v>
-      </c>
-      <c r="E12" t="s">
-        <v>136</v>
-      </c>
-      <c r="F12" s="6" t="s">
+      <c r="G14" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="I14" s="23">
+        <v>256120250</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>7034</v>
+      </c>
+      <c r="B15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="H12">
-        <v>256120003</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>7029</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5" t="s">
+      <c r="G15" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="H13">
-        <v>221202919</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>7031</v>
-      </c>
-      <c r="B14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="I15" s="23">
+        <v>221202922</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>7037</v>
+      </c>
+      <c r="B16" t="s">
         <v>72</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="C16" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G16" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="H14">
-        <v>256120250</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>7034</v>
-      </c>
-      <c r="B15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F15" s="5" t="s">
+      <c r="I16" s="23">
+        <v>256120252</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>7038</v>
+      </c>
+      <c r="B17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G17" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="H15">
-        <v>221202922</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>7037</v>
-      </c>
-      <c r="B16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" s="10" t="s">
+      <c r="I17" s="23">
+        <v>233120010</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>7040</v>
+      </c>
+      <c r="B18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G18" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="H16">
-        <v>256120252</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>7038</v>
-      </c>
-      <c r="B17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" t="s">
-        <v>77</v>
-      </c>
-      <c r="F17" s="11" t="s">
+      <c r="I18" s="23">
+        <v>232120210</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>7045</v>
+      </c>
+      <c r="B19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G19" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="H17">
-        <v>233120010</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>7040</v>
-      </c>
-      <c r="B18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" t="s">
-        <v>79</v>
-      </c>
-      <c r="F18" s="6" t="s">
+      <c r="I19" s="23">
+        <v>256120251</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>7056</v>
+      </c>
+      <c r="B20" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G20" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="H18">
-        <v>232120210</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>7045</v>
-      </c>
-      <c r="B19" t="s">
-        <v>80</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="I20" s="23">
+        <v>221202923</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>7066</v>
+      </c>
+      <c r="B21" t="s">
         <v>81</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="C21" t="s">
+        <v>82</v>
+      </c>
+      <c r="F21" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G21" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="H19">
-        <v>256120251</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>7056</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="I21" s="23">
+        <v>239127942</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>7064</v>
+      </c>
+      <c r="B22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" t="s">
         <v>82</v>
       </c>
-      <c r="C20" t="s">
-        <v>53</v>
-      </c>
-      <c r="F20" s="10" t="s">
+      <c r="F22" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G22" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="H20">
-        <v>221202923</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>7066</v>
-      </c>
-      <c r="B21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="I22" s="23">
+        <v>239127941</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>7067</v>
+      </c>
+      <c r="B23" t="s">
         <v>84</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="C23" t="s">
+        <v>84</v>
+      </c>
+      <c r="F23" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G23" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="H21">
-        <v>239127942</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>7064</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="I23" s="23">
+        <v>271127941</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>7078</v>
+      </c>
+      <c r="B24" t="s">
         <v>85</v>
       </c>
-      <c r="C22" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" t="s">
-        <v>140</v>
-      </c>
-      <c r="E22" t="s">
-        <v>139</v>
-      </c>
-      <c r="F22" s="6" t="s">
+      <c r="C24" t="s">
+        <v>56</v>
+      </c>
+      <c r="F24" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G24" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="H22">
-        <v>239127941</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>7067</v>
-      </c>
-      <c r="B23" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" t="s">
-        <v>86</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="H23">
-        <v>271127941</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>7078</v>
-      </c>
-      <c r="B24" t="s">
-        <v>87</v>
-      </c>
-      <c r="C24" t="s">
-        <v>58</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="H24">
+      <c r="I24" s="23">
         <v>221201005</v>
       </c>
     </row>
+    <row r="25" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>7033</v>
+      </c>
+      <c r="B25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" t="s">
+        <v>46</v>
+      </c>
+      <c r="F25" s="24" t="s">
+        <v>278</v>
+      </c>
+      <c r="G25" s="24" t="s">
+        <v>298</v>
+      </c>
+      <c r="I25" s="23">
+        <v>265121501</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>7036</v>
+      </c>
+      <c r="B26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" t="s">
+        <v>44</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="G26" s="26" t="s">
+        <v>299</v>
+      </c>
+      <c r="I26" s="23">
+        <v>211202941</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>7041</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" s="25" t="s">
+        <v>280</v>
+      </c>
+      <c r="G27" s="24" t="s">
+        <v>300</v>
+      </c>
+      <c r="I27" s="23">
+        <v>211202943</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>7044</v>
+      </c>
+      <c r="B28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" t="s">
+        <v>35</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>281</v>
+      </c>
+      <c r="G28" s="26" t="s">
+        <v>301</v>
+      </c>
+      <c r="I28" s="23">
+        <v>211202942</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>7046</v>
+      </c>
+      <c r="B29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" t="s">
+        <v>39</v>
+      </c>
+      <c r="F29" s="25" t="s">
+        <v>282</v>
+      </c>
+      <c r="G29" s="24" t="s">
+        <v>302</v>
+      </c>
+      <c r="I29" s="23">
+        <v>243120160</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>7048</v>
+      </c>
+      <c r="B30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" t="s">
+        <v>35</v>
+      </c>
+      <c r="F30" s="26" t="s">
+        <v>283</v>
+      </c>
+      <c r="G30" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="I30" s="23">
+        <v>211202946</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>7049</v>
+      </c>
+      <c r="B31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" t="s">
+        <v>37</v>
+      </c>
+      <c r="F31" s="24" t="s">
+        <v>284</v>
+      </c>
+      <c r="G31" s="24" t="s">
+        <v>304</v>
+      </c>
+      <c r="I31" s="23">
+        <v>262130010</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>7054</v>
+      </c>
+      <c r="B32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" t="s">
+        <v>35</v>
+      </c>
+      <c r="F32" s="26" t="s">
+        <v>285</v>
+      </c>
+      <c r="G32" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="I32" s="23">
+        <v>211202945</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>7055</v>
+      </c>
+      <c r="B33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" t="s">
+        <v>34</v>
+      </c>
+      <c r="F33" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="G33" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="I33" s="23">
+        <v>261133001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>7057</v>
+      </c>
+      <c r="B34" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="G34" s="26" t="s">
+        <v>307</v>
+      </c>
+      <c r="I34" s="23">
+        <v>211202951</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>7058</v>
+      </c>
+      <c r="B35" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" t="s">
+        <v>31</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="G35" s="24" t="s">
+        <v>308</v>
+      </c>
+      <c r="I35" s="23">
+        <v>263137011</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>7060</v>
+      </c>
+      <c r="B36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" t="s">
+        <v>30</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="G36" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="I36" s="23">
+        <v>266127951</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>7061</v>
+      </c>
+      <c r="B37" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" t="s">
+        <v>28</v>
+      </c>
+      <c r="F37" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="G37" s="24" t="s">
+        <v>310</v>
+      </c>
+      <c r="I37" s="23">
+        <v>265121502</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>7068</v>
+      </c>
+      <c r="B38" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" t="s">
+        <v>26</v>
+      </c>
+      <c r="F38" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="G38" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="I38" s="23">
+        <v>211202947</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>7069</v>
+      </c>
+      <c r="B39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="G39" s="24" t="s">
+        <v>312</v>
+      </c>
+      <c r="I39" s="23">
+        <v>244122590</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>7073</v>
+      </c>
+      <c r="B40" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" t="s">
+        <v>24</v>
+      </c>
+      <c r="F40" s="27" t="s">
+        <v>293</v>
+      </c>
+      <c r="G40" s="26" t="s">
+        <v>313</v>
+      </c>
+      <c r="I40" s="23">
+        <v>910759388</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>7076</v>
+      </c>
+      <c r="B41" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" t="s">
+        <v>22</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>7079</v>
+      </c>
+      <c r="B42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C42" t="s">
+        <v>20</v>
+      </c>
+      <c r="F42" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="G42" s="26" t="s">
+        <v>315</v>
+      </c>
+      <c r="I42" s="23">
+        <v>211202948</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>7082</v>
+      </c>
+      <c r="B43" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" t="s">
+        <v>18</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="I43" s="23">
+        <v>244122591</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>7084</v>
+      </c>
+      <c r="B44" t="s">
+        <v>17</v>
+      </c>
+      <c r="C44" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="G44" s="29" t="s">
+        <v>317</v>
+      </c>
+      <c r="I44" s="23" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>7088</v>
+      </c>
+      <c r="B45" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" t="s">
+        <v>14</v>
+      </c>
+      <c r="F45" s="28"/>
+      <c r="G45" s="24"/>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="F2">
+    <cfRule type="dataBar" priority="33">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{30FB49D0-576F-484A-9F04-F762F69B2151}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F3">
+    <cfRule type="dataBar" priority="32">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{755BD77B-8CC4-44FC-BA03-787B988F6015}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="dataBar" priority="31">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{40FC922F-FA9C-4D3B-8263-77C3E6A8432D}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6:F10">
+    <cfRule type="dataBar" priority="30">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{6E1206DF-6DEB-4E04-8F31-0757049B7953}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F11">
+    <cfRule type="dataBar" priority="27">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{2E030C97-BB3C-4CF7-9B70-C9814F9D0EF6}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="dataBar" priority="28">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{DD305FE1-D086-4E0E-89C1-0C7E85D65DC8}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F13">
+    <cfRule type="dataBar" priority="26">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{B9AA7D27-186B-4161-94E5-C5AEE1281ABF}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14">
+    <cfRule type="dataBar" priority="25">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{0544B7F7-CF4F-4F07-A689-AB7D33CC8C32}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
+    <cfRule type="dataBar" priority="29">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{670BF0A7-01F3-4D70-90D9-AE6DF983C372}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F16">
+    <cfRule type="dataBar" priority="22">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{65C34C26-3515-4418-BBE5-4ABB4918FA10}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17">
     <cfRule type="dataBar" priority="20">
       <dataBar>
         <cfvo type="min"/>
@@ -1841,12 +2605,138 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4EB981CD-BB3E-4E18-80E2-1E124DD4C1BD}</x14:id>
+          <x14:id>{1B231A9C-893F-4E93-9C5B-C0DB43F1A147}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
+  <conditionalFormatting sqref="F18">
+    <cfRule type="dataBar" priority="23">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{DD447D69-353A-452A-BE80-2E9AD1AE239D}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="dataBar" priority="24">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{A55A45F4-B920-48DC-979D-A23CFD2E5C94}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F23">
+    <cfRule type="dataBar" priority="21">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{8DF9DF4E-6BFF-407F-861A-9AF060F1D43E}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24 F5">
+    <cfRule type="dataBar" priority="34">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{3A9CB92F-0E10-4058-8028-650674652E6E}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2">
+    <cfRule type="dataBar" priority="18">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{39E40594-1983-4307-8FCC-CD695BAE4F9D}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="dataBar" priority="17">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{1C2AE5ED-0584-4F6C-9461-A25DDC6E5B4C}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4">
+    <cfRule type="dataBar" priority="16">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{100D9A8C-9878-42B4-9125-55F4698B2A77}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6:G8 G10:G23">
+    <cfRule type="dataBar" priority="15">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{FD6A10F4-AAFE-4C96-B132-41ADE092E178}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G9">
+    <cfRule type="dataBar" priority="14">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{8C76355E-2D6D-40AF-ABE4-E00AFEA5067D}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5 G24">
     <cfRule type="dataBar" priority="19">
       <dataBar>
         <cfvo type="min"/>
@@ -1855,13 +2745,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{F6A40BF1-B9F4-45C6-8D53-103870EB4B39}</x14:id>
+          <x14:id>{75CD4E91-DDF8-4F36-9EFD-977D50110370}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6:F10">
-    <cfRule type="dataBar" priority="18">
+  <conditionalFormatting sqref="F25">
+    <cfRule type="dataBar" priority="8">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -1869,13 +2759,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{F2D78B82-B72A-4421-874B-4CD843CDF88E}</x14:id>
+          <x14:id>{664D1B66-6622-4592-94D2-639F27A1F1AD}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F11">
-    <cfRule type="dataBar" priority="15">
+  <conditionalFormatting sqref="F26">
+    <cfRule type="dataBar" priority="9">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -1883,13 +2773,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{86C0E903-4BA0-47B4-B905-76C3F67C57CE}</x14:id>
+          <x14:id>{A729F339-7E62-4DAA-87FF-C47EC2017AA4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
-    <cfRule type="dataBar" priority="16">
+  <conditionalFormatting sqref="F27">
+    <cfRule type="dataBar" priority="10">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -1897,13 +2787,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0818DE56-5C48-406A-9BA9-84F492B36229}</x14:id>
+          <x14:id>{14176752-41FA-4408-B48B-8FAD9181A2B0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F13">
-    <cfRule type="dataBar" priority="14">
+  <conditionalFormatting sqref="F28">
+    <cfRule type="dataBar" priority="11">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -1911,12 +2801,54 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{A4D5ADE0-6176-459A-85F6-CA1B33C513EB}</x14:id>
+          <x14:id>{DAD877A4-AFA8-4B89-887E-3C22D3BC592C}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
+  <conditionalFormatting sqref="F31">
+    <cfRule type="dataBar" priority="12">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{71894A45-03F3-4503-8BC0-DB7B706128A2}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F43">
+    <cfRule type="dataBar" priority="5">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{AFA383BA-BA2E-4063-95A7-349BC308FC0D}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F44">
+    <cfRule type="dataBar" priority="7">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{0D3C0B7F-90B5-40CB-95EA-07EAD79DDADF}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F44:F45 F25:F42">
     <cfRule type="dataBar" priority="13">
       <dataBar>
         <cfvo type="min"/>
@@ -1925,13 +2857,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{F54F33F8-6906-4139-9934-65E447715085}</x14:id>
+          <x14:id>{65BD2DCD-8E5D-481E-A632-21B990203C2D}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
-    <cfRule type="dataBar" priority="17">
+  <conditionalFormatting sqref="F45">
+    <cfRule type="dataBar" priority="6">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -1939,13 +2871,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{B47EB2CE-358C-486D-A189-F0DB279E373E}</x14:id>
+          <x14:id>{9555C3D9-BB94-4209-9E97-FF27BD0AD1F8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F16">
-    <cfRule type="dataBar" priority="10">
+  <conditionalFormatting sqref="G43">
+    <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -1953,13 +2885,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{043C1E1A-E301-4083-A263-12038E96B7B7}</x14:id>
+          <x14:id>{3F0C9A87-E1FE-4BBD-9709-FACAE2BEA80A}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F17">
-    <cfRule type="dataBar" priority="8">
+  <conditionalFormatting sqref="G44">
+    <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -1967,96 +2899,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5AB8BCA4-C044-47C5-AF38-746497910378}</x14:id>
+          <x14:id>{6CBA4C1D-548E-4347-B9E1-D5B16DE7B84A}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F18">
-    <cfRule type="dataBar" priority="11">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9F36BD4E-26D9-4004-B4E3-EF6523A1D063}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="dataBar" priority="12">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{E7A31A38-B52D-477B-98E9-2A0CBD7F2119}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F22:F23">
-    <cfRule type="dataBar" priority="9">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{79500CEB-4C30-43A5-96A9-4489878BC6BF}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5 F24">
-    <cfRule type="dataBar" priority="22">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0E5B2793-E734-42AC-9ABC-298292A3FE2F}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
-    <cfRule type="dataBar" priority="7">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D8AD0291-2D57-4E56-B3D2-4CE3552BC305}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2">
-    <cfRule type="dataBar" priority="5">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{41C1945A-74C1-4CAA-B2D4-E31D3AD9AE40}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
+  <conditionalFormatting sqref="G44:G45 G25:G42">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
@@ -2065,26 +2913,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{CDF136A3-4357-467B-B289-155FA14F29A8}</x14:id>
+          <x14:id>{4F3ABC73-5AAD-49D7-8A56-2BA2BC10DABA}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4">
-    <cfRule type="dataBar" priority="3">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{62ED83B1-7CDB-43D8-9643-E976CF99F150}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6:G8 G10:G23">
+  <conditionalFormatting sqref="G45">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -2093,84 +2927,102 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8ADD97A5-EC2B-4596-924A-65E0AE378C8D}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G9">
-    <cfRule type="dataBar" priority="1">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{E7893CEF-82CD-4050-8BD2-796D578215EF}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G5 G24">
-    <cfRule type="dataBar" priority="6">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{E79D7C0A-53D6-421E-89FD-B49CC226495F}</x14:id>
+          <x14:id>{4CED1CF9-2405-406A-BEB7-9F6DBD8E1CC5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="https://www.google.com/maps/place/41%C2%B007'32.7%22N+8%C2%B038'15.3%22W/@41.1257397,-8.641813,17z/data=!3m1!4b1!4m13!1m8!3m7!1s0xd2465605bb840af:0x500ebbde4904a60!2sCanidelo,+Vila+Nova+de+Gaia,+Portugal!3b1!8m2!3d41.1233052!4d-8.6461724!16s%2Fm%2F03cmkjx!3m3!8m2!3d41.125736!4d-8.637575" xr:uid="{19AA09C0-BB00-42C9-AE9F-80BEF3B7895A}"/>
-    <hyperlink ref="F3" r:id="rId2" display="https://www.google.com/maps/place/Galp/@41.2000023,-8.5840168,15z/data=!4m10!1m2!2m1!1sarea+de+servi%C3%A7o+A4!3m6!1s0xd2463fdd2d14787:0xe54397b5855d8659!8m2!3d41.2000023!4d-8.5665073!15sChNhcmVhIGRlIHNlcnZpw6dvIEE0WhUiE2FyZWEgZGUgc2VydmnDp28gYTSSAQtnYXNfc3RhdGlvbpoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VRdGJWbHFRbkJCUlJBQuABAA!16s%2Fg%2F11b6glyzq3" xr:uid="{F86785E8-34B2-4417-84E1-61BFB52D3D78}"/>
-    <hyperlink ref="F4" r:id="rId3" xr:uid="{838A2B0E-F885-4894-B5F3-4562C7D493FD}"/>
-    <hyperlink ref="F5" r:id="rId4" xr:uid="{5A2D1402-EC3A-4047-929C-77A025AFD230}"/>
-    <hyperlink ref="F10" r:id="rId5" xr:uid="{B3433C29-4165-41B9-A0CA-911FAB0647B9}"/>
-    <hyperlink ref="F14" r:id="rId6" xr:uid="{61644480-88F4-4245-9FD6-FB736A24EEDA}"/>
-    <hyperlink ref="F19" r:id="rId7" xr:uid="{75B85A1E-4AC0-458F-A4A2-73E1AD786CBC}"/>
-    <hyperlink ref="F11" r:id="rId8" display="https://www.google.com/maps/place/41%C2%B001'32.5%22N+8%C2%B037'15.2%22W/@41.025699,-8.625366,17z/data=!3m1!4b1!4m13!1m8!3m7!1s0xd2479c7cd31a89b:0x73c82fb2f5e003f8!2sEspinho,+Portugal!3b1!8m2!3d41.0071914!4d-8.6410332!16zL20vMDNqMGs4!3m3!8m2!3d41.025695!4d-8.620876" xr:uid="{86B1731B-A1BC-44D9-AF65-177B78EE1519}"/>
-    <hyperlink ref="F15" r:id="rId9" xr:uid="{CD632606-9DD9-499B-8810-62FF547D7F43}"/>
-    <hyperlink ref="F12" r:id="rId10" xr:uid="{3F6652BF-D6A6-4834-A146-7A5E512DF694}"/>
-    <hyperlink ref="F20" r:id="rId11" display="https://www.google.com/maps/@41.0845386,-8.6187478,3a,75y,110.4h,90t/data=!3m7!1e1!3m5!1sLIYhBDg9FYzt7FcbWR5jZw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D0%26panoid%3DLIYhBDg9FYzt7FcbWR5jZw%26yaw%3D110.4041920217924!7i16384!8i8192?coh=205410&amp;entry=ttu&amp;g_ep=EgoyMDI0MDkyOS4wIKXMDSoASAFQAw%3D%3D" xr:uid="{78DCE02D-F81E-4277-8541-DF7E4C63A6AB}"/>
-    <hyperlink ref="F18" r:id="rId12" display="https://www.google.com/maps/place/Repsol+A25+Viseu+(sul)/@40.623534,-7.930495,17z/data=!4m14!1m7!3m6!1s0xd233706899600ed:0xb5ac567012a36aae!2sMercadona+Viseu!8m2!3d40.6326254!4d-7.9091179!16s%2Fg%2F11s2j25vhc!3m5!1s0xd23373e65fbfa6b:0x2354da54d5b13e37!8m2!3d40.623897!4d-7.933134!16s%2Fg%2F11bvcvn15h" xr:uid="{28578BE6-12BA-471E-82A5-111560DDD170}"/>
-    <hyperlink ref="F16" r:id="rId13" xr:uid="{F3F1B3D6-9528-400B-A5EF-C13DAA7D9EC5}"/>
-    <hyperlink ref="F6" r:id="rId14" xr:uid="{3388296C-9D48-4FF4-B58A-DE5A140E079B}"/>
-    <hyperlink ref="F7" r:id="rId15" xr:uid="{8FC35D1F-A3C7-4358-8AAD-5860E6019C11}"/>
-    <hyperlink ref="F9" r:id="rId16" xr:uid="{E7BD4AE1-B61A-46F1-AFDB-0BF749B2ED5A}"/>
-    <hyperlink ref="F17" r:id="rId17" xr:uid="{C36926B3-A65D-4FBC-8CD1-3ABCB11B2249}"/>
-    <hyperlink ref="F22" r:id="rId18" xr:uid="{2B4606B0-9891-4753-B802-CC966A8967EF}"/>
-    <hyperlink ref="F21" r:id="rId19" xr:uid="{B0FAADD4-EB10-4006-B700-2D489F41EA04}"/>
-    <hyperlink ref="F23" r:id="rId20" xr:uid="{25D72EC1-2EA4-460E-9D82-5274BBF4749A}"/>
-    <hyperlink ref="G5" r:id="rId21" xr:uid="{5ACD7D42-12EC-4DCA-84F2-4946F1A38CA5}"/>
-    <hyperlink ref="G21" r:id="rId22" xr:uid="{8B6F81C5-3270-45FF-BFF0-A7842E5DBDE2}"/>
-    <hyperlink ref="G7" r:id="rId23" xr:uid="{E184D786-EE4A-4781-9824-6F7D8B49FBDE}"/>
-    <hyperlink ref="G8" r:id="rId24" xr:uid="{B5C9E3E7-1402-4252-AE1E-7F4334F8AFA5}"/>
-    <hyperlink ref="G17" r:id="rId25" xr:uid="{25551BDD-0E8C-4577-BD45-AFEE5369E426}"/>
-    <hyperlink ref="G23" r:id="rId26" xr:uid="{4E92188D-DED9-4E9C-B6CA-68CDDDB2368E}"/>
-    <hyperlink ref="G6" r:id="rId27" xr:uid="{0790B85E-9275-47F2-9806-967353FEA854}"/>
-    <hyperlink ref="G9" r:id="rId28" xr:uid="{9A4168A3-3351-452B-96D0-F46764C7EF20}"/>
-    <hyperlink ref="G10" r:id="rId29" xr:uid="{D0C2FCE6-F417-4C60-83C9-2DC27CAAEF88}"/>
-    <hyperlink ref="G11" r:id="rId30" xr:uid="{A10111A9-5855-4053-B198-5913BF6CDA09}"/>
-    <hyperlink ref="G12" r:id="rId31" xr:uid="{75F09E22-DD66-46FD-97C9-B8F6D22B9A35}"/>
-    <hyperlink ref="G13" r:id="rId32" xr:uid="{B7B8D6E5-7B8D-4C93-8C75-1F6B6DA2DD22}"/>
-    <hyperlink ref="G15" r:id="rId33" xr:uid="{EDD28860-C80B-4522-8E09-285835234F9A}"/>
-    <hyperlink ref="G18" r:id="rId34" xr:uid="{C0C61306-92A5-40FD-96B0-E931783E712C}"/>
-    <hyperlink ref="G19" r:id="rId35" xr:uid="{FC56AA1F-BABF-4ECC-9E9C-3C6DED65D859}"/>
-    <hyperlink ref="G20" r:id="rId36" xr:uid="{8121E1B0-CFF7-488B-85A1-D2969EA79341}"/>
-    <hyperlink ref="G22" r:id="rId37" xr:uid="{6381B25B-8A67-4D0E-9DDE-4264F67AC8C3}"/>
+    <hyperlink ref="F2" r:id="rId1" display="https://www.google.com/maps/place/41%C2%B007'32.7%22N+8%C2%B038'15.3%22W/@41.1257397,-8.641813,17z/data=!3m1!4b1!4m13!1m8!3m7!1s0xd2465605bb840af:0x500ebbde4904a60!2sCanidelo,+Vila+Nova+de+Gaia,+Portugal!3b1!8m2!3d41.1233052!4d-8.6461724!16s%2Fm%2F03cmkjx!3m3!8m2!3d41.125736!4d-8.637575" xr:uid="{5F275EB4-8402-4F8D-8925-76F0B1D1896E}"/>
+    <hyperlink ref="F3" r:id="rId2" display="https://www.google.com/maps/place/Galp/@41.2000023,-8.5840168,15z/data=!4m10!1m2!2m1!1sarea+de+servi%C3%A7o+A4!3m6!1s0xd2463fdd2d14787:0xe54397b5855d8659!8m2!3d41.2000023!4d-8.5665073!15sChNhcmVhIGRlIHNlcnZpw6dvIEE0WhUiE2FyZWEgZGUgc2VydmnDp28gYTSSAQtnYXNfc3RhdGlvbpoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VRdGJWbHFRbkJCUlJBQuABAA!16s%2Fg%2F11b6glyzq3" xr:uid="{5BC15C91-2573-4090-B07A-F44F1586E8C1}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{98FD9011-84CC-4339-A5D2-718D9B942905}"/>
+    <hyperlink ref="F5" r:id="rId4" xr:uid="{4EF6DB39-DFA9-410F-8652-639EF692ED5C}"/>
+    <hyperlink ref="F10" r:id="rId5" xr:uid="{EADE799A-2C0B-45FA-9BE7-89C2CC7644BC}"/>
+    <hyperlink ref="F14" r:id="rId6" xr:uid="{CE167075-E8A1-496D-B4E3-34C35ABE1343}"/>
+    <hyperlink ref="F19" r:id="rId7" xr:uid="{64141498-D306-4BF4-9EAB-A220EC8CD602}"/>
+    <hyperlink ref="F11" r:id="rId8" display="https://www.google.com/maps/place/41%C2%B001'32.5%22N+8%C2%B037'15.2%22W/@41.025699,-8.625366,17z/data=!3m1!4b1!4m13!1m8!3m7!1s0xd2479c7cd31a89b:0x73c82fb2f5e003f8!2sEspinho,+Portugal!3b1!8m2!3d41.0071914!4d-8.6410332!16zL20vMDNqMGs4!3m3!8m2!3d41.025695!4d-8.620876" xr:uid="{F75CF23D-ACA1-47D8-8C50-89E09910692F}"/>
+    <hyperlink ref="F15" r:id="rId9" xr:uid="{3F111C1D-3490-4FE6-880A-AA5616060957}"/>
+    <hyperlink ref="F12" r:id="rId10" xr:uid="{BAFBA4C9-E0EB-4328-B5AE-231BC879BB0B}"/>
+    <hyperlink ref="F20" r:id="rId11" display="https://www.google.com/maps/@41.0845386,-8.6187478,3a,75y,110.4h,90t/data=!3m7!1e1!3m5!1sLIYhBDg9FYzt7FcbWR5jZw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D0%26panoid%3DLIYhBDg9FYzt7FcbWR5jZw%26yaw%3D110.4041920217924!7i16384!8i8192?coh=205410&amp;entry=ttu&amp;g_ep=EgoyMDI0MDkyOS4wIKXMDSoASAFQAw%3D%3D" xr:uid="{6083FFBA-D043-4CE8-938E-FD7897302C90}"/>
+    <hyperlink ref="F18" r:id="rId12" display="https://www.google.com/maps/place/Repsol+A25+Viseu+(sul)/@40.623534,-7.930495,17z/data=!4m14!1m7!3m6!1s0xd233706899600ed:0xb5ac567012a36aae!2sMercadona+Viseu!8m2!3d40.6326254!4d-7.9091179!16s%2Fg%2F11s2j25vhc!3m5!1s0xd23373e65fbfa6b:0x2354da54d5b13e37!8m2!3d40.623897!4d-7.933134!16s%2Fg%2F11bvcvn15h" xr:uid="{F197E301-F17A-4CC3-ADC3-8A802FCB1DAD}"/>
+    <hyperlink ref="F16" r:id="rId13" xr:uid="{B876396C-9A69-4EDB-9295-D1229F4E64B1}"/>
+    <hyperlink ref="F6" r:id="rId14" xr:uid="{99DFDA68-E962-477D-B89E-A713E131D40D}"/>
+    <hyperlink ref="F7" r:id="rId15" xr:uid="{5D906E3A-6D8A-4645-BE7A-5A8F269E45DD}"/>
+    <hyperlink ref="F9" r:id="rId16" xr:uid="{13662DC7-E1F1-48E3-A661-8A7991B40B65}"/>
+    <hyperlink ref="F17" r:id="rId17" xr:uid="{94659B98-BC17-44DA-9327-5B1572CCD288}"/>
+    <hyperlink ref="F22" r:id="rId18" xr:uid="{F860D09E-C87F-407E-8D33-A47DC94D2BDE}"/>
+    <hyperlink ref="F21" r:id="rId19" xr:uid="{2613AD08-857D-44EE-A354-09319A3CD507}"/>
+    <hyperlink ref="F23" r:id="rId20" xr:uid="{F26A824F-461F-44B6-9263-1944883781FB}"/>
+    <hyperlink ref="G5" r:id="rId21" xr:uid="{AA4EC664-5239-4F8D-8BB9-C63DAAE26FC3}"/>
+    <hyperlink ref="G21" r:id="rId22" xr:uid="{893B243F-8BF3-4624-A6F6-0EC6D481A87E}"/>
+    <hyperlink ref="G7" r:id="rId23" xr:uid="{43253076-819D-4877-A211-5DE4F410F4AB}"/>
+    <hyperlink ref="G8" r:id="rId24" xr:uid="{E4141D76-C388-4B41-AECE-D563C5EAFFFF}"/>
+    <hyperlink ref="G17" r:id="rId25" xr:uid="{A24151DC-2EC4-4945-84FD-04E1CFEABCC5}"/>
+    <hyperlink ref="G23" r:id="rId26" xr:uid="{49E2B942-8BCD-499E-BE5F-B8AE53E17BF5}"/>
+    <hyperlink ref="G6" r:id="rId27" xr:uid="{E43A11FB-95EE-47D6-8783-54F24B4ED229}"/>
+    <hyperlink ref="G9" r:id="rId28" xr:uid="{20FE1184-92A7-4E96-ADDA-58FB3015AAAD}"/>
+    <hyperlink ref="G10" r:id="rId29" xr:uid="{8A4BDC97-0438-44A1-A0A9-0F93CFDAD5D4}"/>
+    <hyperlink ref="G11" r:id="rId30" xr:uid="{48508D98-59F5-4524-846C-F11A0CE004F1}"/>
+    <hyperlink ref="G12" r:id="rId31" xr:uid="{30CDAFA9-F37A-4E02-BEF0-FCCB6A09D2C8}"/>
+    <hyperlink ref="G13" r:id="rId32" xr:uid="{F87E3F1A-9105-483D-A2B7-C7F19D613F2E}"/>
+    <hyperlink ref="G15" r:id="rId33" xr:uid="{E1A0BFE4-64BD-47FD-A10B-7359B90B3EF1}"/>
+    <hyperlink ref="G18" r:id="rId34" xr:uid="{6CBCAE4F-E4A1-4E46-B669-6E08E46B17E6}"/>
+    <hyperlink ref="G19" r:id="rId35" xr:uid="{B28235EF-B7F1-487A-B4EC-2B7FCF8DD22C}"/>
+    <hyperlink ref="G20" r:id="rId36" xr:uid="{9D39C109-4671-4A2F-84E3-53E6F9A33986}"/>
+    <hyperlink ref="G22" r:id="rId37" xr:uid="{BB56D9FD-586A-4012-8A98-46B58C26CFFF}"/>
+    <hyperlink ref="F33" r:id="rId38" xr:uid="{CA8F94AB-54B2-4396-9433-46831FD5AEBD}"/>
+    <hyperlink ref="F35" r:id="rId39" xr:uid="{B22CC345-9580-4A39-94E9-895F1A1C8833}"/>
+    <hyperlink ref="F37" r:id="rId40" xr:uid="{B1484A8D-01E4-4CD1-9249-877EF343F35D}"/>
+    <hyperlink ref="F39" r:id="rId41" display="https://eur02.safelinks.protection.outlook.com/?url=https%3A%2F%2Fmaps.app.goo.gl%2FDamK2p292amLCpfP8&amp;data=05%7C02%7Cnhenriqu%40mercadona.com%7Ce35ed0f47e244292758a08dcd25e073f%7C8f04bc3b38414627b64c594c3c7ddaac%7C0%7C0%7C638616548491244000%7CUnknown%7CTWFpbGZsb3d8eyJWIjoiMC4wLjAwMDAiLCJQIjoiV2luMzIiLCJBTiI6Ik1haWwiLCJXVCI6Mn0%3D%7C0%7C%7C%7C&amp;sdata=xyLmVVfVuqQ9RAp2VTq5dWVRcApkHhASqXz0u5nihXM%3D&amp;reserved=0" xr:uid="{6D9EC756-6E2E-4DB1-8036-DEF1A618C80C}"/>
+    <hyperlink ref="F32" r:id="rId42" xr:uid="{EDDEE375-020D-4170-B00B-0D9D0E6C79C8}"/>
+    <hyperlink ref="F28" r:id="rId43" xr:uid="{B3ED84D2-CD69-48BE-B2FD-4FB9E3C49D35}"/>
+    <hyperlink ref="F30" r:id="rId44" xr:uid="{B35EBE38-BDA5-4A7B-A336-ED3746E534A7}"/>
+    <hyperlink ref="F27" r:id="rId45" xr:uid="{BD70C6AD-0AC4-4D3D-A5A2-336BFFC510F2}"/>
+    <hyperlink ref="F26" r:id="rId46" xr:uid="{97C5DAF2-E776-4090-A752-972C3D4E4575}"/>
+    <hyperlink ref="F25" r:id="rId47" xr:uid="{0504388C-AA3B-4D66-9F77-FD78FD07E12C}"/>
+    <hyperlink ref="F31" r:id="rId48" xr:uid="{10166358-07DD-413F-BF42-F78804824B2D}"/>
+    <hyperlink ref="F42" r:id="rId49" xr:uid="{C2465E5F-CA73-4956-8E95-2F42980547B1}"/>
+    <hyperlink ref="F38" r:id="rId50" xr:uid="{C1484E8C-3C6E-4928-A9E1-97EEEFEC2C81}"/>
+    <hyperlink ref="F29" r:id="rId51" display="https://maps.app.goo.gl/FakydaijmJaz7n2Y7" xr:uid="{7AA9A038-313A-48A3-B3B4-6A87966BDEC6}"/>
+    <hyperlink ref="F40" r:id="rId52" xr:uid="{B025309B-6A00-4739-97F1-1BCCEB6D3E41}"/>
+    <hyperlink ref="F44" r:id="rId53" xr:uid="{16B76CF4-A6DF-4E92-8B25-D07BF7D21E76}"/>
+    <hyperlink ref="F36" r:id="rId54" xr:uid="{54CA4F92-4C49-421C-A150-79C9468541B1}"/>
+    <hyperlink ref="F41" r:id="rId55" xr:uid="{34B95B28-3232-4392-A975-DA4AE4AF37E9}"/>
+    <hyperlink ref="G36" r:id="rId56" xr:uid="{6FA3B268-38C5-4224-980A-5CB235E07F2F}"/>
+    <hyperlink ref="G39" r:id="rId57" xr:uid="{9EA1C444-5677-429C-9343-5764CE0F041A}"/>
+    <hyperlink ref="G26" r:id="rId58" xr:uid="{CDCE51D9-7C65-4A87-88C5-AA25658084DD}"/>
+    <hyperlink ref="G25" r:id="rId59" xr:uid="{312FCA81-522A-40B6-9913-A8D55CDCAE8E}"/>
+    <hyperlink ref="G28" r:id="rId60" xr:uid="{B1500DBF-0FD4-4D27-826E-8ABDB36C0F68}"/>
+    <hyperlink ref="G31" r:id="rId61" xr:uid="{92241696-6521-493C-8961-2F0B1A8A63AF}"/>
+    <hyperlink ref="G33" r:id="rId62" xr:uid="{96EF6FF0-A504-4D92-B31F-387087DED18E}"/>
+    <hyperlink ref="G35" r:id="rId63" xr:uid="{561A3B49-8E3D-4374-BE0D-76EDE3B50F21}"/>
+    <hyperlink ref="G37" r:id="rId64" xr:uid="{105B744D-3740-444D-9DF1-D33493ED1D8B}"/>
+    <hyperlink ref="G42" r:id="rId65" xr:uid="{6F8A1B54-F1DF-4BD6-B244-1318F6B66CA5}"/>
+    <hyperlink ref="G40" r:id="rId66" xr:uid="{8B30F535-FF05-4EAF-91F8-D8D03E3EFCBB}"/>
+    <hyperlink ref="G30" r:id="rId67" xr:uid="{183B23FB-7465-426C-A2DA-2CF959C58F7A}"/>
+    <hyperlink ref="G27" r:id="rId68" xr:uid="{15380698-F79C-4CD5-B267-88B3253810D8}"/>
+    <hyperlink ref="G32" r:id="rId69" xr:uid="{37478915-48E4-410E-BB3A-6D3C6CC567B0}"/>
+    <hyperlink ref="G43" r:id="rId70" xr:uid="{7348BB3D-FF9C-460B-9003-572F3EA88A9B}"/>
+    <hyperlink ref="G41" r:id="rId71" xr:uid="{7ADBC77E-D7EE-4619-9DF3-D9D75ADFABA5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId72"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4EB981CD-BB3E-4E18-80E2-1E124DD4C1BD}">
+          <x14:cfRule type="dataBar" id="{30FB49D0-576F-484A-9F04-F762F69B2151}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F2</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{755BD77B-8CC4-44FC-BA03-787B988F6015}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2181,7 +3033,7 @@
           <xm:sqref>F3</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{F6A40BF1-B9F4-45C6-8D53-103870EB4B39}">
+          <x14:cfRule type="dataBar" id="{40FC922F-FA9C-4D3B-8263-77C3E6A8432D}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2192,7 +3044,7 @@
           <xm:sqref>F4</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{F2D78B82-B72A-4421-874B-4CD843CDF88E}">
+          <x14:cfRule type="dataBar" id="{6E1206DF-6DEB-4E04-8F31-0757049B7953}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2203,7 +3055,7 @@
           <xm:sqref>F6:F10</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{86C0E903-4BA0-47B4-B905-76C3F67C57CE}">
+          <x14:cfRule type="dataBar" id="{2E030C97-BB3C-4CF7-9B70-C9814F9D0EF6}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2214,7 +3066,7 @@
           <xm:sqref>F11</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0818DE56-5C48-406A-9BA9-84F492B36229}">
+          <x14:cfRule type="dataBar" id="{DD305FE1-D086-4E0E-89C1-0C7E85D65DC8}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2225,7 +3077,7 @@
           <xm:sqref>F12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{A4D5ADE0-6176-459A-85F6-CA1B33C513EB}">
+          <x14:cfRule type="dataBar" id="{B9AA7D27-186B-4161-94E5-C5AEE1281ABF}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2236,7 +3088,7 @@
           <xm:sqref>F13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{F54F33F8-6906-4139-9934-65E447715085}">
+          <x14:cfRule type="dataBar" id="{0544B7F7-CF4F-4F07-A689-AB7D33CC8C32}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2247,7 +3099,7 @@
           <xm:sqref>F14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{B47EB2CE-358C-486D-A189-F0DB279E373E}">
+          <x14:cfRule type="dataBar" id="{670BF0A7-01F3-4D70-90D9-AE6DF983C372}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2258,7 +3110,7 @@
           <xm:sqref>F15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{043C1E1A-E301-4083-A263-12038E96B7B7}">
+          <x14:cfRule type="dataBar" id="{65C34C26-3515-4418-BBE5-4ABB4918FA10}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2269,7 +3121,7 @@
           <xm:sqref>F16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5AB8BCA4-C044-47C5-AF38-746497910378}">
+          <x14:cfRule type="dataBar" id="{1B231A9C-893F-4E93-9C5B-C0DB43F1A147}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2280,7 +3132,7 @@
           <xm:sqref>F17</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9F36BD4E-26D9-4004-B4E3-EF6523A1D063}">
+          <x14:cfRule type="dataBar" id="{DD447D69-353A-452A-BE80-2E9AD1AE239D}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2291,7 +3143,7 @@
           <xm:sqref>F18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{E7A31A38-B52D-477B-98E9-2A0CBD7F2119}">
+          <x14:cfRule type="dataBar" id="{A55A45F4-B920-48DC-979D-A23CFD2E5C94}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2302,7 +3154,7 @@
           <xm:sqref>F19</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{79500CEB-4C30-43A5-96A9-4489878BC6BF}">
+          <x14:cfRule type="dataBar" id="{8DF9DF4E-6BFF-407F-861A-9AF060F1D43E}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2313,7 +3165,7 @@
           <xm:sqref>F22:F23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0E5B2793-E734-42AC-9ABC-298292A3FE2F}">
+          <x14:cfRule type="dataBar" id="{3A9CB92F-0E10-4058-8028-650674652E6E}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2321,10 +3173,1637 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>F5 F24</xm:sqref>
+          <xm:sqref>F24 F5</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D8AD0291-2D57-4E56-B3D2-4CE3552BC305}">
+          <x14:cfRule type="dataBar" id="{39E40594-1983-4307-8FCC-CD695BAE4F9D}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G2</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{1C2AE5ED-0584-4F6C-9461-A25DDC6E5B4C}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G3</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{100D9A8C-9878-42B4-9125-55F4698B2A77}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G4</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{FD6A10F4-AAFE-4C96-B132-41ADE092E178}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G6:G8 G10:G23</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{8C76355E-2D6D-40AF-ABE4-E00AFEA5067D}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{75CD4E91-DDF8-4F36-9EFD-977D50110370}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G5 G24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{664D1B66-6622-4592-94D2-639F27A1F1AD}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{A729F339-7E62-4DAA-87FF-C47EC2017AA4}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{14176752-41FA-4408-B48B-8FAD9181A2B0}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F27</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{DAD877A4-AFA8-4B89-887E-3C22D3BC592C}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F28</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{71894A45-03F3-4503-8BC0-DB7B706128A2}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F31</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{AFA383BA-BA2E-4063-95A7-349BC308FC0D}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F43</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{0D3C0B7F-90B5-40CB-95EA-07EAD79DDADF}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F44</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{65BD2DCD-8E5D-481E-A632-21B990203C2D}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F44:F45 F25:F42</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{9555C3D9-BB94-4209-9E97-FF27BD0AD1F8}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F45</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{3F0C9A87-E1FE-4BBD-9709-FACAE2BEA80A}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G43</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{6CBA4C1D-548E-4347-B9E1-D5B16DE7B84A}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G44</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{4F3ABC73-5AAD-49D7-8A56-2BA2BC10DABA}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G44:G45 G25:G42</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{4CED1CF9-2405-406A-BEB7-9F6DBD8E1CC5}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G45</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF5F13FE-4E63-48A0-84FC-D9B1FB307CA9}">
+  <dimension ref="A1:J51"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.109375" customWidth="1"/>
+    <col min="2" max="2" width="31.77734375" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" customWidth="1"/>
+    <col min="4" max="4" width="20.21875" customWidth="1"/>
+    <col min="5" max="5" width="31.6640625" customWidth="1"/>
+    <col min="6" max="6" width="24.33203125" customWidth="1"/>
+    <col min="7" max="8" width="18.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>7000</v>
+      </c>
+      <c r="B2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="H2" s="10">
+        <v>221201095</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>7001</v>
+      </c>
+      <c r="B3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" t="s">
+        <v>259</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="H3" s="11">
+        <v>221201098</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>7002</v>
+      </c>
+      <c r="B4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H4" s="10">
+        <v>221201094</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>7003</v>
+      </c>
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="H5" s="11">
+        <v>221205059</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>7004</v>
+      </c>
+      <c r="B6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C6" t="s">
+        <v>232</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="H6" s="10">
+        <v>221205055</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>7005</v>
+      </c>
+      <c r="B7" t="s">
+        <v>233</v>
+      </c>
+      <c r="C7" t="s">
+        <v>233</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H7" s="11">
+        <v>221201096</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7006</v>
+      </c>
+      <c r="B8" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" t="s">
+        <v>260</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="H8" s="10">
+        <v>253127941</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>7007</v>
+      </c>
+      <c r="B9" t="s">
+        <v>235</v>
+      </c>
+      <c r="C9" t="s">
+        <v>261</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="H9" s="11">
+        <v>221202911</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>7008</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="H10" s="10">
+        <v>221205056</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>7009</v>
+      </c>
+      <c r="B11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="H11" s="11">
+        <v>221205057</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>7010</v>
+      </c>
+      <c r="B12" t="s">
+        <v>236</v>
+      </c>
+      <c r="C12" t="s">
+        <v>262</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H12" s="10">
+        <v>253127942</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>7011</v>
+      </c>
+      <c r="B13" t="s">
+        <v>237</v>
+      </c>
+      <c r="C13" t="s">
+        <v>263</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="H13" s="11">
+        <v>253127943</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>7012</v>
+      </c>
+      <c r="B14" t="s">
+        <v>238</v>
+      </c>
+      <c r="C14" t="s">
+        <v>264</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="H14" s="10">
+        <v>221202910</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>7013</v>
+      </c>
+      <c r="B15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" t="s">
+        <v>130</v>
+      </c>
+      <c r="E15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="H15" s="11">
+        <v>256120000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>7014</v>
+      </c>
+      <c r="B16" t="s">
+        <v>239</v>
+      </c>
+      <c r="C16" t="s">
+        <v>265</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="H16" s="10">
+        <v>221202916</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>7015</v>
+      </c>
+      <c r="B17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="H17" s="11">
+        <v>221205058</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>7016</v>
+      </c>
+      <c r="B18" t="s">
+        <v>240</v>
+      </c>
+      <c r="C18" t="s">
+        <v>266</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="H18" s="10">
+        <v>221202912</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>7017</v>
+      </c>
+      <c r="B19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" t="s">
+        <v>131</v>
+      </c>
+      <c r="E19" t="s">
+        <v>132</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="H19" s="11">
+        <v>256120002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>7018</v>
+      </c>
+      <c r="B20" t="s">
+        <v>241</v>
+      </c>
+      <c r="C20" t="s">
+        <v>267</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="H20" s="10">
+        <v>258127880</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>7019</v>
+      </c>
+      <c r="B21" t="s">
+        <v>242</v>
+      </c>
+      <c r="C21" t="s">
+        <v>268</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="H21" s="11">
+        <v>221202913</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>7020</v>
+      </c>
+      <c r="B22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="H22" s="10">
+        <v>221202915</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>7021</v>
+      </c>
+      <c r="B23" t="s">
+        <v>243</v>
+      </c>
+      <c r="C23" t="s">
+        <v>269</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="H23" s="11">
+        <v>221202917</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>7022</v>
+      </c>
+      <c r="B24" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" t="s">
+        <v>133</v>
+      </c>
+      <c r="E24" t="s">
+        <v>134</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="H24" s="10">
+        <v>256120004</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>7023</v>
+      </c>
+      <c r="B25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="H25" s="11">
+        <v>256120003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>7025</v>
+      </c>
+      <c r="B26" t="s">
+        <v>244</v>
+      </c>
+      <c r="C26" t="s">
+        <v>270</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="H26" s="10">
+        <v>253127944</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>7026</v>
+      </c>
+      <c r="B27" t="s">
+        <v>245</v>
+      </c>
+      <c r="C27" t="s">
+        <v>260</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="H27" s="11">
+        <v>253120210</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>7027</v>
+      </c>
+      <c r="B28" t="s">
+        <v>246</v>
+      </c>
+      <c r="C28" t="s">
+        <v>271</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="H28" s="10">
+        <v>221202920</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>7028</v>
+      </c>
+      <c r="B29" t="s">
+        <v>247</v>
+      </c>
+      <c r="C29" t="s">
+        <v>272</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="H29" s="11">
+        <v>221202914</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>7029</v>
+      </c>
+      <c r="B30" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" t="s">
+        <v>56</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H30" s="10">
+        <v>221202919</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>7030</v>
+      </c>
+      <c r="B31" t="s">
+        <v>248</v>
+      </c>
+      <c r="C31" t="s">
+        <v>273</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="H31" s="11">
+        <v>221202921</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>7031</v>
+      </c>
+      <c r="B32" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" t="s">
+        <v>70</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="H32" s="10">
+        <v>256120250</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>7034</v>
+      </c>
+      <c r="B33" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" t="s">
+        <v>53</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="H33" s="11">
+        <v>221202922</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>7035</v>
+      </c>
+      <c r="B34" t="s">
+        <v>249</v>
+      </c>
+      <c r="C34" t="s">
+        <v>274</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="H34" s="10">
+        <v>221202918</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>7037</v>
+      </c>
+      <c r="B35" t="s">
+        <v>72</v>
+      </c>
+      <c r="C35" t="s">
+        <v>73</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="H35" s="11">
+        <v>256120252</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>7038</v>
+      </c>
+      <c r="B36" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" t="s">
+        <v>75</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="H36" s="10">
+        <v>233120010</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>7040</v>
+      </c>
+      <c r="B37" t="s">
+        <v>76</v>
+      </c>
+      <c r="C37" t="s">
+        <v>77</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="H37" s="11">
+        <v>232120210</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>7042</v>
+      </c>
+      <c r="B38" t="s">
+        <v>250</v>
+      </c>
+      <c r="C38" t="s">
+        <v>250</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="H38" s="8"/>
+    </row>
+    <row r="39" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>7043</v>
+      </c>
+      <c r="B39" t="s">
+        <v>251</v>
+      </c>
+      <c r="C39" t="s">
+        <v>260</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="H39" s="11">
+        <v>253120211</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>7045</v>
+      </c>
+      <c r="B40" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40" t="s">
+        <v>79</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="H40" s="10">
+        <v>256120251</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>7050</v>
+      </c>
+      <c r="B41" t="s">
+        <v>252</v>
+      </c>
+      <c r="C41" t="s">
+        <v>275</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="H41" s="11">
+        <v>255120210</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>7052</v>
+      </c>
+      <c r="B42" t="s">
+        <v>253</v>
+      </c>
+      <c r="C42" t="s">
+        <v>276</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="H42" s="10">
+        <v>255120211</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>7053</v>
+      </c>
+      <c r="B43" t="s">
+        <v>254</v>
+      </c>
+      <c r="C43" t="s">
+        <v>259</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="H43" s="11">
+        <v>221202925</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>7056</v>
+      </c>
+      <c r="B44" t="s">
+        <v>255</v>
+      </c>
+      <c r="C44" t="s">
+        <v>51</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H44" s="10">
+        <v>221202923</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>7063</v>
+      </c>
+      <c r="B45" t="s">
+        <v>256</v>
+      </c>
+      <c r="C45" t="s">
+        <v>277</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="H45" s="11">
+        <v>253127945</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>7064</v>
+      </c>
+      <c r="B46" t="s">
+        <v>83</v>
+      </c>
+      <c r="C46" t="s">
+        <v>82</v>
+      </c>
+      <c r="D46" t="s">
+        <v>138</v>
+      </c>
+      <c r="E46" t="s">
+        <v>137</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="H46" s="10">
+        <v>239127941</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>7066</v>
+      </c>
+      <c r="B47" t="s">
+        <v>81</v>
+      </c>
+      <c r="C47" t="s">
+        <v>82</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="H47" s="11">
+        <v>239127942</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>7067</v>
+      </c>
+      <c r="B48" t="s">
+        <v>84</v>
+      </c>
+      <c r="C48" t="s">
+        <v>84</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="H48" s="12">
+        <v>271127941</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>7072</v>
+      </c>
+      <c r="B49" t="s">
+        <v>257</v>
+      </c>
+      <c r="C49" t="s">
+        <v>233</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="H49" s="13">
+        <v>221202924</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>7074</v>
+      </c>
+      <c r="B50" t="s">
+        <v>258</v>
+      </c>
+      <c r="C50" t="s">
+        <v>261</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="H50" s="10">
+        <v>255120212</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>7078</v>
+      </c>
+      <c r="B51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C51" t="s">
+        <v>56</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="H51" s="14">
+        <v>221201005</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="G51">
+    <cfRule type="dataBar" priority="15">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{E210761F-77A8-4D7C-965F-1C0C52BCCA56}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G50">
+    <cfRule type="dataBar" priority="16">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{B493B05B-9934-45EE-B9DE-77818E0EF606}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2">
+    <cfRule type="dataBar" priority="9">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{72FBEE63-E823-4772-A920-A6A62526114C}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3">
+    <cfRule type="dataBar" priority="10">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{E4D2AF57-EFB6-4863-8046-9063AAEF2885}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="dataBar" priority="11">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{6B12723F-B9C2-4860-94F9-5692EDD76094}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:F6">
+    <cfRule type="dataBar" priority="13">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{E5532447-EDAA-431D-8CEA-96C954B29720}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{3730D5EE-D404-4B0C-A207-1BAABF28C436}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{265C1D59-958D-43BA-AE3C-E430A27E8A85}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{DDDCA558-9158-44C0-8C8C-DBB41DDE4F40}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="5">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{4FFD795C-23A0-4BD5-8414-A2A4AC943D07}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="6">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{E61A3283-E02A-460F-A963-217BB11315C7}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="7">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{5BEE5DE2-055C-41D9-8309-8CE451F9A7C6}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="8">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{DBC38A5C-B091-4661-BFE3-7B8D1D5A604E}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="dataBar" priority="14">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{EC91A8F3-B120-49FF-9D3F-4A54F3CE0DE7}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F51">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{D557EAD4-67B3-41AE-B45A-6D4E69675DF3}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F42:F45 F49:F50 F2:F40">
+    <cfRule type="dataBar" priority="12">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{3875FD82-566A-4200-84A1-C9E574E28293}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{6AD1EBD4-7194-4406-9C70-E9BE7CCC60E8}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{B4A2B6F6-0A66-40EE-9551-BE9A6694C0A6}"/>
+    <hyperlink ref="G5" r:id="rId3" xr:uid="{98AF7985-4473-4A2A-B72E-C3EFFD9561F0}"/>
+    <hyperlink ref="G10" r:id="rId4" xr:uid="{338FBFD1-19D7-4408-B446-69D0999D42BC}"/>
+    <hyperlink ref="G11" r:id="rId5" xr:uid="{87273ADD-8A1F-47CD-98EA-FA33CAF523C1}"/>
+    <hyperlink ref="G14" r:id="rId6" xr:uid="{32641DED-5CBB-4B01-877B-74F391608DF6}"/>
+    <hyperlink ref="G16" r:id="rId7" xr:uid="{880B2237-FE5B-4270-9863-0580DAA41B3B}"/>
+    <hyperlink ref="G17" r:id="rId8" xr:uid="{C0486DC8-B83F-4500-A28A-A887BAFC3525}"/>
+    <hyperlink ref="G18" r:id="rId9" xr:uid="{7716216C-A342-4C97-9E7D-20FC86E4C61B}"/>
+    <hyperlink ref="G19" r:id="rId10" xr:uid="{4371B161-1162-44B5-8772-096F53B07CA5}"/>
+    <hyperlink ref="G21" r:id="rId11" xr:uid="{3F320643-1859-4F22-BFB7-3315B656BFA3}"/>
+    <hyperlink ref="G22" r:id="rId12" xr:uid="{E9A2F416-8CFF-401D-8EC0-3375A1F8092A}"/>
+    <hyperlink ref="G23" r:id="rId13" xr:uid="{DC2EE553-C662-4934-8DC8-7B7C3374D7CF}"/>
+    <hyperlink ref="G24" r:id="rId14" xr:uid="{345CBDC4-8FF2-43FB-941A-DAC35106676E}"/>
+    <hyperlink ref="G25" r:id="rId15" xr:uid="{948E26AA-8F46-4646-AC23-A8FBA222CD0B}"/>
+    <hyperlink ref="G26" r:id="rId16" xr:uid="{4C7627EE-74DA-44CB-B831-DC07B5E0982B}"/>
+    <hyperlink ref="G27" r:id="rId17" xr:uid="{0412BDBD-BA55-4CE0-A837-A2359AD641AC}"/>
+    <hyperlink ref="G29" r:id="rId18" xr:uid="{CA4482E6-B152-4955-A106-60C1ED0A89DC}"/>
+    <hyperlink ref="G30" r:id="rId19" xr:uid="{A524704C-9801-48DF-9F82-40B0DDD0E5AB}"/>
+    <hyperlink ref="G31" r:id="rId20" xr:uid="{8FFAF48D-F15D-4430-8834-9092A47A6065}"/>
+    <hyperlink ref="G32" r:id="rId21" xr:uid="{16E01A3B-5D3E-4108-9639-12AC7EED83FC}"/>
+    <hyperlink ref="G33" r:id="rId22" xr:uid="{0A21C455-E6AE-464A-B6D8-B067AC94A3B2}"/>
+    <hyperlink ref="G35" r:id="rId23" xr:uid="{55795B1E-5F93-434E-9F7C-89D9CDC49A74}"/>
+    <hyperlink ref="G37" r:id="rId24" xr:uid="{DCAAB6C9-2A64-45B0-B0EE-6DA62A73D6A3}"/>
+    <hyperlink ref="G36" r:id="rId25" xr:uid="{4BFD334B-CD8A-4A69-8821-EC427B63CAFD}"/>
+    <hyperlink ref="G39" r:id="rId26" xr:uid="{2558E316-1BEE-4B3A-A040-6DF24519E0D5}"/>
+    <hyperlink ref="G40" r:id="rId27" xr:uid="{3D1A05EC-7186-46CA-AAA2-CB6802C3DA4F}"/>
+    <hyperlink ref="G41" r:id="rId28" xr:uid="{A09064D2-6E19-42C5-82AC-9F95B0CB61BC}"/>
+    <hyperlink ref="G42" r:id="rId29" xr:uid="{42000BF5-B840-4B8D-9F59-AC41827108A6}"/>
+    <hyperlink ref="G45" r:id="rId30" xr:uid="{D7E64226-B63B-4171-BED1-F35B504422CF}"/>
+    <hyperlink ref="G46" r:id="rId31" xr:uid="{60490C5A-3E58-4D8D-9675-AB529535A318}"/>
+    <hyperlink ref="G12" r:id="rId32" xr:uid="{4B1C1F08-0BCE-4F9B-B8EF-81C85142EA4C}"/>
+    <hyperlink ref="G20" r:id="rId33" xr:uid="{D6DA2DB5-288E-473E-8791-557B0EF8C39A}"/>
+    <hyperlink ref="G48" r:id="rId34" xr:uid="{1791754B-F01A-4FE7-B7D3-D56461485453}"/>
+    <hyperlink ref="G47" r:id="rId35" xr:uid="{D43DCCAA-9A58-476E-920A-E9D8C0BB5F45}"/>
+    <hyperlink ref="G49" r:id="rId36" xr:uid="{1C885C7C-2DC1-4C79-B225-0DD677D84670}"/>
+    <hyperlink ref="G4" r:id="rId37" xr:uid="{E5763BB2-8BC3-4B74-8E27-764E930300A8}"/>
+    <hyperlink ref="G7" r:id="rId38" xr:uid="{85D6CAB3-1F78-45F0-82FE-6E94A8C39036}"/>
+    <hyperlink ref="G28" r:id="rId39" xr:uid="{6E7E25A2-BF93-4BAE-AA29-17ECF250B924}"/>
+    <hyperlink ref="G34" r:id="rId40" xr:uid="{F7D71926-9BD3-49E5-B806-D5690AB23365}"/>
+    <hyperlink ref="G51" r:id="rId41" xr:uid="{7ADE1528-2B44-4546-880A-9DBD707C0320}"/>
+    <hyperlink ref="G38" r:id="rId42" xr:uid="{5420E1D0-F766-4F17-AA78-BD4C052F05E5}"/>
+    <hyperlink ref="F4" r:id="rId43" xr:uid="{27908F85-814D-4460-891A-82F2B849F43A}"/>
+    <hyperlink ref="F5" r:id="rId44" xr:uid="{EA15A9F2-909E-43CE-8C2D-D3EE7D1CD258}"/>
+    <hyperlink ref="F37" r:id="rId45" xr:uid="{98748FF1-34DB-4ECB-AC00-28D38252F35A}"/>
+    <hyperlink ref="F8" r:id="rId46" xr:uid="{DBF13841-5F33-4D45-96BD-8DBA5753C23B}"/>
+    <hyperlink ref="F9" r:id="rId47" xr:uid="{48A01F28-AA82-40CD-BADF-C62392438AB4}"/>
+    <hyperlink ref="F10" r:id="rId48" xr:uid="{17D467A1-9A96-4120-8576-B5B3949B2EBB}"/>
+    <hyperlink ref="F11" r:id="rId49" xr:uid="{B4276D14-6D85-4CAB-91D4-31BFFF059361}"/>
+    <hyperlink ref="F14" r:id="rId50" xr:uid="{6804DE22-C155-472C-86AE-3E34E70C7931}"/>
+    <hyperlink ref="F13" r:id="rId51" xr:uid="{731A5AE1-1328-4313-89E1-598157188DA0}"/>
+    <hyperlink ref="F15" r:id="rId52" xr:uid="{E5961BA0-6A1C-4D27-B38D-39532D531278}"/>
+    <hyperlink ref="F19" r:id="rId53" xr:uid="{C097405F-3D3B-483F-84F2-2194E1910C26}"/>
+    <hyperlink ref="F16" r:id="rId54" xr:uid="{FFFE79D5-229E-4813-A031-8EC172DEE9C7}"/>
+    <hyperlink ref="F17" r:id="rId55" xr:uid="{995AC86A-C50C-4BC6-B4A2-6A248996AC05}"/>
+    <hyperlink ref="F18" r:id="rId56" xr:uid="{A680E36E-B785-4C75-8106-D4916082C843}"/>
+    <hyperlink ref="F20" r:id="rId57" xr:uid="{7FE8E28C-0D6C-43E6-B3C8-F2CE133CC284}"/>
+    <hyperlink ref="F21" r:id="rId58" xr:uid="{8AE5EDE8-BAC1-467C-87F7-9E3CF316839A}"/>
+    <hyperlink ref="F22" r:id="rId59" xr:uid="{03F03F49-EA03-4869-9B82-98482357C34E}"/>
+    <hyperlink ref="F23" r:id="rId60" xr:uid="{7A22F1A6-2F75-44E1-890C-E6BD83FEC979}"/>
+    <hyperlink ref="F24" r:id="rId61" xr:uid="{B17FFAAE-FC35-4937-AC1E-35BAC2EEF4AF}"/>
+    <hyperlink ref="F25" r:id="rId62" xr:uid="{370873A1-8039-453B-812D-EC643C6EDDDF}"/>
+    <hyperlink ref="F26" r:id="rId63" xr:uid="{D5D7DC72-FCA5-4972-A2D3-276F239832C4}"/>
+    <hyperlink ref="F28" r:id="rId64" xr:uid="{51553FFD-3831-43EC-AF1E-8DBB690EE2D5}"/>
+    <hyperlink ref="F29" r:id="rId65" xr:uid="{8EDC1A4A-0361-4DA8-9A72-8A3A150F3C9F}"/>
+    <hyperlink ref="F30" r:id="rId66" xr:uid="{80AEEFB5-5849-4F39-95ED-DCFE748A3494}"/>
+    <hyperlink ref="F32" r:id="rId67" xr:uid="{60CB020B-F2C7-4F5B-955E-069FFD598F8E}"/>
+    <hyperlink ref="F33" r:id="rId68" xr:uid="{8ECA7072-DF53-4D96-B027-CAEB71DC7B66}"/>
+    <hyperlink ref="F34" r:id="rId69" xr:uid="{46A5D059-D25D-439B-B55D-03DE04C815C5}"/>
+    <hyperlink ref="F35" r:id="rId70" xr:uid="{2E645EAF-1BCD-4125-9710-62EA6DB3AC45}"/>
+    <hyperlink ref="F36" r:id="rId71" xr:uid="{1FC71352-9069-4758-BDE8-D0CC5DA8C4C4}"/>
+    <hyperlink ref="F39" r:id="rId72" xr:uid="{CB6A5ECB-8DF7-40D2-8796-B14C01513C8F}"/>
+    <hyperlink ref="F27" r:id="rId73" xr:uid="{5E1F9F42-F84C-4BBE-BFBF-9384B0915DF7}"/>
+    <hyperlink ref="F40" r:id="rId74" xr:uid="{F58A0126-4D02-4DCD-8022-1F11A73EAFC4}"/>
+    <hyperlink ref="F41" r:id="rId75" xr:uid="{0051A337-1D7E-434B-A40C-9EA96FFE81A0}"/>
+    <hyperlink ref="F42" r:id="rId76" xr:uid="{BCA15C55-0B3C-4BBC-97F8-47E3C220FDA2}"/>
+    <hyperlink ref="F44" r:id="rId77" xr:uid="{DEAF6D45-1D01-4933-A55D-C76F52B19085}"/>
+    <hyperlink ref="F45" r:id="rId78" xr:uid="{80774BD0-824A-440C-9142-1430148E7647}"/>
+    <hyperlink ref="F46" r:id="rId79" xr:uid="{B10BC7EB-7A1D-4A69-A19E-7CC6899E15EB}"/>
+    <hyperlink ref="F50" r:id="rId80" xr:uid="{1C7D3A5F-ADFA-4EF8-9A46-8E270D76A75E}"/>
+    <hyperlink ref="F48" r:id="rId81" xr:uid="{9E16EADF-2DBC-457A-AA13-1BCDD97BB29F}"/>
+    <hyperlink ref="F47" r:id="rId82" xr:uid="{475B7D32-091C-4BA3-852C-74F047F9C615}"/>
+    <hyperlink ref="F49" r:id="rId83" xr:uid="{2E0E1F65-1703-4AD5-AE11-77FAC74FE7F5}"/>
+    <hyperlink ref="F31" r:id="rId84" xr:uid="{6FB8A625-64CA-4A31-9DD1-B36898534D20}"/>
+    <hyperlink ref="F7" r:id="rId85" xr:uid="{1AE6D223-D178-46E5-9DE3-983120EFC60C}"/>
+    <hyperlink ref="F2" r:id="rId86" xr:uid="{C2121640-3B5F-4584-994D-94A4D3841ACE}"/>
+    <hyperlink ref="F6" r:id="rId87" xr:uid="{6A560BE6-8E3D-46AA-A8A6-2C7A3248254F}"/>
+    <hyperlink ref="F12" r:id="rId88" xr:uid="{5C1A230B-5C48-4E65-97C5-A1EB5A0EFAA8}"/>
+    <hyperlink ref="F3" r:id="rId89" xr:uid="{7A5D1D71-DE48-4DD9-9316-407A20F3BA8B}"/>
+    <hyperlink ref="F51" r:id="rId90" xr:uid="{B2556BAB-0652-48C9-AB95-99BDB764EB0D}"/>
+    <hyperlink ref="F38" r:id="rId91" xr:uid="{9398E282-056F-4E66-A793-BF21B766E0E9}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{E210761F-77A8-4D7C-965F-1C0C52BCCA56}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G51</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{B493B05B-9934-45EE-B9DE-77818E0EF606}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G2:G50</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{72FBEE63-E823-4772-A920-A6A62526114C}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2335,7 +4814,7 @@
           <xm:sqref>F2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{41C1945A-74C1-4CAA-B2D4-E31D3AD9AE40}">
+          <x14:cfRule type="dataBar" id="{E4D2AF57-EFB6-4863-8046-9063AAEF2885}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2343,10 +4822,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>G2</xm:sqref>
+          <xm:sqref>F3</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{CDF136A3-4357-467B-B289-155FA14F29A8}">
+          <x14:cfRule type="dataBar" id="{6B12723F-B9C2-4860-94F9-5692EDD76094}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2354,10 +4833,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>G3</xm:sqref>
+          <xm:sqref>F4</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{62ED83B1-7CDB-43D8-9643-E976CF99F150}">
+          <x14:cfRule type="dataBar" id="{E5532447-EDAA-431D-8CEA-96C954B29720}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2365,10 +4844,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>G4</xm:sqref>
+          <xm:sqref>F5:F6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8ADD97A5-EC2B-4596-924A-65E0AE378C8D}">
+          <x14:cfRule type="dataBar" id="{3730D5EE-D404-4B0C-A207-1BAABF28C436}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2376,10 +4855,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>G6:G8 G10:G23</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{E7893CEF-82CD-4050-8BD2-796D578215EF}">
+          <x14:cfRule type="dataBar" id="{265C1D59-958D-43BA-AE3C-E430A27E8A85}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2387,10 +4863,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>G9</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{E79D7C0A-53D6-421E-89FD-B49CC226495F}">
+          <x14:cfRule type="dataBar" id="{DDDCA558-9158-44C0-8C8C-DBB41DDE4F40}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2398,7 +4871,72 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>G5 G24</xm:sqref>
+          <x14:cfRule type="dataBar" id="{4FFD795C-23A0-4BD5-8414-A2A4AC943D07}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{E61A3283-E02A-460F-A963-217BB11315C7}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{5BEE5DE2-055C-41D9-8309-8CE451F9A7C6}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{DBC38A5C-B091-4661-BFE3-7B8D1D5A604E}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F6</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{EC91A8F3-B120-49FF-9D3F-4A54F3CE0DE7}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F8</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{D557EAD4-67B3-41AE-B45A-6D4E69675DF3}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F51</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{3875FD82-566A-4200-84A1-C9E574E28293}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F42:F45 F49:F50 F2:F40</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/Dados.xlsx
+++ b/Dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/paulo_martins_tja_pt/Documents/Dep. Formação/Ambiente Formadores/Mercadona HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="8_{3ECB6CA0-9746-43FE-8E62-14652AAF4818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6514B761-4580-446A-AA78-2F12B78F0BF0}"/>
+  <xr:revisionPtr revIDLastSave="147" documentId="8_{3ECB6CA0-9746-43FE-8E62-14652AAF4818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD3DBDE7-5970-4091-9F14-1B8649B0E4FE}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{462C5653-B832-456D-BA7D-C78D43202BCF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{462C5653-B832-456D-BA7D-C78D43202BCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Almeirim" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="339">
   <si>
     <t>Número</t>
   </si>
@@ -994,6 +994,66 @@
   </si>
   <si>
     <t>211 202 950</t>
+  </si>
+  <si>
+    <t>41.007347393660645, -8.621831522617562</t>
+  </si>
+  <si>
+    <t>R. 19 1966, 4500-400 Espinho</t>
+  </si>
+  <si>
+    <t>Av. Oliveira Martins 1195, 4420-230 Gondomar</t>
+  </si>
+  <si>
+    <t>41.14394061531503, -8.54124137614113</t>
+  </si>
+  <si>
+    <t>41.17786328590812, -8.681388609016453</t>
+  </si>
+  <si>
+    <t>R. Sousa Aroso 705, 4450-290 Matosinhos</t>
+  </si>
+  <si>
+    <t>41.16940741589204, -8.54136516437712</t>
+  </si>
+  <si>
+    <t>Rua Joaquim Ribeiro 30, 4510-716 Fânzeres</t>
+  </si>
+  <si>
+    <t>41.12335637251172, -8.596801267503777</t>
+  </si>
+  <si>
+    <t>Rua de Raimundo de Carvalho 724, 4430-185 Vila Nova de Gaia</t>
+  </si>
+  <si>
+    <t>R. Filipa Borges 414, 4750-809 Barcelos</t>
+  </si>
+  <si>
+    <t>41.5321458073948, -8.626158562761148</t>
+  </si>
+  <si>
+    <t>41.23181298172971, -8.60695926103612</t>
+  </si>
+  <si>
+    <t>Av. do Eng. José Afonso Moreira de Figueiredo 683, 4470-285 Maia</t>
+  </si>
+  <si>
+    <t>Av. Dr. António Palha 5, 4715-213 Braga</t>
+  </si>
+  <si>
+    <t>41.54763741948135, -8.39888659008707</t>
+  </si>
+  <si>
+    <t>41.19903943066096, -8.31174396818275</t>
+  </si>
+  <si>
+    <t>Av. Dr. Francisco Sá Carneiro 218, 4560-131 Guilhufe</t>
+  </si>
+  <si>
+    <t>41.16314307596957, -8.629920348274434</t>
+  </si>
+  <si>
+    <t>R. de Domingos Sequeira 225, 4050-424 Porto</t>
   </si>
 </sst>
 </file>
@@ -1595,6 +1655,12 @@
       <c r="C2" s="1" t="s">
         <v>51</v>
       </c>
+      <c r="D2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E2" t="s">
+        <v>136</v>
+      </c>
       <c r="F2" s="15" t="s">
         <v>86</v>
       </c>
@@ -2652,7 +2718,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F24 F5">
+  <conditionalFormatting sqref="F5 F24">
     <cfRule type="dataBar" priority="34">
       <dataBar>
         <cfvo type="min"/>
@@ -3173,7 +3239,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>F24 F5</xm:sqref>
+          <xm:sqref>F5 F24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{39E40594-1983-4307-8FCC-CD695BAE4F9D}">
@@ -3472,6 +3538,12 @@
       <c r="C3" t="s">
         <v>259</v>
       </c>
+      <c r="D3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E3" t="s">
+        <v>323</v>
+      </c>
       <c r="F3" s="7" t="s">
         <v>189</v>
       </c>
@@ -3492,6 +3564,12 @@
       <c r="C4" t="s">
         <v>53</v>
       </c>
+      <c r="D4" t="s">
+        <v>326</v>
+      </c>
+      <c r="E4" t="s">
+        <v>325</v>
+      </c>
       <c r="F4" s="8" t="s">
         <v>190</v>
       </c>
@@ -3512,6 +3590,12 @@
       <c r="C5" t="s">
         <v>51</v>
       </c>
+      <c r="D5" t="s">
+        <v>328</v>
+      </c>
+      <c r="E5" t="s">
+        <v>327</v>
+      </c>
       <c r="F5" s="7" t="s">
         <v>191</v>
       </c>
@@ -3532,6 +3616,12 @@
       <c r="C6" t="s">
         <v>232</v>
       </c>
+      <c r="D6" t="s">
+        <v>329</v>
+      </c>
+      <c r="E6" t="s">
+        <v>330</v>
+      </c>
       <c r="F6" s="8" t="s">
         <v>192</v>
       </c>
@@ -3552,6 +3642,12 @@
       <c r="C7" t="s">
         <v>233</v>
       </c>
+      <c r="D7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E7" t="s">
+        <v>331</v>
+      </c>
       <c r="F7" s="7" t="s">
         <v>193</v>
       </c>
@@ -3572,6 +3668,12 @@
       <c r="C8" t="s">
         <v>260</v>
       </c>
+      <c r="D8" t="s">
+        <v>333</v>
+      </c>
+      <c r="E8" t="s">
+        <v>334</v>
+      </c>
       <c r="F8" s="8" t="s">
         <v>194</v>
       </c>
@@ -3592,6 +3694,12 @@
       <c r="C9" t="s">
         <v>261</v>
       </c>
+      <c r="D9" t="s">
+        <v>336</v>
+      </c>
+      <c r="E9" t="s">
+        <v>335</v>
+      </c>
       <c r="F9" s="7" t="s">
         <v>195</v>
       </c>
@@ -3612,6 +3720,12 @@
       <c r="C10" t="s">
         <v>56</v>
       </c>
+      <c r="D10" t="s">
+        <v>338</v>
+      </c>
+      <c r="E10" t="s">
+        <v>337</v>
+      </c>
       <c r="F10" s="8" t="s">
         <v>89</v>
       </c>
@@ -3911,10 +4025,10 @@
         <v>65</v>
       </c>
       <c r="D24" t="s">
-        <v>133</v>
+        <v>320</v>
       </c>
       <c r="E24" t="s">
-        <v>134</v>
+        <v>319</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>206</v>
@@ -3936,6 +4050,12 @@
       <c r="C25" t="s">
         <v>67</v>
       </c>
+      <c r="D25" t="s">
+        <v>133</v>
+      </c>
+      <c r="E25" t="s">
+        <v>134</v>
+      </c>
       <c r="F25" s="7" t="s">
         <v>207</v>
       </c>
@@ -4096,6 +4216,12 @@
       <c r="C33" t="s">
         <v>53</v>
       </c>
+      <c r="D33" t="s">
+        <v>321</v>
+      </c>
+      <c r="E33" t="s">
+        <v>322</v>
+      </c>
       <c r="F33" s="7" t="s">
         <v>214</v>
       </c>
@@ -4202,7 +4328,9 @@
       <c r="G38" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="H38" s="8"/>
+      <c r="H38" s="10">
+        <v>259127941</v>
+      </c>
     </row>
     <row r="39" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39">
@@ -4775,6 +4903,9 @@
     <hyperlink ref="F3" r:id="rId89" xr:uid="{7A5D1D71-DE48-4DD9-9316-407A20F3BA8B}"/>
     <hyperlink ref="F51" r:id="rId90" xr:uid="{B2556BAB-0652-48C9-AB95-99BDB764EB0D}"/>
     <hyperlink ref="F38" r:id="rId91" xr:uid="{9398E282-056F-4E66-A793-BF21B766E0E9}"/>
+    <hyperlink ref="G6" r:id="rId92" xr:uid="{1D28B480-C842-4291-9517-40E04BBACE3E}"/>
+    <hyperlink ref="G8" r:id="rId93" xr:uid="{56B6B4CA-AFAD-4C2A-A40E-B3D5053A9BA5}"/>
+    <hyperlink ref="G9" r:id="rId94" xr:uid="{BAB6F0B5-8BE9-4611-A4F7-5AAC0A0080D3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>

--- a/Dados.xlsx
+++ b/Dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/paulo_martins_tja_pt/Documents/Dep. Formação/Ambiente Formadores/Mercadona HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="147" documentId="8_{3ECB6CA0-9746-43FE-8E62-14652AAF4818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD3DBDE7-5970-4091-9F14-1B8649B0E4FE}"/>
+  <xr:revisionPtr revIDLastSave="157" documentId="8_{3ECB6CA0-9746-43FE-8E62-14652AAF4818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8FA41AD-EF08-40F7-8B17-AA00942E07FF}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{462C5653-B832-456D-BA7D-C78D43202BCF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{462C5653-B832-456D-BA7D-C78D43202BCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Almeirim" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="344">
   <si>
     <t>Número</t>
   </si>
@@ -1054,6 +1054,21 @@
   </si>
   <si>
     <t>R. de Domingos Sequeira 225, 4050-424 Porto</t>
+  </si>
+  <si>
+    <t>R. Capitao Salgueiro Maia 30, 4835-400 Silvares</t>
+  </si>
+  <si>
+    <t>41.444810976324035, -8.340040818950758</t>
+  </si>
+  <si>
+    <t>41.4362439391197, -8.298584672182127</t>
+  </si>
+  <si>
+    <t>R. Eduardo Manuel de Almeida 530, 4810-225 Guimarães</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1raHznT-Ny7-5DvWbcBuBH-E3yOWIq4-N/view?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -1192,7 +1207,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1279,6 +1294,7 @@
     <xf numFmtId="20" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperligação" xfId="1" builtinId="8"/>
@@ -1831,6 +1847,9 @@
       </c>
       <c r="I10" s="23">
         <v>221202915</v>
+      </c>
+      <c r="J10" s="30" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -3070,9 +3089,10 @@
     <hyperlink ref="G32" r:id="rId69" xr:uid="{37478915-48E4-410E-BB3A-6D3C6CC567B0}"/>
     <hyperlink ref="G43" r:id="rId70" xr:uid="{7348BB3D-FF9C-460B-9003-572F3EA88A9B}"/>
     <hyperlink ref="G41" r:id="rId71" xr:uid="{7ADBC77E-D7EE-4619-9DF3-D9D75ADFABA5}"/>
+    <hyperlink ref="J10" r:id="rId72" xr:uid="{CE973074-73E2-49D3-A0C3-26B5C4F2A00C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId72"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId73"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -3461,9 +3481,9 @@
   <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.109375" customWidth="1"/>
-    <col min="2" max="2" width="31.77734375" customWidth="1"/>
-    <col min="3" max="3" width="18.109375" customWidth="1"/>
+    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.21875" customWidth="1"/>
     <col min="5" max="5" width="31.6640625" customWidth="1"/>
     <col min="6" max="6" width="24.33203125" customWidth="1"/>
@@ -3772,6 +3792,12 @@
       <c r="C12" t="s">
         <v>262</v>
       </c>
+      <c r="D12" t="s">
+        <v>339</v>
+      </c>
+      <c r="E12" t="s">
+        <v>340</v>
+      </c>
       <c r="F12" s="8" t="s">
         <v>197</v>
       </c>
@@ -3792,6 +3818,12 @@
       <c r="C13" t="s">
         <v>263</v>
       </c>
+      <c r="D13" t="s">
+        <v>342</v>
+      </c>
+      <c r="E13" t="s">
+        <v>341</v>
+      </c>
       <c r="F13" s="7" t="s">
         <v>197</v>
       </c>
@@ -3868,7 +3900,7 @@
         <v>221202916</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>7015</v>
       </c>
@@ -3888,7 +3920,7 @@
         <v>221205058</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>7016</v>
       </c>
@@ -3908,7 +3940,7 @@
         <v>221202912</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>7017</v>
       </c>
@@ -3934,7 +3966,7 @@
         <v>256120002</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>7018</v>
       </c>
@@ -3954,7 +3986,7 @@
         <v>258127880</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>7019</v>
       </c>
@@ -3974,7 +4006,7 @@
         <v>221202913</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>7020</v>
       </c>
@@ -3993,8 +4025,11 @@
       <c r="H22" s="10">
         <v>221202915</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I22" s="30" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>7021</v>
       </c>
@@ -4014,7 +4049,7 @@
         <v>221202917</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>7022</v>
       </c>
@@ -4040,7 +4075,7 @@
         <v>256120004</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>7023</v>
       </c>
@@ -4066,7 +4101,7 @@
         <v>256120003</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>7025</v>
       </c>
@@ -4086,7 +4121,7 @@
         <v>253127944</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>7026</v>
       </c>
@@ -4106,7 +4141,7 @@
         <v>253120210</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>7027</v>
       </c>
@@ -4126,7 +4161,7 @@
         <v>221202920</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>7028</v>
       </c>
@@ -4146,7 +4181,7 @@
         <v>221202914</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>7029</v>
       </c>
@@ -4166,7 +4201,7 @@
         <v>221202919</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>7030</v>
       </c>
@@ -4186,7 +4221,7 @@
         <v>221202921</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>7031</v>
       </c>
@@ -4906,6 +4941,8 @@
     <hyperlink ref="G6" r:id="rId92" xr:uid="{1D28B480-C842-4291-9517-40E04BBACE3E}"/>
     <hyperlink ref="G8" r:id="rId93" xr:uid="{56B6B4CA-AFAD-4C2A-A40E-B3D5053A9BA5}"/>
     <hyperlink ref="G9" r:id="rId94" xr:uid="{BAB6F0B5-8BE9-4611-A4F7-5AAC0A0080D3}"/>
+    <hyperlink ref="G13" r:id="rId95" xr:uid="{3C282117-15DF-4E03-8857-1DD40EDA9FBF}"/>
+    <hyperlink ref="I22" r:id="rId96" xr:uid="{F440581C-EE3F-4102-9F1C-658DEDB2E9BC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>

--- a/Dados.xlsx
+++ b/Dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/paulo_martins_tja_pt/Documents/Dep. Formação/Ambiente Formadores/Mercadona HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="157" documentId="8_{3ECB6CA0-9746-43FE-8E62-14652AAF4818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8FA41AD-EF08-40F7-8B17-AA00942E07FF}"/>
+  <xr:revisionPtr revIDLastSave="191" documentId="8_{3ECB6CA0-9746-43FE-8E62-14652AAF4818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{272106F4-1419-4A9E-99CB-09574A32E3AE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{462C5653-B832-456D-BA7D-C78D43202BCF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{462C5653-B832-456D-BA7D-C78D43202BCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Almeirim" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="355">
   <si>
     <t>Número</t>
   </si>
@@ -1069,6 +1069,39 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1raHznT-Ny7-5DvWbcBuBH-E3yOWIq4-N/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1orsus1RBOw-k7LYJupf8lMFA6jYKuHXP/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1TUfK5EkFFw4bmGbvQQddG1eOLfrsuEju/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1SDp_s00ltBxWvENQ8Q1ogjWqaBRjdZRj/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ZGpoesrb_i79GTnkkZ6qwZrgBcB8PUaa/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1OnoruMAnq-EIt1OFJ_MCMxArpF19hLah/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1_8Q2q5I7SkeNQqNs7Wj-9fDfI3OnBypH/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1cHoIHfwWbQgsAlWntGJaHwi5apvV84rd/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/16xWkKwC5UVjXyZRUUdWA541SfH8PAy-r/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1k76T8VW6Z3wJCdez7NxBqG1R7z8S8QLd/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1PO1FvUIoJkBqdkEJi1ge_Nn9liQIgyCu/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1e-T16UQ6uh9oCKt0rmLAT1S9VJ-uXotk/view?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -1124,7 +1157,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1146,6 +1179,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1207,7 +1246,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1229,9 +1268,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1258,50 +1294,117 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="20" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="5" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="20" fontId="5" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperligação" xfId="1" builtinId="8"/>
     <cellStyle name="Hyperlink" xfId="2" xr:uid="{66064622-232A-4B66-8D8E-344707DA0960}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1312,6 +1415,51 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4CADE461-DCE6-4D4D-A4A1-D312A88E939C}" name="Tabela2" displayName="Tabela2" ref="A1:K45" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:K45" xr:uid="{4CADE461-DCE6-4D4D-A4A1-D312A88E939C}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K45">
+    <sortCondition ref="A1:A45"/>
+  </sortState>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{DC55ED28-0E01-4284-9ADF-4C1C7E0BA32F}" name="Número" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{C5B39310-F969-45B5-80D4-34581D61F882}" name="Nome"/>
+    <tableColumn id="3" xr3:uid="{E2DFD2FD-2B5F-44FC-9C74-960CC47BDC31}" name="Localidade"/>
+    <tableColumn id="4" xr3:uid="{85FD4A60-9779-4E9B-830A-D6B5030AE8F9}" name="Morada"/>
+    <tableColumn id="5" xr3:uid="{C055D503-08E5-453C-8C5E-766522EFDFFA}" name="Coordenadas"/>
+    <tableColumn id="6" xr3:uid="{825D9359-5344-423D-978D-9EFF317010C6}" name="Ponto espera"/>
+    <tableColumn id="7" xr3:uid="{AD1E5214-E233-4B8B-82E4-596C493537D6}" name="Precurso"/>
+    <tableColumn id="8" xr3:uid="{382149AB-CE26-4792-97B6-6A989B144FA1}" name="Notas"/>
+    <tableColumn id="9" xr3:uid="{B66F1DB3-0B8D-431F-B635-14A85E95294F}" name="Contacto" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{805F075D-1C25-4A2C-95E3-BDA9D56884C7}" name="Video1"/>
+    <tableColumn id="11" xr3:uid="{165EE159-A814-4F41-9A23-55982F96B1AB}" name="Video2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{91A3505B-8507-465E-8681-5F21BB7987AE}" name="Tabela1" displayName="Tabela1" ref="A1:J51" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="A1:J51" xr:uid="{91A3505B-8507-465E-8681-5F21BB7987AE}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J51">
+    <sortCondition ref="A1:A51"/>
+  </sortState>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{069BCA38-6B9A-40B4-AC25-8BB8526B976B}" name="Número"/>
+    <tableColumn id="2" xr3:uid="{F299F84D-5579-4D6A-9ADC-DA7C0C2CBB0D}" name="Nome"/>
+    <tableColumn id="3" xr3:uid="{76679A00-7A8C-48AA-A878-C65F2B3C0445}" name="Localidade"/>
+    <tableColumn id="4" xr3:uid="{5920DD92-8FA3-433A-877F-5DF02D347F13}" name="Morada"/>
+    <tableColumn id="5" xr3:uid="{B9B71405-06AE-45A4-9FBA-1A03F8177D30}" name="Coordenadas"/>
+    <tableColumn id="6" xr3:uid="{A0C70671-7EDF-4973-AE91-F0DCFCCF4963}" name="Ponto espera" dataDxfId="5" dataCellStyle="Hiperligação"/>
+    <tableColumn id="7" xr3:uid="{D109BFE1-D3EF-4CEB-9900-118FDB6D6828}" name="Precurso" dataDxfId="4" dataCellStyle="Hiperligação"/>
+    <tableColumn id="8" xr3:uid="{ADF2BDD4-E4CC-4BBF-981A-CE374898476C}" name="Contacto"/>
+    <tableColumn id="9" xr3:uid="{A55694C5-7C05-4149-B919-7D119BE88CA0}" name="Video1"/>
+    <tableColumn id="10" xr3:uid="{C68AC60C-A3CF-43FD-9343-E9FD59397C89}" name="Video2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1614,50 +1762,50 @@
   <dimension ref="A1:K45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="30.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="3" max="3" width="18.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="33.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="36.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="39.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="39.6640625" customWidth="1"/>
-    <col min="9" max="9" width="18.5546875" style="23" customWidth="1"/>
+    <col min="6" max="6" width="15" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="7.77734375" customWidth="1"/>
+    <col min="9" max="9" width="10.88671875" style="19" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="18.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="22" t="s">
         <v>49</v>
       </c>
       <c r="I1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="22" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1677,14 +1825,14 @@
       <c r="E2" t="s">
         <v>136</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="14" t="s">
         <v>86</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>107</v>
       </c>
       <c r="H2" s="3"/>
-      <c r="I2" s="23">
+      <c r="I2" s="19">
         <v>221201095</v>
       </c>
       <c r="J2" s="2"/>
@@ -1699,13 +1847,13 @@
       <c r="C3" t="s">
         <v>53</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="15" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="19">
         <v>221201094</v>
       </c>
     </row>
@@ -1719,14 +1867,17 @@
       <c r="C4" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="16" t="s">
         <v>88</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="I4" s="23">
+      <c r="I4" s="19">
         <v>221205059</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -1739,13 +1890,13 @@
       <c r="C5" t="s">
         <v>56</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="I5" s="23">
+      <c r="I5" s="19">
         <v>221205056</v>
       </c>
     </row>
@@ -1759,13 +1910,13 @@
       <c r="C6" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="15" t="s">
         <v>12</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="23">
+      <c r="I6" s="19">
         <v>221205057</v>
       </c>
     </row>
@@ -1779,13 +1930,13 @@
       <c r="C7" t="s">
         <v>59</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="14" t="s">
         <v>90</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="19">
         <v>256120000</v>
       </c>
     </row>
@@ -1799,13 +1950,13 @@
       <c r="C8" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="15" t="s">
         <v>91</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="19">
         <v>221205058</v>
       </c>
     </row>
@@ -1819,13 +1970,13 @@
       <c r="C9" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="14" t="s">
         <v>92</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="I9" s="23">
+      <c r="I9" s="19">
         <v>256120002</v>
       </c>
     </row>
@@ -1839,16 +1990,16 @@
       <c r="C10" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="15" t="s">
         <v>93</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="I10" s="23">
+      <c r="I10" s="19">
         <v>221202915</v>
       </c>
-      <c r="J10" s="30" t="s">
+      <c r="J10" s="20" t="s">
         <v>343</v>
       </c>
     </row>
@@ -1862,14 +2013,17 @@
       <c r="C11" t="s">
         <v>65</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="14" t="s">
         <v>94</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="I11" s="23">
+      <c r="I11" s="19">
         <v>256120004</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -1882,13 +2036,13 @@
       <c r="C12" t="s">
         <v>67</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="15" t="s">
         <v>95</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="19">
         <v>256120003</v>
       </c>
     </row>
@@ -1902,11 +2056,11 @@
       <c r="C13" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="15"/>
+      <c r="F13" s="14"/>
       <c r="G13" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="I13" s="23">
+      <c r="I13" s="19">
         <v>221202919</v>
       </c>
     </row>
@@ -1920,551 +2074,563 @@
       <c r="C14" t="s">
         <v>70</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="17" t="s">
         <v>96</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="19">
         <v>256120250</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <v>7034</v>
+        <v>7033</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="I15" s="23">
-        <v>221202922</v>
+        <v>46</v>
+      </c>
+      <c r="F15" s="24" t="s">
+        <v>278</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>298</v>
+      </c>
+      <c r="I15" s="19">
+        <v>265121501</v>
+      </c>
+      <c r="J15" s="20" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
+        <v>7034</v>
+      </c>
+      <c r="B16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="I16" s="19">
+        <v>221202922</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>7036</v>
+      </c>
+      <c r="B17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="G17" s="26" t="s">
+        <v>299</v>
+      </c>
+      <c r="I17" s="19">
+        <v>211202941</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
         <v>7037</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B18" t="s">
         <v>72</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C18" t="s">
         <v>73</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="F18" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G18" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="I16" s="23">
+      <c r="I18" s="19">
         <v>256120252</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
+    <row r="19" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
         <v>7038</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B19" t="s">
         <v>74</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C19" t="s">
         <v>75</v>
       </c>
-      <c r="F17" s="21" t="s">
+      <c r="F19" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G19" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="I17" s="23">
+      <c r="I19" s="19">
         <v>233120010</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
+    <row r="20" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
         <v>7040</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B20" t="s">
         <v>76</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C20" t="s">
         <v>77</v>
       </c>
-      <c r="F18" s="16" t="s">
+      <c r="F20" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G20" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I18" s="23">
+      <c r="I20" s="19">
         <v>232120210</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
+    <row r="21" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>7041</v>
+      </c>
+      <c r="B21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="25" t="s">
+        <v>280</v>
+      </c>
+      <c r="G21" s="24" t="s">
+        <v>300</v>
+      </c>
+      <c r="I21" s="19">
+        <v>211202943</v>
+      </c>
+      <c r="J21" s="20" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>7044</v>
+      </c>
+      <c r="B22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="26" t="s">
+        <v>281</v>
+      </c>
+      <c r="G22" s="26" t="s">
+        <v>301</v>
+      </c>
+      <c r="I22" s="19">
+        <v>211202942</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
         <v>7045</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B23" t="s">
         <v>78</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C23" t="s">
         <v>79</v>
       </c>
-      <c r="F19" s="17" t="s">
+      <c r="F23" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G23" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="I19" s="23">
+      <c r="I23" s="19">
         <v>256120251</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
+    <row r="24" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>7046</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" s="30" t="s">
+        <v>282</v>
+      </c>
+      <c r="G24" s="31" t="s">
+        <v>302</v>
+      </c>
+      <c r="I24" s="19">
+        <v>243120160</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>7048</v>
+      </c>
+      <c r="B25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" t="s">
+        <v>35</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>283</v>
+      </c>
+      <c r="G25" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="I25" s="19">
+        <v>211202946</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>7049</v>
+      </c>
+      <c r="B26" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" t="s">
+        <v>37</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>284</v>
+      </c>
+      <c r="G26" s="24" t="s">
+        <v>304</v>
+      </c>
+      <c r="I26" s="19">
+        <v>262130010</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>7054</v>
+      </c>
+      <c r="B27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" t="s">
+        <v>35</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>285</v>
+      </c>
+      <c r="G27" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="I27" s="19">
+        <v>211202945</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>7055</v>
+      </c>
+      <c r="B28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="G28" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="I28" s="19">
+        <v>261133001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
         <v>7056</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B29" t="s">
         <v>80</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C29" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="20" t="s">
+      <c r="F29" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G29" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="I20" s="23">
+      <c r="I29" s="19">
         <v>221202923</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
-        <v>7066</v>
-      </c>
-      <c r="B21" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" t="s">
-        <v>82</v>
-      </c>
-      <c r="F21" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="I21" s="23">
-        <v>239127942</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
-        <v>7064</v>
-      </c>
-      <c r="B22" t="s">
-        <v>83</v>
-      </c>
-      <c r="C22" t="s">
-        <v>82</v>
-      </c>
-      <c r="F22" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="I22" s="23">
-        <v>239127941</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
-        <v>7067</v>
-      </c>
-      <c r="B23" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" t="s">
-        <v>84</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="I23" s="23">
-        <v>271127941</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
-        <v>7078</v>
-      </c>
-      <c r="B24" t="s">
-        <v>85</v>
-      </c>
-      <c r="C24" t="s">
-        <v>56</v>
-      </c>
-      <c r="F24" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="I24" s="23">
-        <v>221201005</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
-        <v>7033</v>
-      </c>
-      <c r="B25" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" t="s">
-        <v>46</v>
-      </c>
-      <c r="F25" s="24" t="s">
-        <v>278</v>
-      </c>
-      <c r="G25" s="24" t="s">
-        <v>298</v>
-      </c>
-      <c r="I25" s="23">
-        <v>265121501</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
-        <v>7036</v>
-      </c>
-      <c r="B26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" t="s">
-        <v>44</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="G26" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="I26" s="23">
-        <v>211202941</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
-        <v>7041</v>
-      </c>
-      <c r="B27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" t="s">
-        <v>42</v>
-      </c>
-      <c r="F27" s="25" t="s">
-        <v>280</v>
-      </c>
-      <c r="G27" s="24" t="s">
-        <v>300</v>
-      </c>
-      <c r="I27" s="23">
-        <v>211202943</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
-        <v>7044</v>
-      </c>
-      <c r="B28" t="s">
-        <v>41</v>
-      </c>
-      <c r="C28" t="s">
-        <v>35</v>
-      </c>
-      <c r="F28" s="26" t="s">
-        <v>281</v>
-      </c>
-      <c r="G28" s="26" t="s">
-        <v>301</v>
-      </c>
-      <c r="I28" s="23">
-        <v>211202942</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
-        <v>7046</v>
-      </c>
-      <c r="B29" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" t="s">
-        <v>39</v>
-      </c>
-      <c r="F29" s="25" t="s">
-        <v>282</v>
-      </c>
-      <c r="G29" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="I29" s="23">
-        <v>243120160</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <v>7048</v>
+        <v>7057</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C30" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="G30" s="26" t="s">
-        <v>303</v>
-      </c>
-      <c r="I30" s="23">
-        <v>211202946</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+        <v>307</v>
+      </c>
+      <c r="I30" s="19">
+        <v>211202951</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <v>7049</v>
+        <v>7058</v>
       </c>
       <c r="B31" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C31" t="s">
-        <v>37</v>
-      </c>
-      <c r="F31" s="24" t="s">
-        <v>284</v>
+        <v>31</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>288</v>
       </c>
       <c r="G31" s="24" t="s">
-        <v>304</v>
-      </c>
-      <c r="I31" s="23">
-        <v>262130010</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+        <v>308</v>
+      </c>
+      <c r="I31" s="19">
+        <v>263137011</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <v>7054</v>
+        <v>7060</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>35</v>
-      </c>
-      <c r="F32" s="26" t="s">
-        <v>285</v>
+        <v>30</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>289</v>
       </c>
       <c r="G32" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="I32" s="23">
-        <v>211202945</v>
+        <v>309</v>
+      </c>
+      <c r="I32" s="19">
+        <v>266127951</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
-        <v>7055</v>
+        <v>7061</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C33" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F33" s="24" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="G33" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="I33" s="23">
-        <v>261133001</v>
+        <v>310</v>
+      </c>
+      <c r="I33" s="19">
+        <v>265121502</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
-        <v>7057</v>
+        <v>7064</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="C34" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" s="26" t="s">
-        <v>287</v>
-      </c>
-      <c r="G34" s="26" t="s">
-        <v>307</v>
-      </c>
-      <c r="I34" s="23">
-        <v>211202951</v>
+        <v>82</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="I34" s="19">
+        <v>239127941</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
-        <v>7058</v>
+        <v>7066</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="C35" t="s">
-        <v>31</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="G35" s="24" t="s">
-        <v>308</v>
-      </c>
-      <c r="I35" s="23">
-        <v>263137011</v>
+        <v>82</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="I35" s="19">
+        <v>239127942</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
-        <v>7060</v>
+        <v>7067</v>
       </c>
       <c r="B36" t="s">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="C36" t="s">
-        <v>30</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="G36" s="26" t="s">
-        <v>309</v>
-      </c>
-      <c r="I36" s="23">
-        <v>266127951</v>
+        <v>84</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="I36" s="19">
+        <v>271127941</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
-        <v>7061</v>
+        <v>7068</v>
       </c>
       <c r="B37" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C37" t="s">
-        <v>28</v>
-      </c>
-      <c r="F37" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="G37" s="24" t="s">
-        <v>310</v>
-      </c>
-      <c r="I37" s="23">
-        <v>265121502</v>
+        <v>26</v>
+      </c>
+      <c r="F37" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="G37" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="I37" s="19">
+        <v>211202947</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
-        <v>7068</v>
+        <v>7069</v>
       </c>
       <c r="B38" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C38" t="s">
-        <v>26</v>
-      </c>
-      <c r="F38" s="26" t="s">
-        <v>291</v>
-      </c>
-      <c r="G38" s="26" t="s">
-        <v>311</v>
-      </c>
-      <c r="I38" s="23">
-        <v>211202947</v>
+        <v>18</v>
+      </c>
+      <c r="F38" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="G38" s="24" t="s">
+        <v>312</v>
+      </c>
+      <c r="I38" s="19">
+        <v>244122590</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
-        <v>7069</v>
+        <v>7073</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
-      </c>
-      <c r="F39" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="G39" s="24" t="s">
-        <v>312</v>
-      </c>
-      <c r="I39" s="23">
-        <v>244122590</v>
+        <v>24</v>
+      </c>
+      <c r="F39" s="27" t="s">
+        <v>293</v>
+      </c>
+      <c r="G39" s="26" t="s">
+        <v>313</v>
+      </c>
+      <c r="I39" s="19">
+        <v>910759388</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
-        <v>7073</v>
+        <v>7076</v>
       </c>
       <c r="B40" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C40" t="s">
-        <v>24</v>
-      </c>
-      <c r="F40" s="27" t="s">
-        <v>293</v>
-      </c>
-      <c r="G40" s="26" t="s">
-        <v>313</v>
-      </c>
-      <c r="I40" s="23">
-        <v>910759388</v>
+        <v>22</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
-        <v>7076</v>
+        <v>7078</v>
       </c>
       <c r="B41" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="C41" t="s">
-        <v>22</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>314</v>
+        <v>56</v>
+      </c>
+      <c r="F41" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I41" s="19">
+        <v>221201005</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
@@ -2483,7 +2649,7 @@
       <c r="G42" s="26" t="s">
         <v>315</v>
       </c>
-      <c r="I42" s="23">
+      <c r="I42" s="19">
         <v>211202948</v>
       </c>
     </row>
@@ -2497,13 +2663,13 @@
       <c r="C43" t="s">
         <v>18</v>
       </c>
-      <c r="F43" s="8" t="s">
+      <c r="F43" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="G43" s="8" t="s">
+      <c r="G43" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="I43" s="23">
+      <c r="I43" s="19">
         <v>244122591</v>
       </c>
     </row>
@@ -2517,13 +2683,13 @@
       <c r="C44" t="s">
         <v>16</v>
       </c>
-      <c r="F44" s="7" t="s">
+      <c r="F44" s="6" t="s">
         <v>297</v>
       </c>
       <c r="G44" s="29" t="s">
         <v>317</v>
       </c>
-      <c r="I44" s="23" t="s">
+      <c r="I44" s="19" t="s">
         <v>318</v>
       </c>
     </row>
@@ -2541,6 +2707,9 @@
       <c r="G45" s="24"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K45">
+    <sortCondition ref="A1:A45"/>
+  </sortState>
   <conditionalFormatting sqref="F2">
     <cfRule type="dataBar" priority="33">
       <dataBar>
@@ -3024,75 +3193,85 @@
     <hyperlink ref="F5" r:id="rId4" xr:uid="{4EF6DB39-DFA9-410F-8652-639EF692ED5C}"/>
     <hyperlink ref="F10" r:id="rId5" xr:uid="{EADE799A-2C0B-45FA-9BE7-89C2CC7644BC}"/>
     <hyperlink ref="F14" r:id="rId6" xr:uid="{CE167075-E8A1-496D-B4E3-34C35ABE1343}"/>
-    <hyperlink ref="F19" r:id="rId7" xr:uid="{64141498-D306-4BF4-9EAB-A220EC8CD602}"/>
+    <hyperlink ref="F23" r:id="rId7" xr:uid="{64141498-D306-4BF4-9EAB-A220EC8CD602}"/>
     <hyperlink ref="F11" r:id="rId8" display="https://www.google.com/maps/place/41%C2%B001'32.5%22N+8%C2%B037'15.2%22W/@41.025699,-8.625366,17z/data=!3m1!4b1!4m13!1m8!3m7!1s0xd2479c7cd31a89b:0x73c82fb2f5e003f8!2sEspinho,+Portugal!3b1!8m2!3d41.0071914!4d-8.6410332!16zL20vMDNqMGs4!3m3!8m2!3d41.025695!4d-8.620876" xr:uid="{F75CF23D-ACA1-47D8-8C50-89E09910692F}"/>
-    <hyperlink ref="F15" r:id="rId9" xr:uid="{3F111C1D-3490-4FE6-880A-AA5616060957}"/>
+    <hyperlink ref="F16" r:id="rId9" xr:uid="{3F111C1D-3490-4FE6-880A-AA5616060957}"/>
     <hyperlink ref="F12" r:id="rId10" xr:uid="{BAFBA4C9-E0EB-4328-B5AE-231BC879BB0B}"/>
-    <hyperlink ref="F20" r:id="rId11" display="https://www.google.com/maps/@41.0845386,-8.6187478,3a,75y,110.4h,90t/data=!3m7!1e1!3m5!1sLIYhBDg9FYzt7FcbWR5jZw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D0%26panoid%3DLIYhBDg9FYzt7FcbWR5jZw%26yaw%3D110.4041920217924!7i16384!8i8192?coh=205410&amp;entry=ttu&amp;g_ep=EgoyMDI0MDkyOS4wIKXMDSoASAFQAw%3D%3D" xr:uid="{6083FFBA-D043-4CE8-938E-FD7897302C90}"/>
-    <hyperlink ref="F18" r:id="rId12" display="https://www.google.com/maps/place/Repsol+A25+Viseu+(sul)/@40.623534,-7.930495,17z/data=!4m14!1m7!3m6!1s0xd233706899600ed:0xb5ac567012a36aae!2sMercadona+Viseu!8m2!3d40.6326254!4d-7.9091179!16s%2Fg%2F11s2j25vhc!3m5!1s0xd23373e65fbfa6b:0x2354da54d5b13e37!8m2!3d40.623897!4d-7.933134!16s%2Fg%2F11bvcvn15h" xr:uid="{F197E301-F17A-4CC3-ADC3-8A802FCB1DAD}"/>
-    <hyperlink ref="F16" r:id="rId13" xr:uid="{B876396C-9A69-4EDB-9295-D1229F4E64B1}"/>
+    <hyperlink ref="F29" r:id="rId11" display="https://www.google.com/maps/@41.0845386,-8.6187478,3a,75y,110.4h,90t/data=!3m7!1e1!3m5!1sLIYhBDg9FYzt7FcbWR5jZw!2e0!6shttps:%2F%2Fstreetviewpixels-pa.googleapis.com%2Fv1%2Fthumbnail%3Fcb_client%3Dmaps_sv.tactile%26w%3D900%26h%3D600%26pitch%3D0%26panoid%3DLIYhBDg9FYzt7FcbWR5jZw%26yaw%3D110.4041920217924!7i16384!8i8192?coh=205410&amp;entry=ttu&amp;g_ep=EgoyMDI0MDkyOS4wIKXMDSoASAFQAw%3D%3D" xr:uid="{6083FFBA-D043-4CE8-938E-FD7897302C90}"/>
+    <hyperlink ref="F20" r:id="rId12" display="https://www.google.com/maps/place/Repsol+A25+Viseu+(sul)/@40.623534,-7.930495,17z/data=!4m14!1m7!3m6!1s0xd233706899600ed:0xb5ac567012a36aae!2sMercadona+Viseu!8m2!3d40.6326254!4d-7.9091179!16s%2Fg%2F11s2j25vhc!3m5!1s0xd23373e65fbfa6b:0x2354da54d5b13e37!8m2!3d40.623897!4d-7.933134!16s%2Fg%2F11bvcvn15h" xr:uid="{F197E301-F17A-4CC3-ADC3-8A802FCB1DAD}"/>
+    <hyperlink ref="F18" r:id="rId13" xr:uid="{B876396C-9A69-4EDB-9295-D1229F4E64B1}"/>
     <hyperlink ref="F6" r:id="rId14" xr:uid="{99DFDA68-E962-477D-B89E-A713E131D40D}"/>
     <hyperlink ref="F7" r:id="rId15" xr:uid="{5D906E3A-6D8A-4645-BE7A-5A8F269E45DD}"/>
     <hyperlink ref="F9" r:id="rId16" xr:uid="{13662DC7-E1F1-48E3-A661-8A7991B40B65}"/>
-    <hyperlink ref="F17" r:id="rId17" xr:uid="{94659B98-BC17-44DA-9327-5B1572CCD288}"/>
-    <hyperlink ref="F22" r:id="rId18" xr:uid="{F860D09E-C87F-407E-8D33-A47DC94D2BDE}"/>
-    <hyperlink ref="F21" r:id="rId19" xr:uid="{2613AD08-857D-44EE-A354-09319A3CD507}"/>
-    <hyperlink ref="F23" r:id="rId20" xr:uid="{F26A824F-461F-44B6-9263-1944883781FB}"/>
+    <hyperlink ref="F19" r:id="rId17" xr:uid="{94659B98-BC17-44DA-9327-5B1572CCD288}"/>
+    <hyperlink ref="F34" r:id="rId18" xr:uid="{F860D09E-C87F-407E-8D33-A47DC94D2BDE}"/>
+    <hyperlink ref="F35" r:id="rId19" xr:uid="{2613AD08-857D-44EE-A354-09319A3CD507}"/>
+    <hyperlink ref="F36" r:id="rId20" xr:uid="{F26A824F-461F-44B6-9263-1944883781FB}"/>
     <hyperlink ref="G5" r:id="rId21" xr:uid="{AA4EC664-5239-4F8D-8BB9-C63DAAE26FC3}"/>
-    <hyperlink ref="G21" r:id="rId22" xr:uid="{893B243F-8BF3-4624-A6F6-0EC6D481A87E}"/>
+    <hyperlink ref="G35" r:id="rId22" xr:uid="{893B243F-8BF3-4624-A6F6-0EC6D481A87E}"/>
     <hyperlink ref="G7" r:id="rId23" xr:uid="{43253076-819D-4877-A211-5DE4F410F4AB}"/>
     <hyperlink ref="G8" r:id="rId24" xr:uid="{E4141D76-C388-4B41-AECE-D563C5EAFFFF}"/>
-    <hyperlink ref="G17" r:id="rId25" xr:uid="{A24151DC-2EC4-4945-84FD-04E1CFEABCC5}"/>
-    <hyperlink ref="G23" r:id="rId26" xr:uid="{49E2B942-8BCD-499E-BE5F-B8AE53E17BF5}"/>
+    <hyperlink ref="G19" r:id="rId25" xr:uid="{A24151DC-2EC4-4945-84FD-04E1CFEABCC5}"/>
+    <hyperlink ref="G36" r:id="rId26" xr:uid="{49E2B942-8BCD-499E-BE5F-B8AE53E17BF5}"/>
     <hyperlink ref="G6" r:id="rId27" xr:uid="{E43A11FB-95EE-47D6-8783-54F24B4ED229}"/>
     <hyperlink ref="G9" r:id="rId28" xr:uid="{20FE1184-92A7-4E96-ADDA-58FB3015AAAD}"/>
     <hyperlink ref="G10" r:id="rId29" xr:uid="{8A4BDC97-0438-44A1-A0A9-0F93CFDAD5D4}"/>
     <hyperlink ref="G11" r:id="rId30" xr:uid="{48508D98-59F5-4524-846C-F11A0CE004F1}"/>
     <hyperlink ref="G12" r:id="rId31" xr:uid="{30CDAFA9-F37A-4E02-BEF0-FCCB6A09D2C8}"/>
     <hyperlink ref="G13" r:id="rId32" xr:uid="{F87E3F1A-9105-483D-A2B7-C7F19D613F2E}"/>
-    <hyperlink ref="G15" r:id="rId33" xr:uid="{E1A0BFE4-64BD-47FD-A10B-7359B90B3EF1}"/>
-    <hyperlink ref="G18" r:id="rId34" xr:uid="{6CBCAE4F-E4A1-4E46-B669-6E08E46B17E6}"/>
-    <hyperlink ref="G19" r:id="rId35" xr:uid="{B28235EF-B7F1-487A-B4EC-2B7FCF8DD22C}"/>
-    <hyperlink ref="G20" r:id="rId36" xr:uid="{9D39C109-4671-4A2F-84E3-53E6F9A33986}"/>
-    <hyperlink ref="G22" r:id="rId37" xr:uid="{BB56D9FD-586A-4012-8A98-46B58C26CFFF}"/>
-    <hyperlink ref="F33" r:id="rId38" xr:uid="{CA8F94AB-54B2-4396-9433-46831FD5AEBD}"/>
-    <hyperlink ref="F35" r:id="rId39" xr:uid="{B22CC345-9580-4A39-94E9-895F1A1C8833}"/>
-    <hyperlink ref="F37" r:id="rId40" xr:uid="{B1484A8D-01E4-4CD1-9249-877EF343F35D}"/>
-    <hyperlink ref="F39" r:id="rId41" display="https://eur02.safelinks.protection.outlook.com/?url=https%3A%2F%2Fmaps.app.goo.gl%2FDamK2p292amLCpfP8&amp;data=05%7C02%7Cnhenriqu%40mercadona.com%7Ce35ed0f47e244292758a08dcd25e073f%7C8f04bc3b38414627b64c594c3c7ddaac%7C0%7C0%7C638616548491244000%7CUnknown%7CTWFpbGZsb3d8eyJWIjoiMC4wLjAwMDAiLCJQIjoiV2luMzIiLCJBTiI6Ik1haWwiLCJXVCI6Mn0%3D%7C0%7C%7C%7C&amp;sdata=xyLmVVfVuqQ9RAp2VTq5dWVRcApkHhASqXz0u5nihXM%3D&amp;reserved=0" xr:uid="{6D9EC756-6E2E-4DB1-8036-DEF1A618C80C}"/>
-    <hyperlink ref="F32" r:id="rId42" xr:uid="{EDDEE375-020D-4170-B00B-0D9D0E6C79C8}"/>
-    <hyperlink ref="F28" r:id="rId43" xr:uid="{B3ED84D2-CD69-48BE-B2FD-4FB9E3C49D35}"/>
-    <hyperlink ref="F30" r:id="rId44" xr:uid="{B35EBE38-BDA5-4A7B-A336-ED3746E534A7}"/>
-    <hyperlink ref="F27" r:id="rId45" xr:uid="{BD70C6AD-0AC4-4D3D-A5A2-336BFFC510F2}"/>
-    <hyperlink ref="F26" r:id="rId46" xr:uid="{97C5DAF2-E776-4090-A752-972C3D4E4575}"/>
-    <hyperlink ref="F25" r:id="rId47" xr:uid="{0504388C-AA3B-4D66-9F77-FD78FD07E12C}"/>
-    <hyperlink ref="F31" r:id="rId48" xr:uid="{10166358-07DD-413F-BF42-F78804824B2D}"/>
+    <hyperlink ref="G16" r:id="rId33" xr:uid="{E1A0BFE4-64BD-47FD-A10B-7359B90B3EF1}"/>
+    <hyperlink ref="G20" r:id="rId34" xr:uid="{6CBCAE4F-E4A1-4E46-B669-6E08E46B17E6}"/>
+    <hyperlink ref="G23" r:id="rId35" xr:uid="{B28235EF-B7F1-487A-B4EC-2B7FCF8DD22C}"/>
+    <hyperlink ref="G29" r:id="rId36" xr:uid="{9D39C109-4671-4A2F-84E3-53E6F9A33986}"/>
+    <hyperlink ref="G34" r:id="rId37" xr:uid="{BB56D9FD-586A-4012-8A98-46B58C26CFFF}"/>
+    <hyperlink ref="F28" r:id="rId38" xr:uid="{CA8F94AB-54B2-4396-9433-46831FD5AEBD}"/>
+    <hyperlink ref="F31" r:id="rId39" xr:uid="{B22CC345-9580-4A39-94E9-895F1A1C8833}"/>
+    <hyperlink ref="F33" r:id="rId40" xr:uid="{B1484A8D-01E4-4CD1-9249-877EF343F35D}"/>
+    <hyperlink ref="F38" r:id="rId41" display="https://eur02.safelinks.protection.outlook.com/?url=https%3A%2F%2Fmaps.app.goo.gl%2FDamK2p292amLCpfP8&amp;data=05%7C02%7Cnhenriqu%40mercadona.com%7Ce35ed0f47e244292758a08dcd25e073f%7C8f04bc3b38414627b64c594c3c7ddaac%7C0%7C0%7C638616548491244000%7CUnknown%7CTWFpbGZsb3d8eyJWIjoiMC4wLjAwMDAiLCJQIjoiV2luMzIiLCJBTiI6Ik1haWwiLCJXVCI6Mn0%3D%7C0%7C%7C%7C&amp;sdata=xyLmVVfVuqQ9RAp2VTq5dWVRcApkHhASqXz0u5nihXM%3D&amp;reserved=0" xr:uid="{6D9EC756-6E2E-4DB1-8036-DEF1A618C80C}"/>
+    <hyperlink ref="F27" r:id="rId42" xr:uid="{EDDEE375-020D-4170-B00B-0D9D0E6C79C8}"/>
+    <hyperlink ref="F22" r:id="rId43" xr:uid="{B3ED84D2-CD69-48BE-B2FD-4FB9E3C49D35}"/>
+    <hyperlink ref="F25" r:id="rId44" xr:uid="{B35EBE38-BDA5-4A7B-A336-ED3746E534A7}"/>
+    <hyperlink ref="F21" r:id="rId45" xr:uid="{BD70C6AD-0AC4-4D3D-A5A2-336BFFC510F2}"/>
+    <hyperlink ref="F17" r:id="rId46" xr:uid="{97C5DAF2-E776-4090-A752-972C3D4E4575}"/>
+    <hyperlink ref="F15" r:id="rId47" xr:uid="{0504388C-AA3B-4D66-9F77-FD78FD07E12C}"/>
+    <hyperlink ref="F26" r:id="rId48" xr:uid="{10166358-07DD-413F-BF42-F78804824B2D}"/>
     <hyperlink ref="F42" r:id="rId49" xr:uid="{C2465E5F-CA73-4956-8E95-2F42980547B1}"/>
-    <hyperlink ref="F38" r:id="rId50" xr:uid="{C1484E8C-3C6E-4928-A9E1-97EEEFEC2C81}"/>
-    <hyperlink ref="F29" r:id="rId51" display="https://maps.app.goo.gl/FakydaijmJaz7n2Y7" xr:uid="{7AA9A038-313A-48A3-B3B4-6A87966BDEC6}"/>
-    <hyperlink ref="F40" r:id="rId52" xr:uid="{B025309B-6A00-4739-97F1-1BCCEB6D3E41}"/>
+    <hyperlink ref="F37" r:id="rId50" xr:uid="{C1484E8C-3C6E-4928-A9E1-97EEEFEC2C81}"/>
+    <hyperlink ref="F24" r:id="rId51" display="https://maps.app.goo.gl/FakydaijmJaz7n2Y7" xr:uid="{7AA9A038-313A-48A3-B3B4-6A87966BDEC6}"/>
+    <hyperlink ref="F39" r:id="rId52" xr:uid="{B025309B-6A00-4739-97F1-1BCCEB6D3E41}"/>
     <hyperlink ref="F44" r:id="rId53" xr:uid="{16B76CF4-A6DF-4E92-8B25-D07BF7D21E76}"/>
-    <hyperlink ref="F36" r:id="rId54" xr:uid="{54CA4F92-4C49-421C-A150-79C9468541B1}"/>
-    <hyperlink ref="F41" r:id="rId55" xr:uid="{34B95B28-3232-4392-A975-DA4AE4AF37E9}"/>
-    <hyperlink ref="G36" r:id="rId56" xr:uid="{6FA3B268-38C5-4224-980A-5CB235E07F2F}"/>
-    <hyperlink ref="G39" r:id="rId57" xr:uid="{9EA1C444-5677-429C-9343-5764CE0F041A}"/>
-    <hyperlink ref="G26" r:id="rId58" xr:uid="{CDCE51D9-7C65-4A87-88C5-AA25658084DD}"/>
-    <hyperlink ref="G25" r:id="rId59" xr:uid="{312FCA81-522A-40B6-9913-A8D55CDCAE8E}"/>
-    <hyperlink ref="G28" r:id="rId60" xr:uid="{B1500DBF-0FD4-4D27-826E-8ABDB36C0F68}"/>
-    <hyperlink ref="G31" r:id="rId61" xr:uid="{92241696-6521-493C-8961-2F0B1A8A63AF}"/>
-    <hyperlink ref="G33" r:id="rId62" xr:uid="{96EF6FF0-A504-4D92-B31F-387087DED18E}"/>
-    <hyperlink ref="G35" r:id="rId63" xr:uid="{561A3B49-8E3D-4374-BE0D-76EDE3B50F21}"/>
-    <hyperlink ref="G37" r:id="rId64" xr:uid="{105B744D-3740-444D-9DF1-D33493ED1D8B}"/>
+    <hyperlink ref="F32" r:id="rId54" xr:uid="{54CA4F92-4C49-421C-A150-79C9468541B1}"/>
+    <hyperlink ref="F40" r:id="rId55" xr:uid="{34B95B28-3232-4392-A975-DA4AE4AF37E9}"/>
+    <hyperlink ref="G32" r:id="rId56" xr:uid="{6FA3B268-38C5-4224-980A-5CB235E07F2F}"/>
+    <hyperlink ref="G38" r:id="rId57" xr:uid="{9EA1C444-5677-429C-9343-5764CE0F041A}"/>
+    <hyperlink ref="G17" r:id="rId58" xr:uid="{CDCE51D9-7C65-4A87-88C5-AA25658084DD}"/>
+    <hyperlink ref="G15" r:id="rId59" xr:uid="{312FCA81-522A-40B6-9913-A8D55CDCAE8E}"/>
+    <hyperlink ref="G22" r:id="rId60" xr:uid="{B1500DBF-0FD4-4D27-826E-8ABDB36C0F68}"/>
+    <hyperlink ref="G26" r:id="rId61" xr:uid="{92241696-6521-493C-8961-2F0B1A8A63AF}"/>
+    <hyperlink ref="G28" r:id="rId62" xr:uid="{96EF6FF0-A504-4D92-B31F-387087DED18E}"/>
+    <hyperlink ref="G31" r:id="rId63" xr:uid="{561A3B49-8E3D-4374-BE0D-76EDE3B50F21}"/>
+    <hyperlink ref="G33" r:id="rId64" xr:uid="{105B744D-3740-444D-9DF1-D33493ED1D8B}"/>
     <hyperlink ref="G42" r:id="rId65" xr:uid="{6F8A1B54-F1DF-4BD6-B244-1318F6B66CA5}"/>
-    <hyperlink ref="G40" r:id="rId66" xr:uid="{8B30F535-FF05-4EAF-91F8-D8D03E3EFCBB}"/>
-    <hyperlink ref="G30" r:id="rId67" xr:uid="{183B23FB-7465-426C-A2DA-2CF959C58F7A}"/>
-    <hyperlink ref="G27" r:id="rId68" xr:uid="{15380698-F79C-4CD5-B267-88B3253810D8}"/>
-    <hyperlink ref="G32" r:id="rId69" xr:uid="{37478915-48E4-410E-BB3A-6D3C6CC567B0}"/>
+    <hyperlink ref="G39" r:id="rId66" xr:uid="{8B30F535-FF05-4EAF-91F8-D8D03E3EFCBB}"/>
+    <hyperlink ref="G25" r:id="rId67" xr:uid="{183B23FB-7465-426C-A2DA-2CF959C58F7A}"/>
+    <hyperlink ref="G21" r:id="rId68" xr:uid="{15380698-F79C-4CD5-B267-88B3253810D8}"/>
+    <hyperlink ref="G27" r:id="rId69" xr:uid="{37478915-48E4-410E-BB3A-6D3C6CC567B0}"/>
     <hyperlink ref="G43" r:id="rId70" xr:uid="{7348BB3D-FF9C-460B-9003-572F3EA88A9B}"/>
-    <hyperlink ref="G41" r:id="rId71" xr:uid="{7ADBC77E-D7EE-4619-9DF3-D9D75ADFABA5}"/>
+    <hyperlink ref="G40" r:id="rId71" xr:uid="{7ADBC77E-D7EE-4619-9DF3-D9D75ADFABA5}"/>
     <hyperlink ref="J10" r:id="rId72" xr:uid="{CE973074-73E2-49D3-A0C3-26B5C4F2A00C}"/>
+    <hyperlink ref="F41" r:id="rId73" xr:uid="{C4846E2B-7CF8-4D84-9602-2AAE965ABC23}"/>
+    <hyperlink ref="J11" r:id="rId74" xr:uid="{C34CFF18-2B74-48FD-A8D6-DE662063BE25}"/>
+    <hyperlink ref="J4" r:id="rId75" xr:uid="{83B648D7-F200-4AF8-A7F9-1DEE7672FF34}"/>
+    <hyperlink ref="J17" r:id="rId76" xr:uid="{2C2B154B-F088-48A2-8A23-0B740AE31F8E}"/>
+    <hyperlink ref="J15" r:id="rId77" xr:uid="{CA6B44D9-44A2-44FB-8039-3BD6D79A6AD6}"/>
+    <hyperlink ref="J24" r:id="rId78" xr:uid="{32838D92-09DA-4BFD-BD97-15F06F2C8260}"/>
+    <hyperlink ref="J21" r:id="rId79" xr:uid="{A7C13944-1156-4FA2-9438-F2BEF4E7D37D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId73"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId80"/>
+  <tableParts count="1">
+    <tablePart r:id="rId81"/>
+  </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -3481,7 +3660,7 @@
   <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5546875" customWidth="1"/>
     <col min="2" max="2" width="30.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.21875" customWidth="1"/>
@@ -3544,7 +3723,7 @@
       <c r="G2" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="9">
         <v>221201095</v>
       </c>
     </row>
@@ -3570,7 +3749,7 @@
       <c r="G3" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H3" s="10">
         <v>221201098</v>
       </c>
     </row>
@@ -3596,7 +3775,7 @@
       <c r="G4" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="9">
         <v>221201094</v>
       </c>
     </row>
@@ -3622,8 +3801,11 @@
       <c r="G5" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="10">
         <v>221205059</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -3648,8 +3830,11 @@
       <c r="G6" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="9">
         <v>221205055</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -3674,8 +3859,11 @@
       <c r="G7" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="10">
         <v>221201096</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -3700,8 +3888,11 @@
       <c r="G8" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="9">
         <v>253127941</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -3726,7 +3917,7 @@
       <c r="G9" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="10">
         <v>221202911</v>
       </c>
     </row>
@@ -3752,7 +3943,7 @@
       <c r="G10" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="9">
         <v>221205056</v>
       </c>
     </row>
@@ -3778,7 +3969,7 @@
       <c r="G11" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="10">
         <v>221205057</v>
       </c>
     </row>
@@ -3804,7 +3995,7 @@
       <c r="G12" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="9">
         <v>253127942</v>
       </c>
     </row>
@@ -3830,7 +4021,7 @@
       <c r="G13" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="10">
         <v>253127943</v>
       </c>
     </row>
@@ -3850,8 +4041,11 @@
       <c r="G14" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="9">
         <v>221202910</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -3876,7 +4070,7 @@
       <c r="G15" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="10">
         <v>256120000</v>
       </c>
     </row>
@@ -3896,7 +4090,7 @@
       <c r="G16" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="9">
         <v>221202916</v>
       </c>
     </row>
@@ -3916,7 +4110,7 @@
       <c r="G17" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="10">
         <v>221205058</v>
       </c>
     </row>
@@ -3936,7 +4130,7 @@
       <c r="G18" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="9">
         <v>221202912</v>
       </c>
     </row>
@@ -3962,7 +4156,7 @@
       <c r="G19" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="10">
         <v>256120002</v>
       </c>
     </row>
@@ -3982,8 +4176,11 @@
       <c r="G20" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="9">
         <v>258127880</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4002,7 +4199,7 @@
       <c r="G21" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H21" s="10">
         <v>221202913</v>
       </c>
     </row>
@@ -4022,10 +4219,10 @@
       <c r="G22" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="9">
         <v>221202915</v>
       </c>
-      <c r="I22" s="30" t="s">
+      <c r="I22" s="20" t="s">
         <v>343</v>
       </c>
     </row>
@@ -4045,7 +4242,7 @@
       <c r="G23" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="10">
         <v>221202917</v>
       </c>
     </row>
@@ -4071,8 +4268,11 @@
       <c r="G24" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="9">
         <v>256120004</v>
+      </c>
+      <c r="I24" s="20" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4097,7 +4297,7 @@
       <c r="G25" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="H25" s="11">
+      <c r="H25" s="10">
         <v>256120003</v>
       </c>
     </row>
@@ -4117,7 +4317,7 @@
       <c r="G26" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="9">
         <v>253127944</v>
       </c>
     </row>
@@ -4137,7 +4337,7 @@
       <c r="G27" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="H27" s="11">
+      <c r="H27" s="10">
         <v>253120210</v>
       </c>
     </row>
@@ -4157,7 +4357,7 @@
       <c r="G28" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="9">
         <v>221202920</v>
       </c>
     </row>
@@ -4177,7 +4377,7 @@
       <c r="G29" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="H29" s="11">
+      <c r="H29" s="10">
         <v>221202914</v>
       </c>
     </row>
@@ -4197,7 +4397,7 @@
       <c r="G30" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="9">
         <v>221202919</v>
       </c>
     </row>
@@ -4217,7 +4417,7 @@
       <c r="G31" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="H31" s="11">
+      <c r="H31" s="10">
         <v>221202921</v>
       </c>
     </row>
@@ -4237,7 +4437,7 @@
       <c r="G32" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="H32" s="10">
+      <c r="H32" s="9">
         <v>256120250</v>
       </c>
     </row>
@@ -4263,7 +4463,7 @@
       <c r="G33" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="H33" s="11">
+      <c r="H33" s="10">
         <v>221202922</v>
       </c>
     </row>
@@ -4283,7 +4483,7 @@
       <c r="G34" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="H34" s="10">
+      <c r="H34" s="9">
         <v>221202918</v>
       </c>
     </row>
@@ -4303,7 +4503,7 @@
       <c r="G35" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="H35" s="11">
+      <c r="H35" s="10">
         <v>256120252</v>
       </c>
     </row>
@@ -4323,7 +4523,7 @@
       <c r="G36" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="H36" s="10">
+      <c r="H36" s="9">
         <v>233120010</v>
       </c>
     </row>
@@ -4343,7 +4543,7 @@
       <c r="G37" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="H37" s="11">
+      <c r="H37" s="10">
         <v>232120210</v>
       </c>
     </row>
@@ -4363,7 +4563,7 @@
       <c r="G38" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="H38" s="10">
+      <c r="H38" s="9">
         <v>259127941</v>
       </c>
     </row>
@@ -4383,7 +4583,7 @@
       <c r="G39" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="H39" s="11">
+      <c r="H39" s="10">
         <v>253120211</v>
       </c>
     </row>
@@ -4403,7 +4603,7 @@
       <c r="G40" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="H40" s="10">
+      <c r="H40" s="9">
         <v>256120251</v>
       </c>
     </row>
@@ -4423,7 +4623,7 @@
       <c r="G41" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="H41" s="11">
+      <c r="H41" s="10">
         <v>255120210</v>
       </c>
     </row>
@@ -4443,7 +4643,7 @@
       <c r="G42" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="H42" s="10">
+      <c r="H42" s="9">
         <v>255120211</v>
       </c>
     </row>
@@ -4463,7 +4663,7 @@
       <c r="G43" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="H43" s="11">
+      <c r="H43" s="10">
         <v>221202925</v>
       </c>
     </row>
@@ -4483,7 +4683,7 @@
       <c r="G44" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="H44" s="10">
+      <c r="H44" s="9">
         <v>221202923</v>
       </c>
     </row>
@@ -4503,7 +4703,7 @@
       <c r="G45" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="H45" s="11">
+      <c r="H45" s="10">
         <v>253127945</v>
       </c>
     </row>
@@ -4529,7 +4729,7 @@
       <c r="G46" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="H46" s="10">
+      <c r="H46" s="9">
         <v>239127941</v>
       </c>
     </row>
@@ -4549,7 +4749,7 @@
       <c r="G47" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="H47" s="11">
+      <c r="H47" s="10">
         <v>239127942</v>
       </c>
     </row>
@@ -4569,7 +4769,7 @@
       <c r="G48" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="H48" s="12">
+      <c r="H48" s="11">
         <v>271127941</v>
       </c>
     </row>
@@ -4589,7 +4789,7 @@
       <c r="G49" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="H49" s="13">
+      <c r="H49" s="12">
         <v>221202924</v>
       </c>
     </row>
@@ -4609,7 +4809,7 @@
       <c r="G50" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="H50" s="10">
+      <c r="H50" s="9">
         <v>255120212</v>
       </c>
     </row>
@@ -4629,11 +4829,14 @@
       <c r="G51" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="H51" s="14">
+      <c r="H51" s="13">
         <v>221201005</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J51">
+    <sortCondition ref="A1:A51"/>
+  </sortState>
   <conditionalFormatting sqref="G51">
     <cfRule type="dataBar" priority="15">
       <dataBar>
@@ -4943,8 +5146,18 @@
     <hyperlink ref="G9" r:id="rId94" xr:uid="{BAB6F0B5-8BE9-4611-A4F7-5AAC0A0080D3}"/>
     <hyperlink ref="G13" r:id="rId95" xr:uid="{3C282117-15DF-4E03-8857-1DD40EDA9FBF}"/>
     <hyperlink ref="I22" r:id="rId96" xr:uid="{F440581C-EE3F-4102-9F1C-658DEDB2E9BC}"/>
+    <hyperlink ref="I24" r:id="rId97" xr:uid="{D53C1E8E-C67C-4D65-A017-0EA9DFC5195E}"/>
+    <hyperlink ref="I20" r:id="rId98" xr:uid="{5A12FEBE-E7D3-4279-AA51-BCB64EA9FE8A}"/>
+    <hyperlink ref="I5" r:id="rId99" xr:uid="{F9667852-84E9-4BCE-901D-CF950D30B6FE}"/>
+    <hyperlink ref="I14" r:id="rId100" xr:uid="{FC683A9F-55FC-4C38-BB41-88181DF84470}"/>
+    <hyperlink ref="I8" r:id="rId101" xr:uid="{4244EB34-C911-4869-97B0-E07B44C4F4A9}"/>
+    <hyperlink ref="I7" r:id="rId102" xr:uid="{9ABCEC51-0830-458E-A3A6-26B89579CA6B}"/>
+    <hyperlink ref="I6" r:id="rId103" xr:uid="{1986B092-D8B6-454B-B194-090416A24EFE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId104"/>
+  </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>

--- a/Dados.xlsx
+++ b/Dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/paulo_martins_tja_pt/Documents/Dep. Formação/Ambiente Formadores/Mercadona HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="191" documentId="8_{3ECB6CA0-9746-43FE-8E62-14652AAF4818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{272106F4-1419-4A9E-99CB-09574A32E3AE}"/>
+  <xr:revisionPtr revIDLastSave="193" documentId="8_{3ECB6CA0-9746-43FE-8E62-14652AAF4818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{427C8B90-A0DD-45F5-906C-F881D62B978A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{462C5653-B832-456D-BA7D-C78D43202BCF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{462C5653-B832-456D-BA7D-C78D43202BCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Almeirim" sheetId="3" r:id="rId1"/>
@@ -1343,28 +1343,6 @@
   </cellStyles>
   <dxfs count="6">
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="25" formatCode="hh:mm"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -1404,6 +1382,28 @@
         <horizontal/>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1418,13 +1418,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4CADE461-DCE6-4D4D-A4A1-D312A88E939C}" name="Tabela2" displayName="Tabela2" ref="A1:K45" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4CADE461-DCE6-4D4D-A4A1-D312A88E939C}" name="Tabela2" displayName="Tabela2" ref="A1:K45" totalsRowShown="0" headerRowDxfId="5">
   <autoFilter ref="A1:K45" xr:uid="{4CADE461-DCE6-4D4D-A4A1-D312A88E939C}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K45">
     <sortCondition ref="A1:A45"/>
   </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{DC55ED28-0E01-4284-9ADF-4C1C7E0BA32F}" name="Número" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{DC55ED28-0E01-4284-9ADF-4C1C7E0BA32F}" name="Número" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{C5B39310-F969-45B5-80D4-34581D61F882}" name="Nome"/>
     <tableColumn id="3" xr3:uid="{E2DFD2FD-2B5F-44FC-9C74-960CC47BDC31}" name="Localidade"/>
     <tableColumn id="4" xr3:uid="{85FD4A60-9779-4E9B-830A-D6B5030AE8F9}" name="Morada"/>
@@ -1432,7 +1432,7 @@
     <tableColumn id="6" xr3:uid="{825D9359-5344-423D-978D-9EFF317010C6}" name="Ponto espera"/>
     <tableColumn id="7" xr3:uid="{AD1E5214-E233-4B8B-82E4-596C493537D6}" name="Precurso"/>
     <tableColumn id="8" xr3:uid="{382149AB-CE26-4792-97B6-6A989B144FA1}" name="Notas"/>
-    <tableColumn id="9" xr3:uid="{B66F1DB3-0B8D-431F-B635-14A85E95294F}" name="Contacto" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{B66F1DB3-0B8D-431F-B635-14A85E95294F}" name="Contacto" dataDxfId="3"/>
     <tableColumn id="10" xr3:uid="{805F075D-1C25-4A2C-95E3-BDA9D56884C7}" name="Video1"/>
     <tableColumn id="11" xr3:uid="{165EE159-A814-4F41-9A23-55982F96B1AB}" name="Video2"/>
   </tableColumns>
@@ -1441,7 +1441,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{91A3505B-8507-465E-8681-5F21BB7987AE}" name="Tabela1" displayName="Tabela1" ref="A1:J51" totalsRowShown="0" headerRowDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{91A3505B-8507-465E-8681-5F21BB7987AE}" name="Tabela1" displayName="Tabela1" ref="A1:J51" totalsRowShown="0" headerRowDxfId="2">
   <autoFilter ref="A1:J51" xr:uid="{91A3505B-8507-465E-8681-5F21BB7987AE}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J51">
     <sortCondition ref="A1:A51"/>
@@ -1452,8 +1452,8 @@
     <tableColumn id="3" xr3:uid="{76679A00-7A8C-48AA-A878-C65F2B3C0445}" name="Localidade"/>
     <tableColumn id="4" xr3:uid="{5920DD92-8FA3-433A-877F-5DF02D347F13}" name="Morada"/>
     <tableColumn id="5" xr3:uid="{B9B71405-06AE-45A4-9FBA-1A03F8177D30}" name="Coordenadas"/>
-    <tableColumn id="6" xr3:uid="{A0C70671-7EDF-4973-AE91-F0DCFCCF4963}" name="Ponto espera" dataDxfId="5" dataCellStyle="Hiperligação"/>
-    <tableColumn id="7" xr3:uid="{D109BFE1-D3EF-4CEB-9900-118FDB6D6828}" name="Precurso" dataDxfId="4" dataCellStyle="Hiperligação"/>
+    <tableColumn id="6" xr3:uid="{A0C70671-7EDF-4973-AE91-F0DCFCCF4963}" name="Ponto espera" dataDxfId="1" dataCellStyle="Hiperligação"/>
+    <tableColumn id="7" xr3:uid="{D109BFE1-D3EF-4CEB-9900-118FDB6D6828}" name="Precurso" dataDxfId="0" dataCellStyle="Hiperligação"/>
     <tableColumn id="8" xr3:uid="{ADF2BDD4-E4CC-4BBF-981A-CE374898476C}" name="Contacto"/>
     <tableColumn id="9" xr3:uid="{A55694C5-7C05-4149-B919-7D119BE88CA0}" name="Video1"/>
     <tableColumn id="10" xr3:uid="{C68AC60C-A3CF-43FD-9343-E9FD59397C89}" name="Video2"/>
@@ -3258,14 +3258,14 @@
     <hyperlink ref="G27" r:id="rId69" xr:uid="{37478915-48E4-410E-BB3A-6D3C6CC567B0}"/>
     <hyperlink ref="G43" r:id="rId70" xr:uid="{7348BB3D-FF9C-460B-9003-572F3EA88A9B}"/>
     <hyperlink ref="G40" r:id="rId71" xr:uid="{7ADBC77E-D7EE-4619-9DF3-D9D75ADFABA5}"/>
-    <hyperlink ref="J10" r:id="rId72" xr:uid="{CE973074-73E2-49D3-A0C3-26B5C4F2A00C}"/>
-    <hyperlink ref="F41" r:id="rId73" xr:uid="{C4846E2B-7CF8-4D84-9602-2AAE965ABC23}"/>
-    <hyperlink ref="J11" r:id="rId74" xr:uid="{C34CFF18-2B74-48FD-A8D6-DE662063BE25}"/>
-    <hyperlink ref="J4" r:id="rId75" xr:uid="{83B648D7-F200-4AF8-A7F9-1DEE7672FF34}"/>
-    <hyperlink ref="J17" r:id="rId76" xr:uid="{2C2B154B-F088-48A2-8A23-0B740AE31F8E}"/>
-    <hyperlink ref="J15" r:id="rId77" xr:uid="{CA6B44D9-44A2-44FB-8039-3BD6D79A6AD6}"/>
-    <hyperlink ref="J24" r:id="rId78" xr:uid="{32838D92-09DA-4BFD-BD97-15F06F2C8260}"/>
-    <hyperlink ref="J21" r:id="rId79" xr:uid="{A7C13944-1156-4FA2-9438-F2BEF4E7D37D}"/>
+    <hyperlink ref="F41" r:id="rId72" xr:uid="{C4846E2B-7CF8-4D84-9602-2AAE965ABC23}"/>
+    <hyperlink ref="J11" r:id="rId73" xr:uid="{C34CFF18-2B74-48FD-A8D6-DE662063BE25}"/>
+    <hyperlink ref="J4" r:id="rId74" xr:uid="{83B648D7-F200-4AF8-A7F9-1DEE7672FF34}"/>
+    <hyperlink ref="J17" r:id="rId75" xr:uid="{2C2B154B-F088-48A2-8A23-0B740AE31F8E}"/>
+    <hyperlink ref="J15" r:id="rId76" xr:uid="{CA6B44D9-44A2-44FB-8039-3BD6D79A6AD6}"/>
+    <hyperlink ref="J24" r:id="rId77" xr:uid="{32838D92-09DA-4BFD-BD97-15F06F2C8260}"/>
+    <hyperlink ref="J21" r:id="rId78" xr:uid="{A7C13944-1156-4FA2-9438-F2BEF4E7D37D}"/>
+    <hyperlink ref="J10" r:id="rId79" xr:uid="{49AB3BD4-9163-4159-92F8-2F9B0FD16C01}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId80"/>

--- a/Dados.xlsx
+++ b/Dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/paulo_martins_tja_pt/Documents/Dep. Formação/Ambiente Formadores/Mercadona HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="193" documentId="8_{3ECB6CA0-9746-43FE-8E62-14652AAF4818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{427C8B90-A0DD-45F5-906C-F881D62B978A}"/>
+  <xr:revisionPtr revIDLastSave="210" documentId="8_{3ECB6CA0-9746-43FE-8E62-14652AAF4818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EFAC087-7C4E-44EE-AF60-D6ABFB0AED9C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{462C5653-B832-456D-BA7D-C78D43202BCF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{462C5653-B832-456D-BA7D-C78D43202BCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Almeirim" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="361">
   <si>
     <t>Número</t>
   </si>
@@ -1102,6 +1102,24 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1e-T16UQ6uh9oCKt0rmLAT1S9VJ-uXotk/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>40.88565805732715, -8.489472602849132</t>
+  </si>
+  <si>
+    <t>Av. Dr. Renato Araújo 1089, 3700-232 São João da Madeira</t>
+  </si>
+  <si>
+    <t>41.338621675082955, -8.480959641178142</t>
+  </si>
+  <si>
+    <t>R. dos Trabalhadores do Arco 20, 4780-424 Santo Tirso</t>
+  </si>
+  <si>
+    <t>41.36783859151568, -8.742252967034474</t>
+  </si>
+  <si>
+    <t>Av. Gen. Humberto Delgado 380, 4480-905 Vila do Conde</t>
   </si>
 </sst>
 </file>
@@ -1847,6 +1865,12 @@
       <c r="C3" t="s">
         <v>53</v>
       </c>
+      <c r="D3" t="s">
+        <v>326</v>
+      </c>
+      <c r="E3" t="s">
+        <v>325</v>
+      </c>
       <c r="F3" s="15" t="s">
         <v>87</v>
       </c>
@@ -1867,6 +1891,12 @@
       <c r="C4" t="s">
         <v>51</v>
       </c>
+      <c r="D4" t="s">
+        <v>328</v>
+      </c>
+      <c r="E4" t="s">
+        <v>327</v>
+      </c>
       <c r="F4" s="16" t="s">
         <v>88</v>
       </c>
@@ -1890,6 +1920,12 @@
       <c r="C5" t="s">
         <v>56</v>
       </c>
+      <c r="D5" t="s">
+        <v>338</v>
+      </c>
+      <c r="E5" t="s">
+        <v>337</v>
+      </c>
       <c r="F5" s="15" t="s">
         <v>89</v>
       </c>
@@ -1910,6 +1946,12 @@
       <c r="C6" t="s">
         <v>48</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="F6" s="15" t="s">
         <v>12</v>
       </c>
@@ -1930,6 +1972,12 @@
       <c r="C7" t="s">
         <v>59</v>
       </c>
+      <c r="D7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E7" t="s">
+        <v>129</v>
+      </c>
       <c r="F7" s="14" t="s">
         <v>90</v>
       </c>
@@ -1950,6 +1998,12 @@
       <c r="C8" t="s">
         <v>61</v>
       </c>
+      <c r="D8" t="s">
+        <v>356</v>
+      </c>
+      <c r="E8" t="s">
+        <v>355</v>
+      </c>
       <c r="F8" s="15" t="s">
         <v>91</v>
       </c>
@@ -1970,6 +2024,12 @@
       <c r="C9" t="s">
         <v>59</v>
       </c>
+      <c r="D9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" t="s">
+        <v>132</v>
+      </c>
       <c r="F9" s="14" t="s">
         <v>92</v>
       </c>
@@ -2013,6 +2073,12 @@
       <c r="C11" t="s">
         <v>65</v>
       </c>
+      <c r="D11" t="s">
+        <v>320</v>
+      </c>
+      <c r="E11" t="s">
+        <v>319</v>
+      </c>
       <c r="F11" s="14" t="s">
         <v>94</v>
       </c>
@@ -2036,6 +2102,12 @@
       <c r="C12" t="s">
         <v>67</v>
       </c>
+      <c r="D12" t="s">
+        <v>133</v>
+      </c>
+      <c r="E12" t="s">
+        <v>134</v>
+      </c>
       <c r="F12" s="15" t="s">
         <v>95</v>
       </c>
@@ -2117,6 +2189,12 @@
       <c r="C16" t="s">
         <v>53</v>
       </c>
+      <c r="D16" t="s">
+        <v>321</v>
+      </c>
+      <c r="E16" t="s">
+        <v>322</v>
+      </c>
       <c r="F16" s="14" t="s">
         <v>97</v>
       </c>
@@ -2485,6 +2563,12 @@
       </c>
       <c r="C34" t="s">
         <v>82</v>
+      </c>
+      <c r="D34" t="s">
+        <v>138</v>
+      </c>
+      <c r="E34" t="s">
+        <v>137</v>
       </c>
       <c r="F34" s="15" t="s">
         <v>104</v>
@@ -4035,6 +4119,12 @@
       <c r="C14" t="s">
         <v>264</v>
       </c>
+      <c r="D14" t="s">
+        <v>358</v>
+      </c>
+      <c r="E14" t="s">
+        <v>357</v>
+      </c>
       <c r="F14" s="8" t="s">
         <v>198</v>
       </c>
@@ -4084,6 +4174,12 @@
       <c r="C16" t="s">
         <v>265</v>
       </c>
+      <c r="D16" t="s">
+        <v>360</v>
+      </c>
+      <c r="E16" t="s">
+        <v>359</v>
+      </c>
       <c r="F16" s="8" t="s">
         <v>200</v>
       </c>
@@ -4103,6 +4199,12 @@
       </c>
       <c r="C17" t="s">
         <v>61</v>
+      </c>
+      <c r="D17" t="s">
+        <v>356</v>
+      </c>
+      <c r="E17" t="s">
+        <v>355</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>201</v>

--- a/Dados.xlsx
+++ b/Dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/paulo_martins_tja_pt/Documents/Dep. Formação/Ambiente Formadores/Mercadona HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="210" documentId="8_{3ECB6CA0-9746-43FE-8E62-14652AAF4818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EFAC087-7C4E-44EE-AF60-D6ABFB0AED9C}"/>
+  <xr:revisionPtr revIDLastSave="238" documentId="8_{3ECB6CA0-9746-43FE-8E62-14652AAF4818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F38DDF6C-56B3-491E-998D-EA9209283630}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{462C5653-B832-456D-BA7D-C78D43202BCF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{462C5653-B832-456D-BA7D-C78D43202BCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Almeirim" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="379">
   <si>
     <t>Número</t>
   </si>
@@ -1120,13 +1120,67 @@
   </si>
   <si>
     <t>Av. Gen. Humberto Delgado 380, 4480-905 Vila do Conde</t>
+  </si>
+  <si>
+    <t>Alameda de Cartes 448, 4350-214 Porto</t>
+  </si>
+  <si>
+    <t>41.16315419857862, -8.575292346748252</t>
+  </si>
+  <si>
+    <t>Rua da Pasteleira 263, 4150-586 Porto</t>
+  </si>
+  <si>
+    <t>41.1534221466463, -8.653499901061133</t>
+  </si>
+  <si>
+    <t>R. Santo André 35, 4520-272 Santa Maria da Feira</t>
+  </si>
+  <si>
+    <t>40.93166889200464, -8.551782482292326</t>
+  </si>
+  <si>
+    <t>38.53938072001326, -8.867979021742425</t>
+  </si>
+  <si>
+    <t>Av. Mte. Lima de Freitas 1, 2910-865 Setúbal</t>
+  </si>
+  <si>
+    <t>38.69374701687859, -8.94839995432174</t>
+  </si>
+  <si>
+    <t>Rua do Laboratório 250, 2870-833 Setúbal</t>
+  </si>
+  <si>
+    <t>R. 12 de Dezembro 40, 3720-210 Oliveira de Azeméis</t>
+  </si>
+  <si>
+    <t>40.84002158362438, -8.479510368191654</t>
+  </si>
+  <si>
+    <t>40.159229679790045, -8.857477642499628</t>
+  </si>
+  <si>
+    <t>R. Dra. CristinaTorres 13, 3080-210 Figueira da Foz</t>
+  </si>
+  <si>
+    <t>National Road 231, 103, N231 103, 3500-606 Viseu</t>
+  </si>
+  <si>
+    <t>40.632971687502526, -7.908568718626131</t>
+  </si>
+  <si>
+    <t>R. Vitor Alves 7, 2730-250</t>
+  </si>
+  <si>
+    <t>38.74963854370516, -9.30391515512724</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1163,19 +1217,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
-      <sz val="12"/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1196,18 +1265,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1230,41 +1293,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1276,12 +1311,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1303,54 +1332,42 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1359,7 +1376,37 @@
     <cellStyle name="Hyperlink" xfId="2" xr:uid="{66064622-232A-4B66-8D8E-344707DA0960}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="25" formatCode="hh:mm"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1436,21 +1483,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4CADE461-DCE6-4D4D-A4A1-D312A88E939C}" name="Tabela2" displayName="Tabela2" ref="A1:K45" totalsRowShown="0" headerRowDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4CADE461-DCE6-4D4D-A4A1-D312A88E939C}" name="Tabela2" displayName="Tabela2" ref="A1:K45" totalsRowShown="0" headerRowDxfId="7">
   <autoFilter ref="A1:K45" xr:uid="{4CADE461-DCE6-4D4D-A4A1-D312A88E939C}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K45">
     <sortCondition ref="A1:A45"/>
   </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{DC55ED28-0E01-4284-9ADF-4C1C7E0BA32F}" name="Número" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{DC55ED28-0E01-4284-9ADF-4C1C7E0BA32F}" name="Número" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{C5B39310-F969-45B5-80D4-34581D61F882}" name="Nome"/>
     <tableColumn id="3" xr3:uid="{E2DFD2FD-2B5F-44FC-9C74-960CC47BDC31}" name="Localidade"/>
     <tableColumn id="4" xr3:uid="{85FD4A60-9779-4E9B-830A-D6B5030AE8F9}" name="Morada"/>
     <tableColumn id="5" xr3:uid="{C055D503-08E5-453C-8C5E-766522EFDFFA}" name="Coordenadas"/>
-    <tableColumn id="6" xr3:uid="{825D9359-5344-423D-978D-9EFF317010C6}" name="Ponto espera"/>
-    <tableColumn id="7" xr3:uid="{AD1E5214-E233-4B8B-82E4-596C493537D6}" name="Precurso"/>
+    <tableColumn id="6" xr3:uid="{825D9359-5344-423D-978D-9EFF317010C6}" name="Ponto espera" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{AD1E5214-E233-4B8B-82E4-596C493537D6}" name="Precurso" dataDxfId="0"/>
     <tableColumn id="8" xr3:uid="{382149AB-CE26-4792-97B6-6A989B144FA1}" name="Notas"/>
-    <tableColumn id="9" xr3:uid="{B66F1DB3-0B8D-431F-B635-14A85E95294F}" name="Contacto" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{B66F1DB3-0B8D-431F-B635-14A85E95294F}" name="Contacto" dataDxfId="5"/>
     <tableColumn id="10" xr3:uid="{805F075D-1C25-4A2C-95E3-BDA9D56884C7}" name="Video1"/>
     <tableColumn id="11" xr3:uid="{165EE159-A814-4F41-9A23-55982F96B1AB}" name="Video2"/>
   </tableColumns>
@@ -1459,7 +1506,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{91A3505B-8507-465E-8681-5F21BB7987AE}" name="Tabela1" displayName="Tabela1" ref="A1:J51" totalsRowShown="0" headerRowDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{91A3505B-8507-465E-8681-5F21BB7987AE}" name="Tabela1" displayName="Tabela1" ref="A1:J51" totalsRowShown="0" headerRowDxfId="4">
   <autoFilter ref="A1:J51" xr:uid="{91A3505B-8507-465E-8681-5F21BB7987AE}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J51">
     <sortCondition ref="A1:A51"/>
@@ -1470,8 +1517,8 @@
     <tableColumn id="3" xr3:uid="{76679A00-7A8C-48AA-A878-C65F2B3C0445}" name="Localidade"/>
     <tableColumn id="4" xr3:uid="{5920DD92-8FA3-433A-877F-5DF02D347F13}" name="Morada"/>
     <tableColumn id="5" xr3:uid="{B9B71405-06AE-45A4-9FBA-1A03F8177D30}" name="Coordenadas"/>
-    <tableColumn id="6" xr3:uid="{A0C70671-7EDF-4973-AE91-F0DCFCCF4963}" name="Ponto espera" dataDxfId="1" dataCellStyle="Hiperligação"/>
-    <tableColumn id="7" xr3:uid="{D109BFE1-D3EF-4CEB-9900-118FDB6D6828}" name="Precurso" dataDxfId="0" dataCellStyle="Hiperligação"/>
+    <tableColumn id="6" xr3:uid="{A0C70671-7EDF-4973-AE91-F0DCFCCF4963}" name="Ponto espera" dataDxfId="3" dataCellStyle="Hiperligação"/>
+    <tableColumn id="7" xr3:uid="{D109BFE1-D3EF-4CEB-9900-118FDB6D6828}" name="Precurso" dataDxfId="2" dataCellStyle="Hiperligação"/>
     <tableColumn id="8" xr3:uid="{ADF2BDD4-E4CC-4BBF-981A-CE374898476C}" name="Contacto"/>
     <tableColumn id="9" xr3:uid="{A55694C5-7C05-4149-B919-7D119BE88CA0}" name="Video1"/>
     <tableColumn id="10" xr3:uid="{C68AC60C-A3CF-43FD-9343-E9FD59397C89}" name="Video2"/>
@@ -1785,45 +1832,45 @@
     <col min="3" max="3" width="18.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="33.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="36.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15" style="18" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" style="18" customWidth="1"/>
     <col min="8" max="8" width="7.77734375" customWidth="1"/>
-    <col min="9" max="9" width="10.88671875" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.88671875" style="12" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="18.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="I1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="J1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="K1" s="15" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1843,14 +1890,14 @@
       <c r="E2" t="s">
         <v>136</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="20" t="s">
         <v>107</v>
       </c>
       <c r="H2" s="3"/>
-      <c r="I2" s="19">
+      <c r="I2" s="12">
         <v>221201095</v>
       </c>
       <c r="J2" s="2"/>
@@ -1871,13 +1918,13 @@
       <c r="E3" t="s">
         <v>325</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="12">
         <v>221201094</v>
       </c>
     </row>
@@ -1897,16 +1944,16 @@
       <c r="E4" t="s">
         <v>327</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="I4" s="19">
+      <c r="I4" s="12">
         <v>221205059</v>
       </c>
-      <c r="J4" s="20" t="s">
+      <c r="J4" s="13" t="s">
         <v>346</v>
       </c>
     </row>
@@ -1926,13 +1973,13 @@
       <c r="E5" t="s">
         <v>337</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="I5" s="19">
+      <c r="I5" s="12">
         <v>221205056</v>
       </c>
     </row>
@@ -1952,13 +1999,13 @@
       <c r="E6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="12">
         <v>221205057</v>
       </c>
     </row>
@@ -1978,13 +2025,13 @@
       <c r="E7" t="s">
         <v>129</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="I7" s="19">
+      <c r="I7" s="12">
         <v>256120000</v>
       </c>
     </row>
@@ -2004,13 +2051,13 @@
       <c r="E8" t="s">
         <v>355</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="I8" s="19">
+      <c r="I8" s="12">
         <v>221205058</v>
       </c>
     </row>
@@ -2030,13 +2077,13 @@
       <c r="E9" t="s">
         <v>132</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="I9" s="19">
+      <c r="I9" s="12">
         <v>256120002</v>
       </c>
     </row>
@@ -2050,16 +2097,22 @@
       <c r="C10" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="D10" t="s">
+        <v>361</v>
+      </c>
+      <c r="E10" t="s">
+        <v>362</v>
+      </c>
+      <c r="F10" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="I10" s="19">
+      <c r="I10" s="12">
         <v>221202915</v>
       </c>
-      <c r="J10" s="20" t="s">
+      <c r="J10" s="13" t="s">
         <v>343</v>
       </c>
     </row>
@@ -2079,16 +2132,16 @@
       <c r="E11" t="s">
         <v>319</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="I11" s="19">
+      <c r="I11" s="12">
         <v>256120004</v>
       </c>
-      <c r="J11" s="20" t="s">
+      <c r="J11" s="13" t="s">
         <v>344</v>
       </c>
     </row>
@@ -2108,13 +2161,13 @@
       <c r="E12" t="s">
         <v>134</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="I12" s="19">
+      <c r="I12" s="12">
         <v>256120003</v>
       </c>
     </row>
@@ -2128,11 +2181,17 @@
       <c r="C13" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="14"/>
-      <c r="G13" s="5" t="s">
+      <c r="D13" t="s">
+        <v>363</v>
+      </c>
+      <c r="E13" t="s">
+        <v>364</v>
+      </c>
+      <c r="F13" s="19"/>
+      <c r="G13" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="I13" s="19">
+      <c r="I13" s="12">
         <v>221202919</v>
       </c>
     </row>
@@ -2146,13 +2205,19 @@
       <c r="C14" t="s">
         <v>70</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="D14" t="s">
+        <v>365</v>
+      </c>
+      <c r="E14" t="s">
+        <v>366</v>
+      </c>
+      <c r="F14" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="I14" s="19">
+      <c r="I14" s="12">
         <v>256120250</v>
       </c>
     </row>
@@ -2166,16 +2231,22 @@
       <c r="C15" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="24" t="s">
+      <c r="D15" t="s">
+        <v>368</v>
+      </c>
+      <c r="E15" t="s">
+        <v>367</v>
+      </c>
+      <c r="F15" s="22" t="s">
         <v>278</v>
       </c>
-      <c r="G15" s="24" t="s">
+      <c r="G15" s="22" t="s">
         <v>298</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="12">
         <v>265121501</v>
       </c>
-      <c r="J15" s="20" t="s">
+      <c r="J15" s="13" t="s">
         <v>350</v>
       </c>
     </row>
@@ -2195,13 +2266,13 @@
       <c r="E16" t="s">
         <v>322</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="12">
         <v>221202922</v>
       </c>
     </row>
@@ -2215,16 +2286,22 @@
       <c r="C17" t="s">
         <v>44</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="D17" t="s">
+        <v>370</v>
+      </c>
+      <c r="E17" t="s">
+        <v>369</v>
+      </c>
+      <c r="F17" s="20" t="s">
         <v>279</v>
       </c>
-      <c r="G17" s="26" t="s">
+      <c r="G17" s="22" t="s">
         <v>299</v>
       </c>
-      <c r="I17" s="19">
+      <c r="I17" s="12">
         <v>211202941</v>
       </c>
-      <c r="J17" s="20" t="s">
+      <c r="J17" s="13" t="s">
         <v>347</v>
       </c>
     </row>
@@ -2238,13 +2315,19 @@
       <c r="C18" t="s">
         <v>73</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="D18" t="s">
+        <v>371</v>
+      </c>
+      <c r="E18" t="s">
+        <v>372</v>
+      </c>
+      <c r="F18" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="I18" s="19">
+      <c r="I18" s="12">
         <v>256120252</v>
       </c>
     </row>
@@ -2258,13 +2341,19 @@
       <c r="C19" t="s">
         <v>75</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="D19" t="s">
+        <v>374</v>
+      </c>
+      <c r="E19" t="s">
+        <v>373</v>
+      </c>
+      <c r="F19" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="I19" s="19">
+      <c r="I19" s="12">
         <v>233120010</v>
       </c>
     </row>
@@ -2278,13 +2367,19 @@
       <c r="C20" t="s">
         <v>77</v>
       </c>
-      <c r="F20" s="15" t="s">
+      <c r="D20" t="s">
+        <v>375</v>
+      </c>
+      <c r="E20" t="s">
+        <v>376</v>
+      </c>
+      <c r="F20" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="12">
         <v>232120210</v>
       </c>
     </row>
@@ -2298,16 +2393,22 @@
       <c r="C21" t="s">
         <v>42</v>
       </c>
-      <c r="F21" s="25" t="s">
+      <c r="D21" t="s">
+        <v>377</v>
+      </c>
+      <c r="E21" t="s">
+        <v>378</v>
+      </c>
+      <c r="F21" s="23" t="s">
         <v>280</v>
       </c>
-      <c r="G21" s="24" t="s">
+      <c r="G21" s="22" t="s">
         <v>300</v>
       </c>
-      <c r="I21" s="19">
+      <c r="I21" s="12">
         <v>211202943</v>
       </c>
-      <c r="J21" s="20" t="s">
+      <c r="J21" s="13" t="s">
         <v>354</v>
       </c>
     </row>
@@ -2321,13 +2422,13 @@
       <c r="C22" t="s">
         <v>35</v>
       </c>
-      <c r="F22" s="26" t="s">
+      <c r="F22" s="22" t="s">
         <v>281</v>
       </c>
-      <c r="G22" s="26" t="s">
+      <c r="G22" s="22" t="s">
         <v>301</v>
       </c>
-      <c r="I22" s="19">
+      <c r="I22" s="12">
         <v>211202942</v>
       </c>
     </row>
@@ -2341,13 +2442,13 @@
       <c r="C23" t="s">
         <v>79</v>
       </c>
-      <c r="F23" s="16" t="s">
+      <c r="F23" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="G23" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="I23" s="19">
+      <c r="I23" s="12">
         <v>256120251</v>
       </c>
     </row>
@@ -2361,16 +2462,16 @@
       <c r="C24" t="s">
         <v>39</v>
       </c>
-      <c r="F24" s="30" t="s">
+      <c r="F24" s="23" t="s">
         <v>282</v>
       </c>
-      <c r="G24" s="31" t="s">
+      <c r="G24" s="22" t="s">
         <v>302</v>
       </c>
-      <c r="I24" s="19">
+      <c r="I24" s="12">
         <v>243120160</v>
       </c>
-      <c r="J24" s="20" t="s">
+      <c r="J24" s="13" t="s">
         <v>353</v>
       </c>
     </row>
@@ -2384,13 +2485,13 @@
       <c r="C25" t="s">
         <v>35</v>
       </c>
-      <c r="F25" s="26" t="s">
+      <c r="F25" s="22" t="s">
         <v>283</v>
       </c>
-      <c r="G25" s="26" t="s">
+      <c r="G25" s="22" t="s">
         <v>303</v>
       </c>
-      <c r="I25" s="19">
+      <c r="I25" s="12">
         <v>211202946</v>
       </c>
     </row>
@@ -2404,13 +2505,13 @@
       <c r="C26" t="s">
         <v>37</v>
       </c>
-      <c r="F26" s="24" t="s">
+      <c r="F26" s="22" t="s">
         <v>284</v>
       </c>
-      <c r="G26" s="24" t="s">
+      <c r="G26" s="22" t="s">
         <v>304</v>
       </c>
-      <c r="I26" s="19">
+      <c r="I26" s="12">
         <v>262130010</v>
       </c>
     </row>
@@ -2424,13 +2525,13 @@
       <c r="C27" t="s">
         <v>35</v>
       </c>
-      <c r="F27" s="26" t="s">
+      <c r="F27" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="G27" s="26" t="s">
+      <c r="G27" s="22" t="s">
         <v>305</v>
       </c>
-      <c r="I27" s="19">
+      <c r="I27" s="12">
         <v>211202945</v>
       </c>
     </row>
@@ -2444,13 +2545,13 @@
       <c r="C28" t="s">
         <v>34</v>
       </c>
-      <c r="F28" s="24" t="s">
+      <c r="F28" s="22" t="s">
         <v>286</v>
       </c>
-      <c r="G28" s="24" t="s">
+      <c r="G28" s="22" t="s">
         <v>306</v>
       </c>
-      <c r="I28" s="19">
+      <c r="I28" s="12">
         <v>261133001</v>
       </c>
     </row>
@@ -2464,13 +2565,13 @@
       <c r="C29" t="s">
         <v>51</v>
       </c>
-      <c r="F29" s="18" t="s">
+      <c r="F29" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="I29" s="19">
+      <c r="I29" s="12">
         <v>221202923</v>
       </c>
     </row>
@@ -2484,13 +2585,13 @@
       <c r="C30" t="s">
         <v>22</v>
       </c>
-      <c r="F30" s="26" t="s">
+      <c r="F30" s="22" t="s">
         <v>287</v>
       </c>
-      <c r="G30" s="26" t="s">
+      <c r="G30" s="22" t="s">
         <v>307</v>
       </c>
-      <c r="I30" s="19">
+      <c r="I30" s="12">
         <v>211202951</v>
       </c>
     </row>
@@ -2504,13 +2605,13 @@
       <c r="C31" t="s">
         <v>31</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="F31" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="G31" s="24" t="s">
+      <c r="G31" s="22" t="s">
         <v>308</v>
       </c>
-      <c r="I31" s="19">
+      <c r="I31" s="12">
         <v>263137011</v>
       </c>
     </row>
@@ -2524,13 +2625,13 @@
       <c r="C32" t="s">
         <v>30</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="G32" s="26" t="s">
+      <c r="G32" s="22" t="s">
         <v>309</v>
       </c>
-      <c r="I32" s="19">
+      <c r="I32" s="12">
         <v>266127951</v>
       </c>
     </row>
@@ -2544,13 +2645,13 @@
       <c r="C33" t="s">
         <v>28</v>
       </c>
-      <c r="F33" s="24" t="s">
+      <c r="F33" s="22" t="s">
         <v>290</v>
       </c>
-      <c r="G33" s="24" t="s">
+      <c r="G33" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="I33" s="19">
+      <c r="I33" s="12">
         <v>265121502</v>
       </c>
     </row>
@@ -2570,13 +2671,13 @@
       <c r="E34" t="s">
         <v>137</v>
       </c>
-      <c r="F34" s="15" t="s">
+      <c r="F34" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="G34" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="I34" s="19">
+      <c r="I34" s="12">
         <v>239127941</v>
       </c>
     </row>
@@ -2590,13 +2691,13 @@
       <c r="C35" t="s">
         <v>82</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="F35" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="G35" s="5" t="s">
+      <c r="G35" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="I35" s="19">
+      <c r="I35" s="12">
         <v>239127942</v>
       </c>
     </row>
@@ -2610,13 +2711,13 @@
       <c r="C36" t="s">
         <v>84</v>
       </c>
-      <c r="F36" s="14" t="s">
+      <c r="F36" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="G36" s="5" t="s">
+      <c r="G36" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="I36" s="19">
+      <c r="I36" s="12">
         <v>271127941</v>
       </c>
     </row>
@@ -2630,13 +2731,13 @@
       <c r="C37" t="s">
         <v>26</v>
       </c>
-      <c r="F37" s="26" t="s">
+      <c r="F37" s="22" t="s">
         <v>291</v>
       </c>
-      <c r="G37" s="26" t="s">
+      <c r="G37" s="22" t="s">
         <v>311</v>
       </c>
-      <c r="I37" s="19">
+      <c r="I37" s="12">
         <v>211202947</v>
       </c>
     </row>
@@ -2650,13 +2751,13 @@
       <c r="C38" t="s">
         <v>18</v>
       </c>
-      <c r="F38" s="24" t="s">
+      <c r="F38" s="22" t="s">
         <v>292</v>
       </c>
-      <c r="G38" s="24" t="s">
+      <c r="G38" s="22" t="s">
         <v>312</v>
       </c>
-      <c r="I38" s="19">
+      <c r="I38" s="12">
         <v>244122590</v>
       </c>
     </row>
@@ -2670,13 +2771,13 @@
       <c r="C39" t="s">
         <v>24</v>
       </c>
-      <c r="F39" s="27" t="s">
+      <c r="F39" s="24" t="s">
         <v>293</v>
       </c>
-      <c r="G39" s="26" t="s">
+      <c r="G39" s="22" t="s">
         <v>313</v>
       </c>
-      <c r="I39" s="19">
+      <c r="I39" s="12">
         <v>910759388</v>
       </c>
     </row>
@@ -2690,10 +2791,10 @@
       <c r="C40" t="s">
         <v>22</v>
       </c>
-      <c r="F40" s="5" t="s">
+      <c r="F40" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="G40" s="5" t="s">
+      <c r="G40" s="20" t="s">
         <v>314</v>
       </c>
     </row>
@@ -2707,13 +2808,13 @@
       <c r="C41" t="s">
         <v>56</v>
       </c>
-      <c r="F41" s="15" t="s">
+      <c r="F41" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="G41" s="6" t="s">
+      <c r="G41" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="I41" s="19">
+      <c r="I41" s="12">
         <v>221201005</v>
       </c>
     </row>
@@ -2727,13 +2828,13 @@
       <c r="C42" t="s">
         <v>20</v>
       </c>
-      <c r="F42" s="26" t="s">
+      <c r="F42" s="22" t="s">
         <v>295</v>
       </c>
-      <c r="G42" s="26" t="s">
+      <c r="G42" s="22" t="s">
         <v>315</v>
       </c>
-      <c r="I42" s="19">
+      <c r="I42" s="12">
         <v>211202948</v>
       </c>
     </row>
@@ -2747,13 +2848,13 @@
       <c r="C43" t="s">
         <v>18</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="F43" s="20" t="s">
         <v>296</v>
       </c>
-      <c r="G43" s="5" t="s">
+      <c r="G43" s="20" t="s">
         <v>316</v>
       </c>
-      <c r="I43" s="19">
+      <c r="I43" s="12">
         <v>244122591</v>
       </c>
     </row>
@@ -2767,13 +2868,13 @@
       <c r="C44" t="s">
         <v>16</v>
       </c>
-      <c r="F44" s="6" t="s">
+      <c r="F44" s="20" t="s">
         <v>297</v>
       </c>
-      <c r="G44" s="29" t="s">
+      <c r="G44" s="22" t="s">
         <v>317</v>
       </c>
-      <c r="I44" s="19" t="s">
+      <c r="I44" s="12" t="s">
         <v>318</v>
       </c>
     </row>
@@ -2787,8 +2888,8 @@
       <c r="C45" t="s">
         <v>14</v>
       </c>
-      <c r="F45" s="28"/>
-      <c r="G45" s="24"/>
+      <c r="F45" s="25"/>
+      <c r="G45" s="22"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K45">
@@ -3350,11 +3451,13 @@
     <hyperlink ref="J24" r:id="rId77" xr:uid="{32838D92-09DA-4BFD-BD97-15F06F2C8260}"/>
     <hyperlink ref="J21" r:id="rId78" xr:uid="{A7C13944-1156-4FA2-9438-F2BEF4E7D37D}"/>
     <hyperlink ref="J10" r:id="rId79" xr:uid="{49AB3BD4-9163-4159-92F8-2F9B0FD16C01}"/>
+    <hyperlink ref="G14" r:id="rId80" xr:uid="{372B9FA1-A43D-4401-B0C9-C9F47C3A905D}"/>
+    <hyperlink ref="G18" r:id="rId81" xr:uid="{0BCBE971-E86A-4EF2-9A4B-88B231B8759B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId80"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId82"/>
   <tableParts count="1">
-    <tablePart r:id="rId81"/>
+    <tablePart r:id="rId83"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -3801,13 +3904,13 @@
       <c r="E2" t="s">
         <v>136</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="7">
         <v>221201095</v>
       </c>
     </row>
@@ -3827,13 +3930,13 @@
       <c r="E3" t="s">
         <v>323</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="8">
         <v>221201098</v>
       </c>
     </row>
@@ -3853,13 +3956,13 @@
       <c r="E4" t="s">
         <v>325</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="7">
         <v>221201094</v>
       </c>
     </row>
@@ -3879,16 +3982,16 @@
       <c r="E5" t="s">
         <v>327</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="8">
         <v>221205059</v>
       </c>
-      <c r="I5" s="20" t="s">
+      <c r="I5" s="13" t="s">
         <v>346</v>
       </c>
     </row>
@@ -3908,16 +4011,16 @@
       <c r="E6" t="s">
         <v>330</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="7">
         <v>221205055</v>
       </c>
-      <c r="I6" s="20" t="s">
+      <c r="I6" s="13" t="s">
         <v>352</v>
       </c>
     </row>
@@ -3937,16 +4040,16 @@
       <c r="E7" t="s">
         <v>331</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="8">
         <v>221201096</v>
       </c>
-      <c r="I7" s="20" t="s">
+      <c r="I7" s="13" t="s">
         <v>351</v>
       </c>
     </row>
@@ -3966,16 +4069,16 @@
       <c r="E8" t="s">
         <v>334</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="7">
         <v>253127941</v>
       </c>
-      <c r="I8" s="20" t="s">
+      <c r="I8" s="13" t="s">
         <v>349</v>
       </c>
     </row>
@@ -3995,13 +4098,13 @@
       <c r="E9" t="s">
         <v>335</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="8">
         <v>221202911</v>
       </c>
     </row>
@@ -4021,13 +4124,13 @@
       <c r="E10" t="s">
         <v>337</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="7">
         <v>221205056</v>
       </c>
     </row>
@@ -4047,13 +4150,13 @@
       <c r="E11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="8">
         <v>221205057</v>
       </c>
     </row>
@@ -4073,13 +4176,13 @@
       <c r="E12" t="s">
         <v>340</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="7">
         <v>253127942</v>
       </c>
     </row>
@@ -4099,13 +4202,13 @@
       <c r="E13" t="s">
         <v>341</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="8">
         <v>253127943</v>
       </c>
     </row>
@@ -4125,16 +4228,16 @@
       <c r="E14" t="s">
         <v>357</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="7">
         <v>221202910</v>
       </c>
-      <c r="I14" s="20" t="s">
+      <c r="I14" s="13" t="s">
         <v>348</v>
       </c>
     </row>
@@ -4154,13 +4257,13 @@
       <c r="E15" t="s">
         <v>129</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="8">
         <v>256120000</v>
       </c>
     </row>
@@ -4180,13 +4283,13 @@
       <c r="E16" t="s">
         <v>359</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="7">
         <v>221202916</v>
       </c>
     </row>
@@ -4206,13 +4309,13 @@
       <c r="E17" t="s">
         <v>355</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="8">
         <v>221205058</v>
       </c>
     </row>
@@ -4226,13 +4329,13 @@
       <c r="C18" t="s">
         <v>266</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="7">
         <v>221202912</v>
       </c>
     </row>
@@ -4252,13 +4355,13 @@
       <c r="E19" t="s">
         <v>132</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="8">
         <v>256120002</v>
       </c>
     </row>
@@ -4272,16 +4375,16 @@
       <c r="C20" t="s">
         <v>267</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G20" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="7">
         <v>258127880</v>
       </c>
-      <c r="I20" s="20" t="s">
+      <c r="I20" s="13" t="s">
         <v>345</v>
       </c>
     </row>
@@ -4295,13 +4398,13 @@
       <c r="C21" t="s">
         <v>268</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="G21" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="8">
         <v>221202913</v>
       </c>
     </row>
@@ -4315,16 +4418,16 @@
       <c r="C22" t="s">
         <v>56</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="G22" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="7">
         <v>221202915</v>
       </c>
-      <c r="I22" s="20" t="s">
+      <c r="I22" s="13" t="s">
         <v>343</v>
       </c>
     </row>
@@ -4338,13 +4441,13 @@
       <c r="C23" t="s">
         <v>269</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="G23" s="7" t="s">
+      <c r="G23" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="8">
         <v>221202917</v>
       </c>
     </row>
@@ -4364,16 +4467,16 @@
       <c r="E24" t="s">
         <v>319</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="G24" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="7">
         <v>256120004</v>
       </c>
-      <c r="I24" s="20" t="s">
+      <c r="I24" s="13" t="s">
         <v>344</v>
       </c>
     </row>
@@ -4393,13 +4496,13 @@
       <c r="E25" t="s">
         <v>134</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="G25" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="H25" s="10">
+      <c r="H25" s="8">
         <v>256120003</v>
       </c>
     </row>
@@ -4413,13 +4516,13 @@
       <c r="C26" t="s">
         <v>270</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="G26" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="7">
         <v>253127944</v>
       </c>
     </row>
@@ -4433,13 +4536,13 @@
       <c r="C27" t="s">
         <v>260</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="G27" s="7" t="s">
+      <c r="G27" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="8">
         <v>253120210</v>
       </c>
     </row>
@@ -4453,13 +4556,13 @@
       <c r="C28" t="s">
         <v>271</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="G28" s="8" t="s">
+      <c r="G28" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="7">
         <v>221202920</v>
       </c>
     </row>
@@ -4473,13 +4576,13 @@
       <c r="C29" t="s">
         <v>272</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="G29" s="7" t="s">
+      <c r="G29" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="8">
         <v>221202914</v>
       </c>
     </row>
@@ -4493,13 +4596,13 @@
       <c r="C30" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="8" t="s">
+      <c r="F30" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="G30" s="8" t="s">
+      <c r="G30" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="H30" s="9">
+      <c r="H30" s="7">
         <v>221202919</v>
       </c>
     </row>
@@ -4513,13 +4616,13 @@
       <c r="C31" t="s">
         <v>273</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="G31" s="7" t="s">
+      <c r="G31" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="8">
         <v>221202921</v>
       </c>
     </row>
@@ -4533,13 +4636,13 @@
       <c r="C32" t="s">
         <v>70</v>
       </c>
-      <c r="F32" s="8" t="s">
+      <c r="F32" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="G32" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="H32" s="9">
+      <c r="H32" s="7">
         <v>256120250</v>
       </c>
     </row>
@@ -4559,13 +4662,13 @@
       <c r="E33" t="s">
         <v>322</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="G33" s="7" t="s">
+      <c r="G33" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="H33" s="10">
+      <c r="H33" s="8">
         <v>221202922</v>
       </c>
     </row>
@@ -4579,13 +4682,13 @@
       <c r="C34" t="s">
         <v>274</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="F34" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="G34" s="8" t="s">
+      <c r="G34" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H34" s="9">
+      <c r="H34" s="7">
         <v>221202918</v>
       </c>
     </row>
@@ -4599,13 +4702,13 @@
       <c r="C35" t="s">
         <v>73</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="G35" s="7" t="s">
+      <c r="G35" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="H35" s="10">
+      <c r="H35" s="8">
         <v>256120252</v>
       </c>
     </row>
@@ -4619,13 +4722,13 @@
       <c r="C36" t="s">
         <v>75</v>
       </c>
-      <c r="F36" s="8" t="s">
+      <c r="F36" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="G36" s="8" t="s">
+      <c r="G36" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="H36" s="9">
+      <c r="H36" s="7">
         <v>233120010</v>
       </c>
     </row>
@@ -4639,13 +4742,13 @@
       <c r="C37" t="s">
         <v>77</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F37" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="G37" s="7" t="s">
+      <c r="G37" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="H37" s="10">
+      <c r="H37" s="8">
         <v>232120210</v>
       </c>
     </row>
@@ -4659,13 +4762,13 @@
       <c r="C38" t="s">
         <v>250</v>
       </c>
-      <c r="F38" s="8" t="s">
+      <c r="F38" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="G38" s="8" t="s">
+      <c r="G38" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="H38" s="9">
+      <c r="H38" s="7">
         <v>259127941</v>
       </c>
     </row>
@@ -4679,13 +4782,13 @@
       <c r="C39" t="s">
         <v>260</v>
       </c>
-      <c r="F39" s="7" t="s">
+      <c r="F39" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="G39" s="7" t="s">
+      <c r="G39" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="H39" s="10">
+      <c r="H39" s="8">
         <v>253120211</v>
       </c>
     </row>
@@ -4699,13 +4802,13 @@
       <c r="C40" t="s">
         <v>79</v>
       </c>
-      <c r="F40" s="8" t="s">
+      <c r="F40" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="G40" s="8" t="s">
+      <c r="G40" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="H40" s="9">
+      <c r="H40" s="7">
         <v>256120251</v>
       </c>
     </row>
@@ -4719,13 +4822,13 @@
       <c r="C41" t="s">
         <v>275</v>
       </c>
-      <c r="F41" s="7" t="s">
+      <c r="F41" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="G41" s="7" t="s">
+      <c r="G41" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="H41" s="10">
+      <c r="H41" s="8">
         <v>255120210</v>
       </c>
     </row>
@@ -4739,13 +4842,13 @@
       <c r="C42" t="s">
         <v>276</v>
       </c>
-      <c r="F42" s="8" t="s">
+      <c r="F42" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="G42" s="8" t="s">
+      <c r="G42" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="H42" s="9">
+      <c r="H42" s="7">
         <v>255120211</v>
       </c>
     </row>
@@ -4759,13 +4862,13 @@
       <c r="C43" t="s">
         <v>259</v>
       </c>
-      <c r="F43" s="7" t="s">
+      <c r="F43" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="G43" s="7" t="s">
+      <c r="G43" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="H43" s="10">
+      <c r="H43" s="8">
         <v>221202925</v>
       </c>
     </row>
@@ -4779,13 +4882,13 @@
       <c r="C44" t="s">
         <v>51</v>
       </c>
-      <c r="F44" s="8" t="s">
+      <c r="F44" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G44" s="8" t="s">
+      <c r="G44" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="H44" s="9">
+      <c r="H44" s="7">
         <v>221202923</v>
       </c>
     </row>
@@ -4799,13 +4902,13 @@
       <c r="C45" t="s">
         <v>277</v>
       </c>
-      <c r="F45" s="7" t="s">
+      <c r="F45" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="G45" s="7" t="s">
+      <c r="G45" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="H45" s="10">
+      <c r="H45" s="8">
         <v>253127945</v>
       </c>
     </row>
@@ -4825,13 +4928,13 @@
       <c r="E46" t="s">
         <v>137</v>
       </c>
-      <c r="F46" s="8" t="s">
+      <c r="F46" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="G46" s="8" t="s">
+      <c r="G46" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="H46" s="9">
+      <c r="H46" s="7">
         <v>239127941</v>
       </c>
     </row>
@@ -4845,13 +4948,13 @@
       <c r="C47" t="s">
         <v>82</v>
       </c>
-      <c r="F47" s="7" t="s">
+      <c r="F47" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="G47" s="7" t="s">
+      <c r="G47" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="H47" s="10">
+      <c r="H47" s="8">
         <v>239127942</v>
       </c>
     </row>
@@ -4865,13 +4968,13 @@
       <c r="C48" t="s">
         <v>84</v>
       </c>
-      <c r="F48" s="8" t="s">
+      <c r="F48" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="G48" s="8" t="s">
+      <c r="G48" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="H48" s="11">
+      <c r="H48" s="9">
         <v>271127941</v>
       </c>
     </row>
@@ -4885,13 +4988,13 @@
       <c r="C49" t="s">
         <v>233</v>
       </c>
-      <c r="F49" s="7" t="s">
+      <c r="F49" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="G49" s="7" t="s">
+      <c r="G49" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="H49" s="12">
+      <c r="H49" s="10">
         <v>221202924</v>
       </c>
     </row>
@@ -4905,13 +5008,13 @@
       <c r="C50" t="s">
         <v>261</v>
       </c>
-      <c r="F50" s="8" t="s">
+      <c r="F50" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="G50" s="8" t="s">
+      <c r="G50" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="H50" s="9">
+      <c r="H50" s="7">
         <v>255120212</v>
       </c>
     </row>
@@ -4925,13 +5028,13 @@
       <c r="C51" t="s">
         <v>56</v>
       </c>
-      <c r="F51" s="7" t="s">
+      <c r="F51" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="G51" s="7" t="s">
+      <c r="G51" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="H51" s="13">
+      <c r="H51" s="11">
         <v>221201005</v>
       </c>
     </row>
